--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V55"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -481,6 +481,8 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,65 +533,75 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Actual FY23-24</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Actual FY24-25</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>ELI Near Term</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ELI Med Term</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>FY24-25</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>FY25-26</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Curt FY1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Curt FY2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Curt FY3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Curt Avg</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Offl FY1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Offl FY2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Offl FY3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
         </is>
@@ -632,24 +644,28 @@
       </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="n">
+      <c r="K2" s="5" t="n">
+        <v>7.689919976716642e-05</v>
+      </c>
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="n">
         <v>0.9659</v>
       </c>
-      <c r="M2" s="5" t="n">
+      <c r="O2" s="5" t="n">
         <v>0.9318</v>
       </c>
-      <c r="N2" s="5" t="n">
+      <c r="P2" s="5" t="n">
         <v>0.9029</v>
       </c>
-      <c r="O2" s="6" t="inlineStr"/>
-      <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="6" t="inlineStr"/>
       <c r="R2" s="6" t="inlineStr"/>
       <c r="S2" s="6" t="inlineStr"/>
       <c r="T2" s="6" t="inlineStr"/>
       <c r="U2" s="6" t="inlineStr"/>
       <c r="V2" s="6" t="inlineStr"/>
+      <c r="W2" s="6" t="inlineStr"/>
+      <c r="X2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -693,29 +709,31 @@
       <c r="I3" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="M3" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="N3" s="5" t="n">
         <v>0.9442</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="O3" s="5" t="n">
         <v>0.9593</v>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="P3" s="5" t="n">
         <v>0.9461000000000001</v>
       </c>
-      <c r="O3" s="6" t="inlineStr"/>
-      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr"/>
       <c r="S3" s="6" t="inlineStr"/>
       <c r="T3" s="6" t="inlineStr"/>
       <c r="U3" s="6" t="inlineStr"/>
       <c r="V3" s="6" t="inlineStr"/>
+      <c r="W3" s="6" t="inlineStr"/>
+      <c r="X3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -755,23 +773,25 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="n">
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="n">
         <v>0.9370000000000001</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="O4" s="5" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="N4" s="5" t="n">
+      <c r="P4" s="5" t="n">
         <v>0.9009</v>
       </c>
-      <c r="O4" s="6" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="6" t="inlineStr"/>
       <c r="R4" s="6" t="inlineStr"/>
       <c r="S4" s="6" t="inlineStr"/>
       <c r="T4" s="6" t="inlineStr"/>
       <c r="U4" s="6" t="inlineStr"/>
       <c r="V4" s="6" t="inlineStr"/>
+      <c r="W4" s="6" t="inlineStr"/>
+      <c r="X4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -816,26 +836,26 @@
         <v>132</v>
       </c>
       <c r="J5" s="5" t="n">
+        <v>0.05651030523317557</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.02317489340857803</v>
+      </c>
+      <c r="L5" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="M5" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>0.9433</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="O5" s="5" t="n">
         <v>0.9543</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="P5" s="5" t="n">
         <v>0.9459</v>
       </c>
-      <c r="O5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
       </c>
@@ -843,15 +863,21 @@
         <v>0</v>
       </c>
       <c r="S5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="V5" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="W5" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V5" s="6" t="n">
+      <c r="X5" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -894,20 +920,22 @@
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="n">
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="P6" s="5" t="n">
         <v>0.9127</v>
       </c>
-      <c r="O6" s="6" t="inlineStr"/>
-      <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="6" t="inlineStr"/>
       <c r="R6" s="6" t="inlineStr"/>
       <c r="S6" s="6" t="inlineStr"/>
       <c r="T6" s="6" t="inlineStr"/>
       <c r="U6" s="6" t="inlineStr"/>
       <c r="V6" s="6" t="inlineStr"/>
+      <c r="W6" s="6" t="inlineStr"/>
+      <c r="X6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -948,18 +976,20 @@
       <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="5" t="inlineStr"/>
       <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="n">
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="n">
         <v>0.9677</v>
       </c>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="6" t="inlineStr"/>
-      <c r="P7" s="6" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
       <c r="Q7" s="6" t="inlineStr"/>
       <c r="R7" s="6" t="inlineStr"/>
       <c r="S7" s="6" t="inlineStr"/>
       <c r="T7" s="6" t="inlineStr"/>
       <c r="U7" s="6" t="inlineStr"/>
       <c r="V7" s="6" t="inlineStr"/>
+      <c r="W7" s="6" t="inlineStr"/>
+      <c r="X7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1004,26 +1034,26 @@
         <v>132</v>
       </c>
       <c r="J8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.122900063022655</v>
+      </c>
+      <c r="L8" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="M8" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="N8" s="5" t="n">
         <v>0.9828</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="O8" s="5" t="n">
         <v>0.9772</v>
       </c>
-      <c r="N8" s="5" t="n">
+      <c r="P8" s="5" t="n">
         <v>0.9566</v>
       </c>
-      <c r="O8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
       </c>
@@ -1031,15 +1061,21 @@
         <v>0</v>
       </c>
       <c r="S8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="V8" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="U8" s="6" t="n">
+      <c r="W8" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="V8" s="6" t="n">
+      <c r="X8" s="6" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -1086,26 +1122,26 @@
         <v>132</v>
       </c>
       <c r="J9" s="5" t="n">
+        <v>0.3112377321785142</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0.1871790685962398</v>
+      </c>
+      <c r="L9" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="M9" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="N9" s="5" t="n">
         <v>0.9116</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="O9" s="5" t="n">
         <v>0.9363</v>
       </c>
-      <c r="N9" s="5" t="n">
+      <c r="P9" s="5" t="n">
         <v>0.885</v>
       </c>
-      <c r="O9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
       </c>
@@ -1113,15 +1149,21 @@
         <v>0</v>
       </c>
       <c r="S9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="V9" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="U9" s="6" t="n">
+      <c r="W9" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="V9" s="6" t="n">
+      <c r="X9" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -1168,26 +1210,26 @@
         <v>132</v>
       </c>
       <c r="J10" s="5" t="n">
+        <v>0.03090932674773172</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0.01575629040469695</v>
+      </c>
+      <c r="L10" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="N10" s="5" t="n">
         <v>0.9370000000000001</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="O10" s="5" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="P10" s="5" t="n">
         <v>0.9009</v>
       </c>
-      <c r="O10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
       </c>
@@ -1195,15 +1237,21 @@
         <v>0</v>
       </c>
       <c r="S10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="V10" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U10" s="6" t="n">
+      <c r="W10" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V10" s="6" t="n">
+      <c r="X10" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -1250,26 +1298,26 @@
         <v>33</v>
       </c>
       <c r="J11" s="5" t="n">
+        <v>0.002490729449382223</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.001782948033825171</v>
+      </c>
+      <c r="L11" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="M11" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="N11" s="5" t="n">
         <v>0.9356</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="O11" s="5" t="n">
         <v>0.9413</v>
       </c>
-      <c r="N11" s="5" t="n">
+      <c r="P11" s="5" t="n">
         <v>0.9016</v>
       </c>
-      <c r="O11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
       </c>
@@ -1277,15 +1325,21 @@
         <v>0</v>
       </c>
       <c r="S11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="V11" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="W11" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="X11" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -1332,26 +1386,26 @@
         <v>132</v>
       </c>
       <c r="J12" s="5" t="n">
+        <v>0.05764898548542752</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0.02771241911937317</v>
+      </c>
+      <c r="L12" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="M12" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="N12" s="5" t="n">
         <v>0.9718</v>
       </c>
-      <c r="M12" s="5" t="n">
+      <c r="O12" s="5" t="n">
         <v>0.9865</v>
       </c>
-      <c r="N12" s="5" t="n">
+      <c r="P12" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
-      <c r="O12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
       </c>
@@ -1359,15 +1413,21 @@
         <v>0</v>
       </c>
       <c r="S12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="V12" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U12" s="6" t="n">
+      <c r="W12" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V12" s="6" t="n">
+      <c r="X12" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -1414,26 +1474,26 @@
         <v>275</v>
       </c>
       <c r="J13" s="5" t="n">
+        <v>0.004763767122036411</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.009994495181866792</v>
+      </c>
+      <c r="L13" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="M13" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="N13" s="5" t="n">
         <v>0.9755</v>
       </c>
-      <c r="M13" s="5" t="n">
+      <c r="O13" s="5" t="n">
         <v>0.9849</v>
       </c>
-      <c r="N13" s="5" t="n">
+      <c r="P13" s="5" t="n">
         <v>0.9798</v>
       </c>
-      <c r="O13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
       </c>
@@ -1441,15 +1501,21 @@
         <v>0</v>
       </c>
       <c r="S13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="V13" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U13" s="6" t="n">
+      <c r="W13" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V13" s="6" t="n">
+      <c r="X13" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -1496,26 +1562,26 @@
         <v>33</v>
       </c>
       <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0.03755494542283377</v>
+      </c>
+      <c r="L14" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="K14" s="5" t="n">
+      <c r="M14" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="N14" s="5" t="n">
         <v>0.9306</v>
       </c>
-      <c r="M14" s="5" t="n">
+      <c r="O14" s="5" t="n">
         <v>0.9396</v>
       </c>
-      <c r="N14" s="5" t="n">
+      <c r="P14" s="5" t="n">
         <v>0.9006999999999999</v>
       </c>
-      <c r="O14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
       </c>
@@ -1523,15 +1589,21 @@
         <v>0</v>
       </c>
       <c r="S14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="V14" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="W14" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V14" s="6" t="n">
+      <c r="X14" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -1578,26 +1650,26 @@
         <v>275</v>
       </c>
       <c r="J15" s="5" t="n">
+        <v>0.01359465836631391</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.05809514889523315</v>
+      </c>
+      <c r="L15" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="M15" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="N15" s="5" t="n">
         <v>0.9707</v>
       </c>
-      <c r="M15" s="5" t="n">
+      <c r="O15" s="5" t="n">
         <v>0.9823</v>
       </c>
-      <c r="N15" s="5" t="n">
+      <c r="P15" s="5" t="n">
         <v>0.9789</v>
       </c>
-      <c r="O15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
       </c>
@@ -1605,15 +1677,21 @@
         <v>0</v>
       </c>
       <c r="S15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="V15" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="W15" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V15" s="6" t="n">
+      <c r="X15" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -1660,28 +1738,34 @@
         <v>66</v>
       </c>
       <c r="J16" s="5" t="n">
+        <v>0.3527404105538041</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="M16" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="N16" s="5" t="n">
         <v>0.9331</v>
       </c>
-      <c r="M16" s="5" t="n">
+      <c r="O16" s="5" t="n">
         <v>0.9381</v>
       </c>
-      <c r="N16" s="5" t="n">
+      <c r="P16" s="5" t="n">
         <v>0.8972</v>
       </c>
-      <c r="O16" s="6" t="inlineStr"/>
-      <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="6" t="inlineStr"/>
       <c r="R16" s="6" t="inlineStr"/>
       <c r="S16" s="6" t="inlineStr"/>
       <c r="T16" s="6" t="inlineStr"/>
       <c r="U16" s="6" t="inlineStr"/>
       <c r="V16" s="6" t="inlineStr"/>
+      <c r="W16" s="6" t="inlineStr"/>
+      <c r="X16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1726,26 +1810,26 @@
         <v>132</v>
       </c>
       <c r="J17" s="5" t="n">
+        <v>0.02047314071674722</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.192909506972327</v>
+      </c>
+      <c r="L17" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="M17" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="N17" s="5" t="n">
         <v>0.9788</v>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="O17" s="5" t="n">
         <v>0.9977</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="P17" s="5" t="n">
         <v>0.9918</v>
       </c>
-      <c r="O17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
       </c>
@@ -1753,15 +1837,21 @@
         <v>0</v>
       </c>
       <c r="S17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="V17" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="W17" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V17" s="6" t="n">
+      <c r="X17" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -1804,20 +1894,22 @@
       <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="n">
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="n">
         <v>0.9836</v>
       </c>
-      <c r="N18" s="5" t="n">
+      <c r="P18" s="5" t="n">
         <v>0.98</v>
       </c>
-      <c r="O18" s="6" t="inlineStr"/>
-      <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="6" t="inlineStr"/>
       <c r="R18" s="6" t="inlineStr"/>
       <c r="S18" s="6" t="inlineStr"/>
       <c r="T18" s="6" t="inlineStr"/>
       <c r="U18" s="6" t="inlineStr"/>
       <c r="V18" s="6" t="inlineStr"/>
+      <c r="W18" s="6" t="inlineStr"/>
+      <c r="X18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1862,26 +1954,26 @@
         <v>33</v>
       </c>
       <c r="J19" s="5" t="n">
+        <v>0.01101053258829965</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.07387293214728219</v>
+      </c>
+      <c r="L19" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="N19" s="5" t="n">
         <v>0.9305</v>
       </c>
-      <c r="M19" s="5" t="n">
+      <c r="O19" s="5" t="n">
         <v>0.9385</v>
       </c>
-      <c r="N19" s="5" t="n">
+      <c r="P19" s="5" t="n">
         <v>0.8977000000000001</v>
       </c>
-      <c r="O19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
       </c>
@@ -1889,15 +1981,21 @@
         <v>0</v>
       </c>
       <c r="S19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="V19" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U19" s="6" t="n">
+      <c r="W19" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V19" s="6" t="n">
+      <c r="X19" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -1944,26 +2042,26 @@
         <v>275</v>
       </c>
       <c r="J20" s="5" t="n">
+        <v>0.1446613578781581</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0.08708169836578294</v>
+      </c>
+      <c r="L20" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="M20" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="N20" s="5" t="n">
         <v>0.9332</v>
       </c>
-      <c r="M20" s="5" t="n">
+      <c r="O20" s="5" t="n">
         <v>0.9475</v>
       </c>
-      <c r="N20" s="5" t="n">
+      <c r="P20" s="5" t="n">
         <v>0.9094</v>
       </c>
-      <c r="O20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
       </c>
@@ -1971,15 +2069,21 @@
         <v>0</v>
       </c>
       <c r="S20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="V20" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="U20" s="6" t="n">
+      <c r="W20" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="V20" s="6" t="n">
+      <c r="X20" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -2026,26 +2130,26 @@
         <v>33</v>
       </c>
       <c r="J21" s="5" t="n">
+        <v>0.08058042423286127</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.214852562805253</v>
+      </c>
+      <c r="L21" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="K21" s="5" t="n">
+      <c r="M21" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="N21" s="5" t="n">
         <v>0.9306</v>
       </c>
-      <c r="M21" s="5" t="n">
+      <c r="O21" s="5" t="n">
         <v>0.9396</v>
       </c>
-      <c r="N21" s="5" t="n">
+      <c r="P21" s="5" t="n">
         <v>0.9006999999999999</v>
       </c>
-      <c r="O21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
       </c>
@@ -2053,15 +2157,21 @@
         <v>0</v>
       </c>
       <c r="S21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="V21" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="W21" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V21" s="6" t="n">
+      <c r="X21" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -2107,29 +2217,31 @@
       <c r="I22" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="K22" s="5" t="n">
+      <c r="M22" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="L22" s="5" t="n">
+      <c r="N22" s="5" t="n">
         <v>0.9385</v>
       </c>
-      <c r="M22" s="5" t="n">
+      <c r="O22" s="5" t="n">
         <v>0.9516</v>
       </c>
-      <c r="N22" s="5" t="n">
+      <c r="P22" s="5" t="n">
         <v>0.918</v>
       </c>
-      <c r="O22" s="6" t="inlineStr"/>
-      <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="6" t="inlineStr"/>
       <c r="R22" s="6" t="inlineStr"/>
       <c r="S22" s="6" t="inlineStr"/>
       <c r="T22" s="6" t="inlineStr"/>
       <c r="U22" s="6" t="inlineStr"/>
       <c r="V22" s="6" t="inlineStr"/>
+      <c r="W22" s="6" t="inlineStr"/>
+      <c r="X22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2174,26 +2286,26 @@
         <v>132</v>
       </c>
       <c r="J23" s="5" t="n">
+        <v>0.1145472215423179</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.09016405734660438</v>
+      </c>
+      <c r="L23" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="K23" s="5" t="n">
+      <c r="M23" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="L23" s="5" t="n">
+      <c r="N23" s="5" t="n">
         <v>0.9703000000000001</v>
       </c>
-      <c r="M23" s="5" t="n">
+      <c r="O23" s="5" t="n">
         <v>0.9813</v>
       </c>
-      <c r="N23" s="5" t="n">
+      <c r="P23" s="5" t="n">
         <v>0.9664</v>
       </c>
-      <c r="O23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
       </c>
@@ -2201,15 +2313,21 @@
         <v>0</v>
       </c>
       <c r="S23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="V23" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U23" s="6" t="n">
+      <c r="W23" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V23" s="6" t="n">
+      <c r="X23" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
     </row>
@@ -2256,26 +2374,26 @@
         <v>132</v>
       </c>
       <c r="J24" s="5" t="n">
+        <v>0.09995898812172677</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.2351425176549525</v>
+      </c>
+      <c r="L24" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="K24" s="5" t="n">
+      <c r="M24" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="L24" s="5" t="n">
+      <c r="N24" s="5" t="n">
         <v>0.9385</v>
       </c>
-      <c r="M24" s="5" t="n">
+      <c r="O24" s="5" t="n">
         <v>0.9516</v>
       </c>
-      <c r="N24" s="5" t="n">
+      <c r="P24" s="5" t="n">
         <v>0.918</v>
       </c>
-      <c r="O24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
       </c>
@@ -2283,15 +2401,21 @@
         <v>0</v>
       </c>
       <c r="S24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="V24" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U24" s="6" t="n">
+      <c r="W24" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V24" s="6" t="n">
+      <c r="X24" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
     </row>
@@ -2337,29 +2461,33 @@
       <c r="I25" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J25" s="5" t="n">
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="n">
+        <v>0.1738300144702074</v>
+      </c>
+      <c r="L25" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
-      <c r="K25" s="5" t="n">
+      <c r="M25" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="N25" s="5" t="n">
         <v>0.9775</v>
       </c>
-      <c r="M25" s="5" t="n">
+      <c r="O25" s="5" t="n">
         <v>0.9795</v>
       </c>
-      <c r="N25" s="5" t="n">
+      <c r="P25" s="5" t="n">
         <v>0.9789</v>
       </c>
-      <c r="O25" s="6" t="inlineStr"/>
-      <c r="P25" s="6" t="inlineStr"/>
       <c r="Q25" s="6" t="inlineStr"/>
       <c r="R25" s="6" t="inlineStr"/>
       <c r="S25" s="6" t="inlineStr"/>
       <c r="T25" s="6" t="inlineStr"/>
       <c r="U25" s="6" t="inlineStr"/>
       <c r="V25" s="6" t="inlineStr"/>
+      <c r="W25" s="6" t="inlineStr"/>
+      <c r="X25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2404,26 +2532,26 @@
         <v>33</v>
       </c>
       <c r="J26" s="5" t="n">
+        <v>0.09652176800628354</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0.102248508656513</v>
+      </c>
+      <c r="L26" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="K26" s="5" t="n">
+      <c r="M26" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="L26" s="5" t="n">
+      <c r="N26" s="5" t="n">
         <v>0.9295</v>
       </c>
-      <c r="M26" s="5" t="n">
+      <c r="O26" s="5" t="n">
         <v>0.9379</v>
       </c>
-      <c r="N26" s="5" t="n">
+      <c r="P26" s="5" t="n">
         <v>0.8953</v>
       </c>
-      <c r="O26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
       </c>
@@ -2431,15 +2559,21 @@
         <v>0</v>
       </c>
       <c r="S26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="V26" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U26" s="6" t="n">
+      <c r="W26" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V26" s="6" t="n">
+      <c r="X26" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -2485,29 +2619,31 @@
       <c r="I27" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J27" s="5" t="n">
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="K27" s="5" t="n">
+      <c r="M27" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="L27" s="5" t="n">
+      <c r="N27" s="5" t="n">
         <v>0.9370000000000001</v>
       </c>
-      <c r="M27" s="5" t="n">
+      <c r="O27" s="5" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="N27" s="5" t="n">
+      <c r="P27" s="5" t="n">
         <v>0.9009</v>
       </c>
-      <c r="O27" s="6" t="inlineStr"/>
-      <c r="P27" s="6" t="inlineStr"/>
       <c r="Q27" s="6" t="inlineStr"/>
       <c r="R27" s="6" t="inlineStr"/>
       <c r="S27" s="6" t="inlineStr"/>
       <c r="T27" s="6" t="inlineStr"/>
       <c r="U27" s="6" t="inlineStr"/>
       <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
+      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2552,26 +2688,26 @@
         <v>110</v>
       </c>
       <c r="J28" s="5" t="n">
+        <v>0.01537795020370658</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0.1155419791589952</v>
+      </c>
+      <c r="L28" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="K28" s="5" t="n">
+      <c r="M28" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="L28" s="5" t="n">
+      <c r="N28" s="5" t="n">
         <v>0.9847</v>
       </c>
-      <c r="M28" s="5" t="n">
+      <c r="O28" s="5" t="n">
         <v>0.9888</v>
       </c>
-      <c r="N28" s="5" t="n">
+      <c r="P28" s="5" t="n">
         <v>0.9852</v>
       </c>
-      <c r="O28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
       </c>
@@ -2579,15 +2715,21 @@
         <v>0</v>
       </c>
       <c r="S28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="V28" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U28" s="6" t="n">
+      <c r="W28" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V28" s="6" t="n">
+      <c r="X28" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -2627,25 +2769,31 @@
         <v>30</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="n">
+      <c r="J29" s="5" t="n">
+        <v>0.03143429868117342</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0.01995818642776526</v>
+      </c>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="n">
         <v>0.9331</v>
       </c>
-      <c r="M29" s="5" t="n">
+      <c r="O29" s="5" t="n">
         <v>0.9381</v>
       </c>
-      <c r="N29" s="5" t="n">
+      <c r="P29" s="5" t="n">
         <v>0.8972</v>
       </c>
-      <c r="O29" s="6" t="inlineStr"/>
-      <c r="P29" s="6" t="inlineStr"/>
       <c r="Q29" s="6" t="inlineStr"/>
       <c r="R29" s="6" t="inlineStr"/>
       <c r="S29" s="6" t="inlineStr"/>
       <c r="T29" s="6" t="inlineStr"/>
       <c r="U29" s="6" t="inlineStr"/>
       <c r="V29" s="6" t="inlineStr"/>
+      <c r="W29" s="6" t="inlineStr"/>
+      <c r="X29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2690,26 +2838,26 @@
         <v>132</v>
       </c>
       <c r="J30" s="5" t="n">
+        <v>0.0163829695880453</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0.004168911693146149</v>
+      </c>
+      <c r="L30" s="5" t="n">
         <v>0.216663358752891</v>
       </c>
-      <c r="K30" s="5" t="n">
+      <c r="M30" s="5" t="n">
         <v>0.0509815379375577</v>
       </c>
-      <c r="L30" s="5" t="n">
+      <c r="N30" s="5" t="n">
         <v>0.9319</v>
       </c>
-      <c r="M30" s="5" t="n">
+      <c r="O30" s="5" t="n">
         <v>0.9328</v>
       </c>
-      <c r="N30" s="5" t="n">
+      <c r="P30" s="5" t="n">
         <v>0.8938</v>
       </c>
-      <c r="O30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
       </c>
@@ -2717,15 +2865,21 @@
         <v>0</v>
       </c>
       <c r="S30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="V30" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="U30" s="6" t="n">
+      <c r="W30" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V30" s="6" t="n">
+      <c r="X30" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -2768,20 +2922,22 @@
       <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="5" t="inlineStr"/>
       <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="n">
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="n">
         <v>0.9759</v>
       </c>
-      <c r="N31" s="5" t="n">
+      <c r="P31" s="5" t="n">
         <v>0.9615</v>
       </c>
-      <c r="O31" s="6" t="inlineStr"/>
-      <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="6" t="inlineStr"/>
       <c r="R31" s="6" t="inlineStr"/>
       <c r="S31" s="6" t="inlineStr"/>
       <c r="T31" s="6" t="inlineStr"/>
       <c r="U31" s="6" t="inlineStr"/>
       <c r="V31" s="6" t="inlineStr"/>
+      <c r="W31" s="6" t="inlineStr"/>
+      <c r="X31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2826,26 +2982,26 @@
         <v>110</v>
       </c>
       <c r="J32" s="5" t="n">
+        <v>0.2335656432170077</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0.3340540034648357</v>
+      </c>
+      <c r="L32" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="K32" s="5" t="n">
+      <c r="M32" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="L32" s="5" t="n">
+      <c r="N32" s="5" t="n">
         <v>0.981</v>
       </c>
-      <c r="M32" s="5" t="n">
+      <c r="O32" s="5" t="n">
         <v>0.9852</v>
       </c>
-      <c r="N32" s="5" t="n">
+      <c r="P32" s="5" t="n">
         <v>0.9838</v>
       </c>
-      <c r="O32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
       </c>
@@ -2853,15 +3009,21 @@
         <v>0</v>
       </c>
       <c r="S32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T32" s="6" t="n">
+      <c r="V32" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U32" s="6" t="n">
+      <c r="W32" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V32" s="6" t="n">
+      <c r="X32" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -2908,26 +3070,26 @@
         <v>110</v>
       </c>
       <c r="J33" s="5" t="n">
+        <v>0.1782243885346131</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0.09525946892443227</v>
+      </c>
+      <c r="L33" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="K33" s="5" t="n">
+      <c r="M33" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="L33" s="5" t="n">
+      <c r="N33" s="5" t="n">
         <v>0.981</v>
       </c>
-      <c r="M33" s="5" t="n">
+      <c r="O33" s="5" t="n">
         <v>0.9852</v>
       </c>
-      <c r="N33" s="5" t="n">
+      <c r="P33" s="5" t="n">
         <v>0.9838</v>
       </c>
-      <c r="O33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
       </c>
@@ -2935,15 +3097,21 @@
         <v>0</v>
       </c>
       <c r="S33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="V33" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U33" s="6" t="n">
+      <c r="W33" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V33" s="6" t="n">
+      <c r="X33" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -2990,26 +3158,26 @@
         <v>132</v>
       </c>
       <c r="J34" s="5" t="n">
+        <v>0.009262663851755781</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0.01087516384193066</v>
+      </c>
+      <c r="L34" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="K34" s="5" t="n">
+      <c r="M34" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="L34" s="5" t="n">
+      <c r="N34" s="5" t="n">
         <v>0.9385</v>
       </c>
-      <c r="M34" s="5" t="n">
+      <c r="O34" s="5" t="n">
         <v>0.9516</v>
       </c>
-      <c r="N34" s="5" t="n">
+      <c r="P34" s="5" t="n">
         <v>0.918</v>
       </c>
-      <c r="O34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
       </c>
@@ -3017,15 +3185,21 @@
         <v>0</v>
       </c>
       <c r="S34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="V34" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="U34" s="6" t="n">
+      <c r="W34" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="V34" s="6" t="n">
+      <c r="X34" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -3072,26 +3246,26 @@
         <v>132</v>
       </c>
       <c r="J35" s="5" t="n">
+        <v>0.01089589162947968</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0.07855967434175215</v>
+      </c>
+      <c r="L35" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="M35" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="L35" s="5" t="n">
+      <c r="N35" s="5" t="n">
         <v>0.9397</v>
       </c>
-      <c r="M35" s="5" t="n">
+      <c r="O35" s="5" t="n">
         <v>0.9463</v>
       </c>
-      <c r="N35" s="5" t="n">
+      <c r="P35" s="5" t="n">
         <v>0.9074</v>
       </c>
-      <c r="O35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
       </c>
@@ -3099,15 +3273,21 @@
         <v>0</v>
       </c>
       <c r="S35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="V35" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U35" s="6" t="n">
+      <c r="W35" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V35" s="6" t="n">
+      <c r="X35" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -3154,26 +3334,26 @@
         <v>132</v>
       </c>
       <c r="J36" s="5" t="n">
+        <v>0.01523671109204405</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0.1002926421719489</v>
+      </c>
+      <c r="L36" s="5" t="n">
         <v>0.219325121104852</v>
       </c>
-      <c r="K36" s="5" t="n">
+      <c r="M36" s="5" t="n">
         <v>0.0509806543175163</v>
       </c>
-      <c r="L36" s="5" t="n">
+      <c r="N36" s="5" t="n">
         <v>1.0159</v>
       </c>
-      <c r="M36" s="5" t="n">
+      <c r="O36" s="5" t="n">
         <v>1.0151</v>
       </c>
-      <c r="N36" s="5" t="n">
+      <c r="P36" s="5" t="n">
         <v>1.0181</v>
       </c>
-      <c r="O36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
       </c>
@@ -3181,15 +3361,21 @@
         <v>0</v>
       </c>
       <c r="S36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T36" s="6" t="n">
+      <c r="V36" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="U36" s="6" t="n">
+      <c r="W36" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="V36" s="6" t="n">
+      <c r="X36" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -3236,26 +3422,26 @@
         <v>132</v>
       </c>
       <c r="J37" s="5" t="n">
+        <v>0.009670335187359713</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0.1188651181441924</v>
+      </c>
+      <c r="L37" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
-      <c r="K37" s="5" t="n">
+      <c r="M37" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
-      <c r="L37" s="5" t="n">
+      <c r="N37" s="5" t="n">
         <v>0.9828</v>
       </c>
-      <c r="M37" s="5" t="n">
+      <c r="O37" s="5" t="n">
         <v>0.9772</v>
       </c>
-      <c r="N37" s="5" t="n">
+      <c r="P37" s="5" t="n">
         <v>0.9566</v>
       </c>
-      <c r="O37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
       </c>
@@ -3263,15 +3449,21 @@
         <v>0</v>
       </c>
       <c r="S37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="V37" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="U37" s="6" t="n">
+      <c r="W37" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="V37" s="6" t="n">
+      <c r="X37" s="6" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -3317,29 +3509,31 @@
       <c r="I38" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J38" s="5" t="n">
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="n">
         <v>0.240575567460725</v>
       </c>
-      <c r="K38" s="5" t="n">
+      <c r="M38" s="5" t="n">
         <v>0.0593284659737539</v>
       </c>
-      <c r="L38" s="5" t="n">
+      <c r="N38" s="5" t="n">
         <v>1.0145</v>
       </c>
-      <c r="M38" s="5" t="n">
+      <c r="O38" s="5" t="n">
         <v>1.0144</v>
       </c>
-      <c r="N38" s="5" t="n">
+      <c r="P38" s="5" t="n">
         <v>1.0133</v>
       </c>
-      <c r="O38" s="6" t="inlineStr"/>
-      <c r="P38" s="6" t="inlineStr"/>
       <c r="Q38" s="6" t="inlineStr"/>
       <c r="R38" s="6" t="inlineStr"/>
       <c r="S38" s="6" t="inlineStr"/>
       <c r="T38" s="6" t="inlineStr"/>
       <c r="U38" s="6" t="inlineStr"/>
       <c r="V38" s="6" t="inlineStr"/>
+      <c r="W38" s="6" t="inlineStr"/>
+      <c r="X38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3384,26 +3578,26 @@
         <v>275</v>
       </c>
       <c r="J39" s="5" t="n">
+        <v>0.1723317533761356</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0.1974440855337861</v>
+      </c>
+      <c r="L39" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
-      <c r="K39" s="5" t="n">
+      <c r="M39" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
-      <c r="L39" s="5" t="n">
+      <c r="N39" s="5" t="n">
         <v>0.9785</v>
       </c>
-      <c r="M39" s="5" t="n">
+      <c r="O39" s="5" t="n">
         <v>0.9975000000000001</v>
       </c>
-      <c r="N39" s="5" t="n">
+      <c r="P39" s="5" t="n">
         <v>0.9915</v>
       </c>
-      <c r="O39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
       </c>
@@ -3411,15 +3605,21 @@
         <v>0</v>
       </c>
       <c r="S39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="V39" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U39" s="6" t="n">
+      <c r="W39" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V39" s="6" t="n">
+      <c r="X39" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -3466,26 +3666,26 @@
         <v>110</v>
       </c>
       <c r="J40" s="5" t="n">
+        <v>0.3233227782048679</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0.390009749761537</v>
+      </c>
+      <c r="L40" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="K40" s="5" t="n">
+      <c r="M40" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="L40" s="5" t="n">
+      <c r="N40" s="5" t="n">
         <v>0.9847</v>
       </c>
-      <c r="M40" s="5" t="n">
+      <c r="O40" s="5" t="n">
         <v>0.9888</v>
       </c>
-      <c r="N40" s="5" t="n">
+      <c r="P40" s="5" t="n">
         <v>0.9852</v>
       </c>
-      <c r="O40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
       </c>
@@ -3493,15 +3693,21 @@
         <v>0</v>
       </c>
       <c r="S40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="V40" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U40" s="6" t="n">
+      <c r="W40" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V40" s="6" t="n">
+      <c r="X40" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -3548,26 +3754,26 @@
         <v>110</v>
       </c>
       <c r="J41" s="5" t="n">
+        <v>0.330054131916018</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.3939618767807501</v>
+      </c>
+      <c r="L41" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="K41" s="5" t="n">
+      <c r="M41" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="L41" s="5" t="n">
+      <c r="N41" s="5" t="n">
         <v>0.9847</v>
       </c>
-      <c r="M41" s="5" t="n">
+      <c r="O41" s="5" t="n">
         <v>0.9888</v>
       </c>
-      <c r="N41" s="5" t="n">
+      <c r="P41" s="5" t="n">
         <v>0.9852</v>
       </c>
-      <c r="O41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
       </c>
@@ -3575,15 +3781,21 @@
         <v>0</v>
       </c>
       <c r="S41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="V41" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U41" s="6" t="n">
+      <c r="W41" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V41" s="6" t="n">
+      <c r="X41" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -3623,25 +3835,31 @@
         <v>501</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr"/>
-      <c r="L42" s="5" t="n">
+      <c r="J42" s="5" t="n">
+        <v>0.2114377575943847</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0.1744522911233145</v>
+      </c>
+      <c r="L42" s="5" t="inlineStr"/>
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="n">
         <v>0.9701</v>
       </c>
-      <c r="M42" s="5" t="n">
+      <c r="O42" s="5" t="n">
         <v>0.9767</v>
       </c>
-      <c r="N42" s="5" t="n">
+      <c r="P42" s="5" t="n">
         <v>0.9751</v>
       </c>
-      <c r="O42" s="6" t="inlineStr"/>
-      <c r="P42" s="6" t="inlineStr"/>
       <c r="Q42" s="6" t="inlineStr"/>
       <c r="R42" s="6" t="inlineStr"/>
       <c r="S42" s="6" t="inlineStr"/>
       <c r="T42" s="6" t="inlineStr"/>
       <c r="U42" s="6" t="inlineStr"/>
       <c r="V42" s="6" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
+      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3686,26 +3904,26 @@
         <v>33</v>
       </c>
       <c r="J43" s="5" t="n">
+        <v>0.3193219098685215</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0.3037218764181746</v>
+      </c>
+      <c r="L43" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="K43" s="5" t="n">
+      <c r="M43" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="L43" s="5" t="n">
+      <c r="N43" s="5" t="n">
         <v>0.9204</v>
       </c>
-      <c r="M43" s="5" t="n">
+      <c r="O43" s="5" t="n">
         <v>0.9398</v>
       </c>
-      <c r="N43" s="5" t="n">
+      <c r="P43" s="5" t="n">
         <v>0.899</v>
       </c>
-      <c r="O43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
       </c>
@@ -3713,15 +3931,21 @@
         <v>0</v>
       </c>
       <c r="S43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="V43" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U43" s="6" t="n">
+      <c r="W43" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V43" s="6" t="n">
+      <c r="X43" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -3768,26 +3992,26 @@
         <v>132</v>
       </c>
       <c r="J44" s="5" t="n">
+        <v>0.1712244976544002</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0.2353335402156503</v>
+      </c>
+      <c r="L44" s="5" t="n">
         <v>0.23173278497921</v>
       </c>
-      <c r="K44" s="5" t="n">
+      <c r="M44" s="5" t="n">
         <v>0.0558256772551647</v>
       </c>
-      <c r="L44" s="5" t="n">
+      <c r="N44" s="5" t="n">
         <v>0.985</v>
       </c>
-      <c r="M44" s="5" t="n">
+      <c r="O44" s="5" t="n">
         <v>0.9787</v>
       </c>
-      <c r="N44" s="5" t="n">
+      <c r="P44" s="5" t="n">
         <v>0.9611</v>
       </c>
-      <c r="O44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
       </c>
@@ -3795,15 +4019,21 @@
         <v>0</v>
       </c>
       <c r="S44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="V44" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="U44" s="6" t="n">
+      <c r="W44" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="V44" s="6" t="n">
+      <c r="X44" s="6" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -3850,26 +4080,26 @@
         <v>110</v>
       </c>
       <c r="J45" s="5" t="n">
+        <v>0.04412090427937254</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.1370696895438673</v>
+      </c>
+      <c r="L45" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="K45" s="5" t="n">
+      <c r="M45" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="L45" s="5" t="n">
+      <c r="N45" s="5" t="n">
         <v>0.9847</v>
       </c>
-      <c r="M45" s="5" t="n">
+      <c r="O45" s="5" t="n">
         <v>0.9888</v>
       </c>
-      <c r="N45" s="5" t="n">
+      <c r="P45" s="5" t="n">
         <v>0.9852</v>
       </c>
-      <c r="O45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
       </c>
@@ -3877,15 +4107,21 @@
         <v>0</v>
       </c>
       <c r="S45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="V45" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U45" s="6" t="n">
+      <c r="W45" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V45" s="6" t="n">
+      <c r="X45" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -3926,24 +4162,28 @@
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="n">
+      <c r="K46" s="5" t="n">
+        <v>0.00914999709266473</v>
+      </c>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="n">
         <v>0.9497</v>
       </c>
-      <c r="M46" s="5" t="n">
+      <c r="O46" s="5" t="n">
         <v>0.9429999999999999</v>
       </c>
-      <c r="N46" s="5" t="n">
+      <c r="P46" s="5" t="n">
         <v>0.9326</v>
       </c>
-      <c r="O46" s="6" t="inlineStr"/>
-      <c r="P46" s="6" t="inlineStr"/>
       <c r="Q46" s="6" t="inlineStr"/>
       <c r="R46" s="6" t="inlineStr"/>
       <c r="S46" s="6" t="inlineStr"/>
       <c r="T46" s="6" t="inlineStr"/>
       <c r="U46" s="6" t="inlineStr"/>
       <c r="V46" s="6" t="inlineStr"/>
+      <c r="W46" s="6" t="inlineStr"/>
+      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3982,24 +4222,28 @@
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="n">
+      <c r="K47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="n">
         <v>0.9497</v>
       </c>
-      <c r="M47" s="5" t="n">
+      <c r="O47" s="5" t="n">
         <v>0.9429999999999999</v>
       </c>
-      <c r="N47" s="5" t="n">
+      <c r="P47" s="5" t="n">
         <v>0.9326</v>
       </c>
-      <c r="O47" s="6" t="inlineStr"/>
-      <c r="P47" s="6" t="inlineStr"/>
       <c r="Q47" s="6" t="inlineStr"/>
       <c r="R47" s="6" t="inlineStr"/>
       <c r="S47" s="6" t="inlineStr"/>
       <c r="T47" s="6" t="inlineStr"/>
       <c r="U47" s="6" t="inlineStr"/>
       <c r="V47" s="6" t="inlineStr"/>
+      <c r="W47" s="6" t="inlineStr"/>
+      <c r="X47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4037,25 +4281,31 @@
         <v>452</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr"/>
-      <c r="L48" s="5" t="n">
+      <c r="J48" s="5" t="n">
+        <v>0.0005151765519970652</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0.02976254778266307</v>
+      </c>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="5" t="n">
         <v>0.9671999999999999</v>
       </c>
-      <c r="M48" s="5" t="n">
+      <c r="O48" s="5" t="n">
         <v>0.9691</v>
       </c>
-      <c r="N48" s="5" t="n">
+      <c r="P48" s="5" t="n">
         <v>0.9705</v>
       </c>
-      <c r="O48" s="6" t="inlineStr"/>
-      <c r="P48" s="6" t="inlineStr"/>
       <c r="Q48" s="6" t="inlineStr"/>
       <c r="R48" s="6" t="inlineStr"/>
       <c r="S48" s="6" t="inlineStr"/>
       <c r="T48" s="6" t="inlineStr"/>
       <c r="U48" s="6" t="inlineStr"/>
       <c r="V48" s="6" t="inlineStr"/>
+      <c r="W48" s="6" t="inlineStr"/>
+      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4093,25 +4343,31 @@
         <v>180</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="n">
+      <c r="J49" s="5" t="n">
+        <v>0.004431688326278604</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.002402426901614629</v>
+      </c>
+      <c r="L49" s="5" t="inlineStr"/>
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="n">
         <v>0.977</v>
       </c>
-      <c r="M49" s="5" t="n">
+      <c r="O49" s="5" t="n">
         <v>0.9853</v>
       </c>
-      <c r="N49" s="5" t="n">
+      <c r="P49" s="5" t="n">
         <v>0.9869</v>
       </c>
-      <c r="O49" s="6" t="inlineStr"/>
-      <c r="P49" s="6" t="inlineStr"/>
       <c r="Q49" s="6" t="inlineStr"/>
       <c r="R49" s="6" t="inlineStr"/>
       <c r="S49" s="6" t="inlineStr"/>
       <c r="T49" s="6" t="inlineStr"/>
       <c r="U49" s="6" t="inlineStr"/>
       <c r="V49" s="6" t="inlineStr"/>
+      <c r="W49" s="6" t="inlineStr"/>
+      <c r="X49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4149,25 +4405,31 @@
         <v>156</v>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="n">
+      <c r="J50" s="5" t="n">
+        <v>0.007044941110596614</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0.01139050990981172</v>
+      </c>
+      <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="5" t="inlineStr"/>
+      <c r="N50" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="M50" s="5" t="n">
+      <c r="O50" s="5" t="n">
         <v>0.9696</v>
       </c>
-      <c r="N50" s="5" t="n">
+      <c r="P50" s="5" t="n">
         <v>0.9484</v>
       </c>
-      <c r="O50" s="6" t="inlineStr"/>
-      <c r="P50" s="6" t="inlineStr"/>
       <c r="Q50" s="6" t="inlineStr"/>
       <c r="R50" s="6" t="inlineStr"/>
       <c r="S50" s="6" t="inlineStr"/>
       <c r="T50" s="6" t="inlineStr"/>
       <c r="U50" s="6" t="inlineStr"/>
       <c r="V50" s="6" t="inlineStr"/>
+      <c r="W50" s="6" t="inlineStr"/>
+      <c r="X50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4205,25 +4467,31 @@
         <v>43</v>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
-      <c r="K51" s="5" t="inlineStr"/>
-      <c r="L51" s="5" t="n">
+      <c r="J51" s="5" t="n">
+        <v>0.009046837819930542</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.02399070794204605</v>
+      </c>
+      <c r="L51" s="5" t="inlineStr"/>
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="n">
         <v>0.9703000000000001</v>
       </c>
-      <c r="M51" s="5" t="n">
+      <c r="O51" s="5" t="n">
         <v>0.9813</v>
       </c>
-      <c r="N51" s="5" t="n">
+      <c r="P51" s="5" t="n">
         <v>0.9664</v>
       </c>
-      <c r="O51" s="6" t="inlineStr"/>
-      <c r="P51" s="6" t="inlineStr"/>
       <c r="Q51" s="6" t="inlineStr"/>
       <c r="R51" s="6" t="inlineStr"/>
       <c r="S51" s="6" t="inlineStr"/>
       <c r="T51" s="6" t="inlineStr"/>
       <c r="U51" s="6" t="inlineStr"/>
       <c r="V51" s="6" t="inlineStr"/>
+      <c r="W51" s="6" t="inlineStr"/>
+      <c r="X51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4262,24 +4530,28 @@
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="inlineStr"/>
-      <c r="L52" s="5" t="n">
+      <c r="K52" s="5" t="n">
+        <v>0.0264405736692952</v>
+      </c>
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="5" t="inlineStr"/>
+      <c r="N52" s="5" t="n">
         <v>0.9734</v>
       </c>
-      <c r="M52" s="5" t="n">
+      <c r="O52" s="5" t="n">
         <v>0.9723000000000001</v>
       </c>
-      <c r="N52" s="5" t="n">
+      <c r="P52" s="5" t="n">
         <v>0.9727</v>
       </c>
-      <c r="O52" s="6" t="inlineStr"/>
-      <c r="P52" s="6" t="inlineStr"/>
       <c r="Q52" s="6" t="inlineStr"/>
       <c r="R52" s="6" t="inlineStr"/>
       <c r="S52" s="6" t="inlineStr"/>
       <c r="T52" s="6" t="inlineStr"/>
       <c r="U52" s="6" t="inlineStr"/>
       <c r="V52" s="6" t="inlineStr"/>
+      <c r="W52" s="6" t="inlineStr"/>
+      <c r="X52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4317,25 +4589,31 @@
         <v>180</v>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr"/>
-      <c r="K53" s="5" t="inlineStr"/>
-      <c r="L53" s="5" t="n">
+      <c r="J53" s="5" t="n">
+        <v>0.02288629735304848</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.039511765388348</v>
+      </c>
+      <c r="L53" s="5" t="inlineStr"/>
+      <c r="M53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="n">
         <v>0.9527</v>
       </c>
-      <c r="M53" s="5" t="n">
+      <c r="O53" s="5" t="n">
         <v>0.9649</v>
       </c>
-      <c r="N53" s="5" t="n">
+      <c r="P53" s="5" t="n">
         <v>0.9451000000000001</v>
       </c>
-      <c r="O53" s="6" t="inlineStr"/>
-      <c r="P53" s="6" t="inlineStr"/>
       <c r="Q53" s="6" t="inlineStr"/>
       <c r="R53" s="6" t="inlineStr"/>
       <c r="S53" s="6" t="inlineStr"/>
       <c r="T53" s="6" t="inlineStr"/>
       <c r="U53" s="6" t="inlineStr"/>
       <c r="V53" s="6" t="inlineStr"/>
+      <c r="W53" s="6" t="inlineStr"/>
+      <c r="X53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4374,24 +4652,28 @@
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="5" t="inlineStr"/>
-      <c r="L54" s="5" t="n">
+      <c r="K54" s="5" t="n">
+        <v>0.002002445296444888</v>
+      </c>
+      <c r="L54" s="5" t="inlineStr"/>
+      <c r="M54" s="5" t="inlineStr"/>
+      <c r="N54" s="5" t="n">
         <v>0.9698</v>
       </c>
-      <c r="M54" s="5" t="n">
+      <c r="O54" s="5" t="n">
         <v>0.967</v>
       </c>
-      <c r="N54" s="5" t="n">
+      <c r="P54" s="5" t="n">
         <v>0.9703000000000001</v>
       </c>
-      <c r="O54" s="6" t="inlineStr"/>
-      <c r="P54" s="6" t="inlineStr"/>
       <c r="Q54" s="6" t="inlineStr"/>
       <c r="R54" s="6" t="inlineStr"/>
       <c r="S54" s="6" t="inlineStr"/>
       <c r="T54" s="6" t="inlineStr"/>
       <c r="U54" s="6" t="inlineStr"/>
       <c r="V54" s="6" t="inlineStr"/>
+      <c r="W54" s="6" t="inlineStr"/>
+      <c r="X54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4431,23 +4713,25 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr"/>
       <c r="K55" s="5" t="inlineStr"/>
-      <c r="L55" s="5" t="n">
+      <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="n">
         <v>1.0142</v>
       </c>
-      <c r="M55" s="5" t="n">
+      <c r="O55" s="5" t="n">
         <v>1.0128</v>
       </c>
-      <c r="N55" s="5" t="n">
+      <c r="P55" s="5" t="n">
         <v>1.01</v>
       </c>
-      <c r="O55" s="6" t="inlineStr"/>
-      <c r="P55" s="6" t="inlineStr"/>
       <c r="Q55" s="6" t="inlineStr"/>
       <c r="R55" s="6" t="inlineStr"/>
       <c r="S55" s="6" t="inlineStr"/>
       <c r="T55" s="6" t="inlineStr"/>
       <c r="U55" s="6" t="inlineStr"/>
       <c r="V55" s="6" t="inlineStr"/>
+      <c r="W55" s="6" t="inlineStr"/>
+      <c r="X55" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4460,7 +4744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U55"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4484,6 +4768,8 @@
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4514,80 +4800,90 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>CURTAILMENT_ACTUAL_FY23-24</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>CURTAILMENT_ACTUAL_FY24-25</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY1</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY1_LABEL</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY2</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY2_LABEL</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY3</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY3_LABEL</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_AVG</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY1</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY1_LABEL</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY2</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY2_LABEL</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY3</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="V1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY3_LABEL</t>
         </is>
       </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_AVG</t>
         </is>
@@ -4614,45 +4910,49 @@
         <v>0.9029</v>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="n">
+        <v>7.689919976716642e-05</v>
+      </c>
       <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="5" t="inlineStr"/>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
       <c r="Q2" s="5" t="inlineStr"/>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S2" s="5" t="inlineStr"/>
       <c r="T2" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -4674,50 +4974,52 @@
       <c r="E3" s="5" t="n">
         <v>0.9461000000000001</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="I3" s="5" t="n">
         <v>0.0559828223482727</v>
-      </c>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
       <c r="Q3" s="5" t="inlineStr"/>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr"/>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -4742,43 +5044,45 @@
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -4801,25 +5105,23 @@
         <v>0.9459</v>
       </c>
       <c r="F5" s="5" t="n">
+        <v>0.05651030523317557</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.02317489340857803</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="H5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L5" s="5" t="n">
@@ -4827,26 +5129,26 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="5" t="n">
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S5" s="5" t="n">
@@ -4854,10 +5156,18 @@
       </c>
       <c r="T5" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U5" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -4882,43 +5192,45 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -4939,43 +5251,45 @@
       <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr"/>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr"/>
       <c r="Q7" s="5" t="inlineStr"/>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S7" s="5" t="inlineStr"/>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -4998,25 +5312,23 @@
         <v>0.9566</v>
       </c>
       <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.122900063022655</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
-      <c r="H8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L8" s="5" t="n">
@@ -5024,37 +5336,45 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="5" t="n">
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="n">
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="n">
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="n">
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -5079,25 +5399,23 @@
         <v>0.885</v>
       </c>
       <c r="F9" s="5" t="n">
+        <v>0.3112377321785142</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.1871790685962398</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="H9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L9" s="5" t="n">
@@ -5105,26 +5423,26 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="5" t="n">
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="n">
-        <v>0.04</v>
-      </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S9" s="5" t="n">
@@ -5132,10 +5450,18 @@
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U9" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -5160,25 +5486,23 @@
         <v>0.9009</v>
       </c>
       <c r="F10" s="5" t="n">
+        <v>0.03090932674773172</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.01575629040469695</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="H10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L10" s="5" t="n">
@@ -5186,26 +5510,26 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="5" t="n">
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S10" s="5" t="n">
@@ -5213,10 +5537,18 @@
       </c>
       <c r="T10" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U10" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -5241,25 +5573,23 @@
         <v>0.9016</v>
       </c>
       <c r="F11" s="5" t="n">
+        <v>0.002490729449382223</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.001782948033825171</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="I11" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="H11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L11" s="5" t="n">
@@ -5267,26 +5597,26 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="5" t="n">
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S11" s="5" t="n">
@@ -5294,10 +5624,18 @@
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U11" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -5322,25 +5660,23 @@
         <v>0.9824000000000001</v>
       </c>
       <c r="F12" s="5" t="n">
+        <v>0.05764898548542752</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.02771241911937317</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="I12" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
-      <c r="H12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L12" s="5" t="n">
@@ -5348,26 +5684,26 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="5" t="n">
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S12" s="5" t="n">
@@ -5375,10 +5711,18 @@
       </c>
       <c r="T12" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U12" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -5403,25 +5747,23 @@
         <v>0.9798</v>
       </c>
       <c r="F13" s="5" t="n">
+        <v>0.004763767122036411</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.009994495181866792</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="I13" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="H13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L13" s="5" t="n">
@@ -5429,26 +5771,26 @@
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="5" t="n">
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S13" s="5" t="n">
@@ -5456,10 +5798,18 @@
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U13" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -5484,25 +5834,23 @@
         <v>0.9006999999999999</v>
       </c>
       <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.03755494542283377</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="I14" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L14" s="5" t="n">
@@ -5510,26 +5858,26 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="5" t="n">
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S14" s="5" t="n">
@@ -5537,10 +5885,18 @@
       </c>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U14" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -5565,25 +5921,23 @@
         <v>0.9789</v>
       </c>
       <c r="F15" s="5" t="n">
+        <v>0.01359465836631391</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.05809514889523315</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="H15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L15" s="5" t="n">
@@ -5591,26 +5945,26 @@
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="5" t="n">
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q15" s="5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S15" s="5" t="n">
@@ -5618,10 +5972,18 @@
       </c>
       <c r="T15" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U15" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -5646,49 +6008,55 @@
         <v>0.8972</v>
       </c>
       <c r="F16" s="5" t="n">
+        <v>0.3527404105538041</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>0.0531062553506225</v>
-      </c>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="5" t="inlineStr"/>
-      <c r="P16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr"/>
       <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr"/>
       <c r="T16" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U16" s="5" t="inlineStr"/>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -5711,25 +6079,23 @@
         <v>0.9918</v>
       </c>
       <c r="F17" s="5" t="n">
+        <v>0.02047314071674722</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.192909506972327</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="H17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L17" s="5" t="n">
@@ -5737,26 +6103,26 @@
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="5" t="n">
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q17" s="5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S17" s="5" t="n">
@@ -5764,10 +6130,18 @@
       </c>
       <c r="T17" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U17" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -5792,43 +6166,45 @@
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr"/>
-      <c r="O18" s="5" t="inlineStr"/>
-      <c r="P18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="inlineStr"/>
       <c r="Q18" s="5" t="inlineStr"/>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr"/>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U18" s="5" t="inlineStr"/>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -5851,25 +6227,23 @@
         <v>0.8977000000000001</v>
       </c>
       <c r="F19" s="5" t="n">
+        <v>0.01101053258829965</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.07387293214728219</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="H19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L19" s="5" t="n">
@@ -5877,26 +6251,26 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="5" t="n">
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q19" s="5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S19" s="5" t="n">
@@ -5904,10 +6278,18 @@
       </c>
       <c r="T19" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U19" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -5932,25 +6314,23 @@
         <v>0.9094</v>
       </c>
       <c r="F20" s="5" t="n">
+        <v>0.1446613578781581</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.08708169836578294</v>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="I20" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="H20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L20" s="5" t="n">
@@ -5958,26 +6338,26 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="5" t="n">
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v>0.04</v>
-      </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S20" s="5" t="n">
@@ -5985,10 +6365,18 @@
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U20" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -6013,25 +6401,23 @@
         <v>0.9006999999999999</v>
       </c>
       <c r="F21" s="5" t="n">
+        <v>0.08058042423286127</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.214852562805253</v>
+      </c>
+      <c r="H21" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="I21" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="H21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L21" s="5" t="n">
@@ -6039,26 +6425,26 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="5" t="n">
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q21" s="5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S21" s="5" t="n">
@@ -6066,10 +6452,18 @@
       </c>
       <c r="T21" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U21" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -6093,50 +6487,52 @@
       <c r="E22" s="5" t="n">
         <v>0.918</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="I22" s="5" t="n">
         <v>0.0510095644706063</v>
-      </c>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="inlineStr"/>
       <c r="Q22" s="5" t="inlineStr"/>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr"/>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U22" s="5" t="inlineStr"/>
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -6159,25 +6555,23 @@
         <v>0.9664</v>
       </c>
       <c r="F23" s="5" t="n">
+        <v>0.1145472215423179</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.09016405734660438</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="I23" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="H23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L23" s="5" t="n">
@@ -6185,26 +6579,26 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="5" t="n">
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="P23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q23" s="5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S23" s="5" t="n">
@@ -6212,10 +6606,18 @@
       </c>
       <c r="T23" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U23" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W23" s="5" t="n">
         <v>0.02666666666666667</v>
       </c>
     </row>
@@ -6240,25 +6642,23 @@
         <v>0.918</v>
       </c>
       <c r="F24" s="5" t="n">
+        <v>0.09995898812172677</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.2351425176549525</v>
+      </c>
+      <c r="H24" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="I24" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="H24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L24" s="5" t="n">
@@ -6266,26 +6666,26 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="5" t="n">
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="P24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q24" s="5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S24" s="5" t="n">
@@ -6293,10 +6693,18 @@
       </c>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U24" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W24" s="5" t="n">
         <v>0.02666666666666667</v>
       </c>
     </row>
@@ -6320,50 +6728,54 @@
       <c r="E25" s="5" t="n">
         <v>0.9789</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="n">
+        <v>0.1738300144702074</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="I25" s="5" t="n">
         <v>0.0559828223482727</v>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="5" t="inlineStr"/>
-      <c r="P25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr"/>
       <c r="Q25" s="5" t="inlineStr"/>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr"/>
       <c r="T25" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U25" s="5" t="inlineStr"/>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -6386,25 +6798,23 @@
         <v>0.8953</v>
       </c>
       <c r="F26" s="5" t="n">
+        <v>0.09652176800628354</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.102248508656513</v>
+      </c>
+      <c r="H26" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="I26" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="H26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L26" s="5" t="n">
@@ -6412,26 +6822,26 @@
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="5" t="n">
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S26" s="5" t="n">
@@ -6439,10 +6849,18 @@
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U26" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W26" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -6466,50 +6884,52 @@
       <c r="E27" s="5" t="n">
         <v>0.9009</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="I27" s="5" t="n">
         <v>0.0531062553506225</v>
-      </c>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr"/>
-      <c r="P27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr"/>
       <c r="Q27" s="5" t="inlineStr"/>
       <c r="R27" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S27" s="5" t="inlineStr"/>
       <c r="T27" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U27" s="5" t="inlineStr"/>
+      <c r="V27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -6532,25 +6952,23 @@
         <v>0.9852</v>
       </c>
       <c r="F28" s="5" t="n">
+        <v>0.01537795020370658</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.1155419791589952</v>
+      </c>
+      <c r="H28" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="I28" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="H28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L28" s="5" t="n">
@@ -6558,26 +6976,26 @@
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="5" t="n">
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q28" s="5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S28" s="5" t="n">
@@ -6585,10 +7003,18 @@
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U28" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W28" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -6612,46 +7038,52 @@
       <c r="E29" s="5" t="n">
         <v>0.8972</v>
       </c>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="n">
+        <v>0.03143429868117342</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.01995818642776526</v>
+      </c>
       <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="5" t="inlineStr"/>
-      <c r="P29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr"/>
       <c r="Q29" s="5" t="inlineStr"/>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S29" s="5" t="inlineStr"/>
       <c r="T29" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U29" s="5" t="inlineStr"/>
+      <c r="V29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -6674,25 +7106,23 @@
         <v>0.8938</v>
       </c>
       <c r="F30" s="5" t="n">
+        <v>0.0163829695880453</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.004168911693146149</v>
+      </c>
+      <c r="H30" s="5" t="n">
         <v>0.216663358752891</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="I30" s="5" t="n">
         <v>0.0509815379375577</v>
       </c>
-      <c r="H30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L30" s="5" t="n">
@@ -6700,37 +7130,45 @@
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="5" t="n">
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q30" s="5" t="n">
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S30" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="R30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S30" s="5" t="n">
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U30" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U30" s="5" t="n">
+      <c r="V30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W30" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -6755,43 +7193,45 @@
       <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="5" t="inlineStr"/>
-      <c r="P31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr"/>
       <c r="Q31" s="5" t="inlineStr"/>
       <c r="R31" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S31" s="5" t="inlineStr"/>
       <c r="T31" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U31" s="5" t="inlineStr"/>
+      <c r="V31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -6814,25 +7254,23 @@
         <v>0.9838</v>
       </c>
       <c r="F32" s="5" t="n">
+        <v>0.2335656432170077</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.3340540034648357</v>
+      </c>
+      <c r="H32" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="I32" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="H32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L32" s="5" t="n">
@@ -6840,26 +7278,26 @@
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="5" t="n">
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="R32" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S32" s="5" t="n">
@@ -6867,10 +7305,18 @@
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U32" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W32" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -6895,25 +7341,23 @@
         <v>0.9838</v>
       </c>
       <c r="F33" s="5" t="n">
+        <v>0.1782243885346131</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.09525946892443227</v>
+      </c>
+      <c r="H33" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="I33" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="H33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L33" s="5" t="n">
@@ -6921,26 +7365,26 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="5" t="n">
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q33" s="5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="R33" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S33" s="5" t="n">
@@ -6948,10 +7392,18 @@
       </c>
       <c r="T33" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U33" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W33" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -6976,25 +7428,23 @@
         <v>0.918</v>
       </c>
       <c r="F34" s="5" t="n">
+        <v>0.009262663851755781</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.01087516384193066</v>
+      </c>
+      <c r="H34" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="G34" s="5" t="n">
+      <c r="I34" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="H34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L34" s="5" t="n">
@@ -7002,26 +7452,26 @@
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="5" t="n">
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <v>0.04</v>
-      </c>
       <c r="R34" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S34" s="5" t="n">
@@ -7029,10 +7479,18 @@
       </c>
       <c r="T34" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U34" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -7057,25 +7515,23 @@
         <v>0.9074</v>
       </c>
       <c r="F35" s="5" t="n">
+        <v>0.01089589162947968</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.07855967434175215</v>
+      </c>
+      <c r="H35" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="I35" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L35" s="5" t="n">
@@ -7083,26 +7539,26 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="5" t="n">
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q35" s="5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S35" s="5" t="n">
@@ -7110,10 +7566,18 @@
       </c>
       <c r="T35" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U35" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -7138,25 +7602,23 @@
         <v>1.0181</v>
       </c>
       <c r="F36" s="5" t="n">
+        <v>0.01523671109204405</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.1002926421719489</v>
+      </c>
+      <c r="H36" s="5" t="n">
         <v>0.219325121104852</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="I36" s="5" t="n">
         <v>0.0509806543175163</v>
       </c>
-      <c r="H36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L36" s="5" t="n">
@@ -7164,26 +7626,26 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="5" t="n">
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <v>0.04</v>
-      </c>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S36" s="5" t="n">
@@ -7191,10 +7653,18 @@
       </c>
       <c r="T36" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U36" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -7219,25 +7689,23 @@
         <v>0.9566</v>
       </c>
       <c r="F37" s="5" t="n">
+        <v>0.009670335187359713</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.1188651181441924</v>
+      </c>
+      <c r="H37" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="I37" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
-      <c r="H37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L37" s="5" t="n">
@@ -7245,37 +7713,45 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="5" t="n">
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="P37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q37" s="5" t="n">
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S37" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="R37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S37" s="5" t="n">
+      <c r="T37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U37" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="T37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U37" s="5" t="n">
+      <c r="V37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W37" s="5" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -7299,50 +7775,52 @@
       <c r="E38" s="5" t="n">
         <v>1.0133</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="n">
         <v>0.240575567460725</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="I38" s="5" t="n">
         <v>0.0593284659737539</v>
-      </c>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="5" t="inlineStr"/>
-      <c r="P38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr"/>
       <c r="Q38" s="5" t="inlineStr"/>
       <c r="R38" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S38" s="5" t="inlineStr"/>
       <c r="T38" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U38" s="5" t="inlineStr"/>
+      <c r="V38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -7365,25 +7843,23 @@
         <v>0.9915</v>
       </c>
       <c r="F39" s="5" t="n">
+        <v>0.1723317533761356</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.1974440855337861</v>
+      </c>
+      <c r="H39" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
-      <c r="G39" s="5" t="n">
+      <c r="I39" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
-      <c r="H39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L39" s="5" t="n">
@@ -7391,26 +7867,26 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O39" s="5" t="n">
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q39" s="5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="R39" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S39" s="5" t="n">
@@ -7418,10 +7894,18 @@
       </c>
       <c r="T39" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U39" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W39" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -7446,25 +7930,23 @@
         <v>0.9852</v>
       </c>
       <c r="F40" s="5" t="n">
+        <v>0.3233227782048679</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.390009749761537</v>
+      </c>
+      <c r="H40" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="I40" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="H40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L40" s="5" t="n">
@@ -7472,26 +7954,26 @@
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="5" t="n">
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q40" s="5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S40" s="5" t="n">
@@ -7499,10 +7981,18 @@
       </c>
       <c r="T40" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U40" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W40" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -7527,25 +8017,23 @@
         <v>0.9852</v>
       </c>
       <c r="F41" s="5" t="n">
+        <v>0.330054131916018</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.3939618767807501</v>
+      </c>
+      <c r="H41" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="I41" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="H41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L41" s="5" t="n">
@@ -7553,26 +8041,26 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O41" s="5" t="n">
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q41" s="5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="R41" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S41" s="5" t="n">
@@ -7580,10 +8068,18 @@
       </c>
       <c r="T41" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U41" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W41" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -7607,46 +8103,52 @@
       <c r="E42" s="5" t="n">
         <v>0.9751</v>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="n">
+        <v>0.2114377575943847</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.1744522911233145</v>
+      </c>
       <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="5" t="inlineStr"/>
-      <c r="P42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr"/>
       <c r="Q42" s="5" t="inlineStr"/>
       <c r="R42" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S42" s="5" t="inlineStr"/>
       <c r="T42" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U42" s="5" t="inlineStr"/>
+      <c r="V42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -7669,25 +8171,23 @@
         <v>0.899</v>
       </c>
       <c r="F43" s="5" t="n">
+        <v>0.3193219098685215</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.3037218764181746</v>
+      </c>
+      <c r="H43" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="G43" s="5" t="n">
+      <c r="I43" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="H43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L43" s="5" t="n">
@@ -7695,26 +8195,26 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O43" s="5" t="n">
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q43" s="5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S43" s="5" t="n">
@@ -7722,10 +8222,18 @@
       </c>
       <c r="T43" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U43" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W43" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -7750,25 +8258,23 @@
         <v>0.9611</v>
       </c>
       <c r="F44" s="5" t="n">
+        <v>0.1712244976544002</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.2353335402156503</v>
+      </c>
+      <c r="H44" s="5" t="n">
         <v>0.23173278497921</v>
       </c>
-      <c r="G44" s="5" t="n">
+      <c r="I44" s="5" t="n">
         <v>0.0558256772551647</v>
       </c>
-      <c r="H44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L44" s="5" t="n">
@@ -7776,37 +8282,45 @@
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N44" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O44" s="5" t="n">
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="P44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q44" s="5" t="n">
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S44" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="R44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S44" s="5" t="n">
+      <c r="T44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U44" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="T44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U44" s="5" t="n">
+      <c r="V44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W44" s="5" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -7831,25 +8345,23 @@
         <v>0.9852</v>
       </c>
       <c r="F45" s="5" t="n">
+        <v>0.04412090427937254</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.1370696895438673</v>
+      </c>
+      <c r="H45" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="G45" s="5" t="n">
+      <c r="I45" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="H45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J45" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L45" s="5" t="n">
@@ -7857,26 +8369,26 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N45" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="5" t="n">
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q45" s="5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="R45" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S45" s="5" t="n">
@@ -7884,10 +8396,18 @@
       </c>
       <c r="T45" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U45" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W45" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -7912,45 +8432,49 @@
         <v>0.9326</v>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="n">
+        <v>0.00914999709266473</v>
+      </c>
       <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr"/>
-      <c r="P46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr"/>
       <c r="Q46" s="5" t="inlineStr"/>
       <c r="R46" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S46" s="5" t="inlineStr"/>
       <c r="T46" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U46" s="5" t="inlineStr"/>
+      <c r="V46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -7973,45 +8497,49 @@
         <v>0.9326</v>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr"/>
-      <c r="P47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="inlineStr"/>
       <c r="Q47" s="5" t="inlineStr"/>
       <c r="R47" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S47" s="5" t="inlineStr"/>
       <c r="T47" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U47" s="5" t="inlineStr"/>
+      <c r="V47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -8033,46 +8561,52 @@
       <c r="E48" s="5" t="n">
         <v>0.9705</v>
       </c>
-      <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="n">
+        <v>0.0005151765519970652</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.02976254778266307</v>
+      </c>
       <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr"/>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="5" t="inlineStr"/>
-      <c r="P48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P48" s="5" t="inlineStr"/>
       <c r="Q48" s="5" t="inlineStr"/>
       <c r="R48" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S48" s="5" t="inlineStr"/>
       <c r="T48" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U48" s="5" t="inlineStr"/>
+      <c r="V48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -8094,46 +8628,52 @@
       <c r="E49" s="5" t="n">
         <v>0.9869</v>
       </c>
-      <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="n">
+        <v>0.004431688326278604</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.002402426901614629</v>
+      </c>
       <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr"/>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr"/>
-      <c r="P49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P49" s="5" t="inlineStr"/>
       <c r="Q49" s="5" t="inlineStr"/>
       <c r="R49" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S49" s="5" t="inlineStr"/>
       <c r="T49" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U49" s="5" t="inlineStr"/>
+      <c r="V49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -8155,46 +8695,52 @@
       <c r="E50" s="5" t="n">
         <v>0.9484</v>
       </c>
-      <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="n">
+        <v>0.007044941110596614</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.01139050990981172</v>
+      </c>
       <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr"/>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="5" t="inlineStr"/>
-      <c r="P50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P50" s="5" t="inlineStr"/>
       <c r="Q50" s="5" t="inlineStr"/>
       <c r="R50" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S50" s="5" t="inlineStr"/>
       <c r="T50" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U50" s="5" t="inlineStr"/>
+      <c r="V50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -8216,46 +8762,52 @@
       <c r="E51" s="5" t="n">
         <v>0.9664</v>
       </c>
-      <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="n">
+        <v>0.009046837819930542</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.02399070794204605</v>
+      </c>
       <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="5" t="inlineStr"/>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr"/>
-      <c r="O51" s="5" t="inlineStr"/>
-      <c r="P51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P51" s="5" t="inlineStr"/>
       <c r="Q51" s="5" t="inlineStr"/>
       <c r="R51" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S51" s="5" t="inlineStr"/>
       <c r="T51" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U51" s="5" t="inlineStr"/>
+      <c r="V51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -8278,45 +8830,49 @@
         <v>0.9727</v>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="n">
+        <v>0.0264405736692952</v>
+      </c>
       <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr"/>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr"/>
-      <c r="O52" s="5" t="inlineStr"/>
-      <c r="P52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P52" s="5" t="inlineStr"/>
       <c r="Q52" s="5" t="inlineStr"/>
       <c r="R52" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S52" s="5" t="inlineStr"/>
       <c r="T52" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U52" s="5" t="inlineStr"/>
+      <c r="V52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -8338,46 +8894,52 @@
       <c r="E53" s="5" t="n">
         <v>0.9451000000000001</v>
       </c>
-      <c r="F53" s="5" t="inlineStr"/>
-      <c r="G53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="n">
+        <v>0.02288629735304848</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.039511765388348</v>
+      </c>
       <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr"/>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr"/>
-      <c r="O53" s="5" t="inlineStr"/>
-      <c r="P53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P53" s="5" t="inlineStr"/>
       <c r="Q53" s="5" t="inlineStr"/>
       <c r="R53" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S53" s="5" t="inlineStr"/>
       <c r="T53" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U53" s="5" t="inlineStr"/>
+      <c r="V53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -8400,45 +8962,49 @@
         <v>0.9703000000000001</v>
       </c>
       <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="n">
+        <v>0.002002445296444888</v>
+      </c>
       <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr"/>
-      <c r="O54" s="5" t="inlineStr"/>
-      <c r="P54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P54" s="5" t="inlineStr"/>
       <c r="Q54" s="5" t="inlineStr"/>
       <c r="R54" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S54" s="5" t="inlineStr"/>
       <c r="T54" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U54" s="5" t="inlineStr"/>
+      <c r="V54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -8463,43 +9029,45 @@
       <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr"/>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
-      <c r="O55" s="5" t="inlineStr"/>
-      <c r="P55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P55" s="5" t="inlineStr"/>
       <c r="Q55" s="5" t="inlineStr"/>
       <c r="R55" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S55" s="5" t="inlineStr"/>
       <c r="T55" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U55" s="5" t="inlineStr"/>
+      <c r="V55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W55" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C55">
@@ -8730,6 +9298,30 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V55">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W55">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,9 +82,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X55"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -475,14 +472,6 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -566,46 +555,6 @@
           <t>FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY2</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY3</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Curt Avg</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY1</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY2</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY3</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Offl Avg</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -644,9 +593,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="n">
-        <v>7.689919976716642e-05</v>
-      </c>
+      <c r="K2" s="5" t="inlineStr"/>
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
       <c r="N2" s="5" t="n">
@@ -658,14 +605,6 @@
       <c r="P2" s="5" t="n">
         <v>0.9029</v>
       </c>
-      <c r="Q2" s="6" t="inlineStr"/>
-      <c r="R2" s="6" t="inlineStr"/>
-      <c r="S2" s="6" t="inlineStr"/>
-      <c r="T2" s="6" t="inlineStr"/>
-      <c r="U2" s="6" t="inlineStr"/>
-      <c r="V2" s="6" t="inlineStr"/>
-      <c r="W2" s="6" t="inlineStr"/>
-      <c r="X2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -704,7 +643,7 @@
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>17.5</v>
+        <v>14.7</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>132</v>
@@ -726,14 +665,6 @@
       <c r="P3" s="5" t="n">
         <v>0.9461000000000001</v>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
-      <c r="V3" s="6" t="inlineStr"/>
-      <c r="W3" s="6" t="inlineStr"/>
-      <c r="X3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -784,14 +715,6 @@
       <c r="P4" s="5" t="n">
         <v>0.9009</v>
       </c>
-      <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr"/>
-      <c r="S4" s="6" t="inlineStr"/>
-      <c r="T4" s="6" t="inlineStr"/>
-      <c r="U4" s="6" t="inlineStr"/>
-      <c r="V4" s="6" t="inlineStr"/>
-      <c r="W4" s="6" t="inlineStr"/>
-      <c r="X4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -830,16 +753,16 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.05651030523317557</v>
+        <v>0.0523</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.02317489340857803</v>
+        <v>0.0221</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0.233985863287972</v>
@@ -855,30 +778,6 @@
       </c>
       <c r="P5" s="5" t="n">
         <v>0.9459</v>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V5" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W5" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X5" s="6" t="n">
-        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -928,14 +827,6 @@
       <c r="P6" s="5" t="n">
         <v>0.9127</v>
       </c>
-      <c r="Q6" s="6" t="inlineStr"/>
-      <c r="R6" s="6" t="inlineStr"/>
-      <c r="S6" s="6" t="inlineStr"/>
-      <c r="T6" s="6" t="inlineStr"/>
-      <c r="U6" s="6" t="inlineStr"/>
-      <c r="V6" s="6" t="inlineStr"/>
-      <c r="W6" s="6" t="inlineStr"/>
-      <c r="X6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -982,14 +873,6 @@
         <v>0.9677</v>
       </c>
       <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="6" t="inlineStr"/>
-      <c r="R7" s="6" t="inlineStr"/>
-      <c r="S7" s="6" t="inlineStr"/>
-      <c r="T7" s="6" t="inlineStr"/>
-      <c r="U7" s="6" t="inlineStr"/>
-      <c r="V7" s="6" t="inlineStr"/>
-      <c r="W7" s="6" t="inlineStr"/>
-      <c r="X7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1034,10 +917,10 @@
         <v>132</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0</v>
+        <v>0.0033</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.122900063022655</v>
+        <v>0.1154</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>0.218738210926131</v>
@@ -1054,30 +937,6 @@
       <c r="P8" s="5" t="n">
         <v>0.9566</v>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V8" s="6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="W8" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="X8" s="6" t="n">
-        <v>0.04666666666666667</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1116,16 +975,16 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>110.262</v>
+        <v>110.4</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.3112377321785142</v>
+        <v>0.2171</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.1871790685962398</v>
+        <v>0.1651</v>
       </c>
       <c r="L9" s="5" t="n">
         <v>0.219557634008624</v>
@@ -1142,30 +1001,6 @@
       <c r="P9" s="5" t="n">
         <v>0.885</v>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V9" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="W9" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="X9" s="6" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1210,10 +1045,10 @@
         <v>132</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.03090932674773172</v>
+        <v>0.0251</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.01575629040469695</v>
+        <v>0.0201</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>0.22576156415161</v>
@@ -1230,30 +1065,6 @@
       <c r="P10" s="5" t="n">
         <v>0.9009</v>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V10" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W10" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X10" s="6" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1292,16 +1103,16 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>33</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.002490729449382223</v>
+        <v>0.0067</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.001782948033825171</v>
+        <v>0.0057</v>
       </c>
       <c r="L11" s="5" t="n">
         <v>0.221997464026796</v>
@@ -1318,30 +1129,6 @@
       <c r="P11" s="5" t="n">
         <v>0.9016</v>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V11" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W11" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X11" s="6" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1380,16 +1167,14 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>217</v>
+        <v>217.25</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>0.05764898548542752</v>
-      </c>
+      <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="5" t="n">
-        <v>0.02771241911937317</v>
+        <v>0.0264</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>0.223370431255546</v>
@@ -1406,30 +1191,6 @@
       <c r="P12" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V12" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W12" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X12" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1474,10 +1235,10 @@
         <v>275</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.004763767122036411</v>
+        <v>0.0047</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.009994495181866792</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="L13" s="5" t="n">
         <v>0.224633904533977</v>
@@ -1494,30 +1255,6 @@
       <c r="P13" s="5" t="n">
         <v>0.9798</v>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V13" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W13" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X13" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1556,16 +1293,16 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>167</v>
+        <v>167.75</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>33</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0</v>
+        <v>0.0048</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.03755494542283377</v>
+        <v>0.0375</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>0.221997464026796</v>
@@ -1582,30 +1319,6 @@
       <c r="P14" s="5" t="n">
         <v>0.9006999999999999</v>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V14" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W14" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X14" s="6" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1650,10 +1363,10 @@
         <v>275</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.01359465836631391</v>
+        <v>0.0135</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.05809514889523315</v>
+        <v>0.053</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>0.224633904533977</v>
@@ -1670,30 +1383,6 @@
       <c r="P15" s="5" t="n">
         <v>0.9789</v>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V15" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W15" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X15" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1732,16 +1421,16 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>66</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.3527404105538041</v>
+        <v>0.3012</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>0.22576156415161</v>
@@ -1758,14 +1447,6 @@
       <c r="P16" s="5" t="n">
         <v>0.8972</v>
       </c>
-      <c r="Q16" s="6" t="inlineStr"/>
-      <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="6" t="inlineStr"/>
-      <c r="T16" s="6" t="inlineStr"/>
-      <c r="U16" s="6" t="inlineStr"/>
-      <c r="V16" s="6" t="inlineStr"/>
-      <c r="W16" s="6" t="inlineStr"/>
-      <c r="X16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1810,10 +1491,10 @@
         <v>132</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.02047314071674722</v>
+        <v>0.0217</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.192909506972327</v>
+        <v>0.1852</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0.224633904533977</v>
@@ -1829,30 +1510,6 @@
       </c>
       <c r="P17" s="5" t="n">
         <v>0.9918</v>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V17" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W17" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X17" s="6" t="n">
-        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -1902,14 +1559,6 @@
       <c r="P18" s="5" t="n">
         <v>0.98</v>
       </c>
-      <c r="Q18" s="6" t="inlineStr"/>
-      <c r="R18" s="6" t="inlineStr"/>
-      <c r="S18" s="6" t="inlineStr"/>
-      <c r="T18" s="6" t="inlineStr"/>
-      <c r="U18" s="6" t="inlineStr"/>
-      <c r="V18" s="6" t="inlineStr"/>
-      <c r="W18" s="6" t="inlineStr"/>
-      <c r="X18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1954,10 +1603,10 @@
         <v>33</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.01101053258829965</v>
+        <v>0.016</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.07387293214728219</v>
+        <v>0.0682</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>0.221997464026796</v>
@@ -1974,30 +1623,6 @@
       <c r="P19" s="5" t="n">
         <v>0.8977000000000001</v>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V19" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W19" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X19" s="6" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2036,16 +1661,16 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>132</v>
+        <v>132.6</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>275</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.1446613578781581</v>
+        <v>0.1235</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.08708169836578294</v>
+        <v>0.0743</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>0.219557634008624</v>
@@ -2062,30 +1687,6 @@
       <c r="P20" s="5" t="n">
         <v>0.9094</v>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V20" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="W20" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="X20" s="6" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2130,10 +1731,10 @@
         <v>33</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.08058042423286127</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.214852562805253</v>
+        <v>0.1862</v>
       </c>
       <c r="L21" s="5" t="n">
         <v>0.221997464026796</v>
@@ -2149,30 +1750,6 @@
       </c>
       <c r="P21" s="5" t="n">
         <v>0.9006999999999999</v>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V21" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W21" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X21" s="6" t="n">
-        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="22">
@@ -2234,14 +1811,6 @@
       <c r="P22" s="5" t="n">
         <v>0.918</v>
       </c>
-      <c r="Q22" s="6" t="inlineStr"/>
-      <c r="R22" s="6" t="inlineStr"/>
-      <c r="S22" s="6" t="inlineStr"/>
-      <c r="T22" s="6" t="inlineStr"/>
-      <c r="U22" s="6" t="inlineStr"/>
-      <c r="V22" s="6" t="inlineStr"/>
-      <c r="W22" s="6" t="inlineStr"/>
-      <c r="X22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2280,16 +1849,16 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.1145472215423179</v>
+        <v>0.1091</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.09016405734660438</v>
+        <v>0.0888</v>
       </c>
       <c r="L23" s="5" t="n">
         <v>0.219557634008624</v>
@@ -2306,30 +1875,6 @@
       <c r="P23" s="5" t="n">
         <v>0.9664</v>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V23" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W23" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X23" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2374,10 +1919,10 @@
         <v>132</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.09995898812172677</v>
+        <v>0.089</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.2351425176549525</v>
+        <v>0.1948</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>0.219557634008624</v>
@@ -2394,30 +1939,6 @@
       <c r="P24" s="5" t="n">
         <v>0.918</v>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V24" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W24" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X24" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2456,15 +1977,13 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>66</v>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="n">
-        <v>0.1738300144702074</v>
-      </c>
+      <c r="K25" s="5" t="inlineStr"/>
       <c r="L25" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
@@ -2480,14 +1999,6 @@
       <c r="P25" s="5" t="n">
         <v>0.9789</v>
       </c>
-      <c r="Q25" s="6" t="inlineStr"/>
-      <c r="R25" s="6" t="inlineStr"/>
-      <c r="S25" s="6" t="inlineStr"/>
-      <c r="T25" s="6" t="inlineStr"/>
-      <c r="U25" s="6" t="inlineStr"/>
-      <c r="V25" s="6" t="inlineStr"/>
-      <c r="W25" s="6" t="inlineStr"/>
-      <c r="X25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2526,16 +2037,16 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>118</v>
+        <v>118.4</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>33</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>0.09652176800628354</v>
+        <v>0.0851</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.102248508656513</v>
+        <v>0.0726</v>
       </c>
       <c r="L26" s="5" t="n">
         <v>0.22576156415161</v>
@@ -2552,30 +2063,6 @@
       <c r="P26" s="5" t="n">
         <v>0.8953</v>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V26" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W26" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X26" s="6" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2614,7 +2101,7 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
         <v>132</v>
@@ -2636,14 +2123,6 @@
       <c r="P27" s="5" t="n">
         <v>0.9009</v>
       </c>
-      <c r="Q27" s="6" t="inlineStr"/>
-      <c r="R27" s="6" t="inlineStr"/>
-      <c r="S27" s="6" t="inlineStr"/>
-      <c r="T27" s="6" t="inlineStr"/>
-      <c r="U27" s="6" t="inlineStr"/>
-      <c r="V27" s="6" t="inlineStr"/>
-      <c r="W27" s="6" t="inlineStr"/>
-      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2682,16 +2161,16 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>110</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0.01537795020370658</v>
+        <v>0.0175</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.1155419791589952</v>
+        <v>0.1106</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>0.23150076097273</v>
@@ -2708,30 +2187,6 @@
       <c r="P28" s="5" t="n">
         <v>0.9852</v>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V28" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W28" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X28" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2770,10 +2225,10 @@
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="5" t="n">
-        <v>0.03143429868117342</v>
+        <v>0.031</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0.01995818642776526</v>
+        <v>0.0506</v>
       </c>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
@@ -2786,14 +2241,6 @@
       <c r="P29" s="5" t="n">
         <v>0.8972</v>
       </c>
-      <c r="Q29" s="6" t="inlineStr"/>
-      <c r="R29" s="6" t="inlineStr"/>
-      <c r="S29" s="6" t="inlineStr"/>
-      <c r="T29" s="6" t="inlineStr"/>
-      <c r="U29" s="6" t="inlineStr"/>
-      <c r="V29" s="6" t="inlineStr"/>
-      <c r="W29" s="6" t="inlineStr"/>
-      <c r="X29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2838,10 +2285,10 @@
         <v>132</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0.0163829695880453</v>
+        <v>0.0179</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.004168911693146149</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="L30" s="5" t="n">
         <v>0.216663358752891</v>
@@ -2857,30 +2304,6 @@
       </c>
       <c r="P30" s="5" t="n">
         <v>0.8938</v>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V30" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="W30" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X30" s="6" t="n">
-        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="31">
@@ -2930,14 +2353,6 @@
       <c r="P31" s="5" t="n">
         <v>0.9615</v>
       </c>
-      <c r="Q31" s="6" t="inlineStr"/>
-      <c r="R31" s="6" t="inlineStr"/>
-      <c r="S31" s="6" t="inlineStr"/>
-      <c r="T31" s="6" t="inlineStr"/>
-      <c r="U31" s="6" t="inlineStr"/>
-      <c r="V31" s="6" t="inlineStr"/>
-      <c r="W31" s="6" t="inlineStr"/>
-      <c r="X31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2976,16 +2391,16 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>110</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>0.2335656432170077</v>
+        <v>0.1688</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0.3340540034648357</v>
+        <v>0.3056</v>
       </c>
       <c r="L32" s="5" t="n">
         <v>0.23150076097273</v>
@@ -3002,30 +2417,6 @@
       <c r="P32" s="5" t="n">
         <v>0.9838</v>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V32" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W32" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X32" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3064,16 +2455,16 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>65</v>
+        <v>55.64</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>110</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>0.1782243885346131</v>
+        <v>0.1152</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.09525946892443227</v>
+        <v>0.0897</v>
       </c>
       <c r="L33" s="5" t="n">
         <v>0.23150076097273</v>
@@ -3090,30 +2481,6 @@
       <c r="P33" s="5" t="n">
         <v>0.9838</v>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V33" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W33" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X33" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3158,10 +2525,10 @@
         <v>132</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>0.009262663851755781</v>
+        <v>0.0094</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.01087516384193066</v>
+        <v>0.0113</v>
       </c>
       <c r="L34" s="5" t="n">
         <v>0.219557634008624</v>
@@ -3178,30 +2545,6 @@
       <c r="P34" s="5" t="n">
         <v>0.918</v>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V34" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="W34" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="X34" s="6" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3240,16 +2583,16 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I35" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>0.01089589162947968</v>
+        <v>0.0146</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0.07855967434175215</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="L35" s="5" t="n">
         <v>0.22576156415161</v>
@@ -3266,30 +2609,6 @@
       <c r="P35" s="5" t="n">
         <v>0.9074</v>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V35" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W35" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X35" s="6" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3334,10 +2653,10 @@
         <v>132</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>0.01523671109204405</v>
+        <v>0.0197</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0.1002926421719489</v>
+        <v>0.0959</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>0.219325121104852</v>
@@ -3354,30 +2673,6 @@
       <c r="P36" s="5" t="n">
         <v>1.0181</v>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V36" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="W36" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="X36" s="6" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3422,10 +2717,10 @@
         <v>132</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>0.009670335187359713</v>
+        <v>0.012</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0.1188651181441924</v>
+        <v>0.1111</v>
       </c>
       <c r="L37" s="5" t="n">
         <v>0.218738210926131</v>
@@ -3441,30 +2736,6 @@
       </c>
       <c r="P37" s="5" t="n">
         <v>0.9566</v>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V37" s="6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="W37" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="X37" s="6" t="n">
-        <v>0.04666666666666667</v>
       </c>
     </row>
     <row r="38">
@@ -3526,14 +2797,6 @@
       <c r="P38" s="5" t="n">
         <v>1.0133</v>
       </c>
-      <c r="Q38" s="6" t="inlineStr"/>
-      <c r="R38" s="6" t="inlineStr"/>
-      <c r="S38" s="6" t="inlineStr"/>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" s="6" t="inlineStr"/>
-      <c r="V38" s="6" t="inlineStr"/>
-      <c r="W38" s="6" t="inlineStr"/>
-      <c r="X38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3572,16 +2835,16 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I39" s="2" t="n">
         <v>275</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>0.1723317533761356</v>
+        <v>0.0743</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0.1974440855337861</v>
+        <v>0.1905</v>
       </c>
       <c r="L39" s="5" t="n">
         <v>0.223370431255546</v>
@@ -3598,30 +2861,6 @@
       <c r="P39" s="5" t="n">
         <v>0.9915</v>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V39" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W39" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X39" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3660,16 +2899,16 @@
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>39</v>
+        <v>32.1</v>
       </c>
       <c r="I40" s="2" t="n">
         <v>110</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0.3233227782048679</v>
+        <v>0.245</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0.390009749761537</v>
+        <v>0.3423</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>0.23150076097273</v>
@@ -3686,30 +2925,6 @@
       <c r="P40" s="5" t="n">
         <v>0.9852</v>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V40" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W40" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X40" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3748,16 +2963,16 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>39</v>
+        <v>32.1</v>
       </c>
       <c r="I41" s="2" t="n">
         <v>110</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>0.330054131916018</v>
+        <v>0.2443</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>0.3939618767807501</v>
+        <v>0.3471</v>
       </c>
       <c r="L41" s="5" t="n">
         <v>0.23150076097273</v>
@@ -3774,30 +2989,6 @@
       <c r="P41" s="5" t="n">
         <v>0.9852</v>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V41" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W41" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X41" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3836,10 +3027,10 @@
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="5" t="n">
-        <v>0.2114377575943847</v>
+        <v>0.1857</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0.1744522911233145</v>
+        <v>0.1226</v>
       </c>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
@@ -3852,14 +3043,6 @@
       <c r="P42" s="5" t="n">
         <v>0.9751</v>
       </c>
-      <c r="Q42" s="6" t="inlineStr"/>
-      <c r="R42" s="6" t="inlineStr"/>
-      <c r="S42" s="6" t="inlineStr"/>
-      <c r="T42" s="6" t="inlineStr"/>
-      <c r="U42" s="6" t="inlineStr"/>
-      <c r="V42" s="6" t="inlineStr"/>
-      <c r="W42" s="6" t="inlineStr"/>
-      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3904,10 +3087,10 @@
         <v>33</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>0.3193219098685215</v>
+        <v>0.216</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>0.3037218764181746</v>
+        <v>0.2744</v>
       </c>
       <c r="L43" s="5" t="n">
         <v>0.221997464026796</v>
@@ -3924,30 +3107,6 @@
       <c r="P43" s="5" t="n">
         <v>0.899</v>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V43" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W43" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X43" s="6" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3992,10 +3151,10 @@
         <v>132</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>0.1712244976544002</v>
+        <v>0.15</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>0.2353335402156503</v>
+        <v>0.1592</v>
       </c>
       <c r="L44" s="5" t="n">
         <v>0.23173278497921</v>
@@ -4012,30 +3171,6 @@
       <c r="P44" s="5" t="n">
         <v>0.9611</v>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V44" s="6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="W44" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="X44" s="6" t="n">
-        <v>0.04666666666666667</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4080,10 +3215,10 @@
         <v>110</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>0.04412090427937254</v>
+        <v>0.0401</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>0.1370696895438673</v>
+        <v>0.1286</v>
       </c>
       <c r="L45" s="5" t="n">
         <v>0.23150076097273</v>
@@ -4100,30 +3235,6 @@
       <c r="P45" s="5" t="n">
         <v>0.9852</v>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V45" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W45" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X45" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4162,9 +3273,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="n">
-        <v>0.00914999709266473</v>
-      </c>
+      <c r="K46" s="5" t="inlineStr"/>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="n">
@@ -4176,14 +3285,6 @@
       <c r="P46" s="5" t="n">
         <v>0.9326</v>
       </c>
-      <c r="Q46" s="6" t="inlineStr"/>
-      <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="6" t="inlineStr"/>
-      <c r="T46" s="6" t="inlineStr"/>
-      <c r="U46" s="6" t="inlineStr"/>
-      <c r="V46" s="6" t="inlineStr"/>
-      <c r="W46" s="6" t="inlineStr"/>
-      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4222,9 +3323,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K47" s="5" t="inlineStr"/>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="n">
@@ -4236,14 +3335,6 @@
       <c r="P47" s="5" t="n">
         <v>0.9326</v>
       </c>
-      <c r="Q47" s="6" t="inlineStr"/>
-      <c r="R47" s="6" t="inlineStr"/>
-      <c r="S47" s="6" t="inlineStr"/>
-      <c r="T47" s="6" t="inlineStr"/>
-      <c r="U47" s="6" t="inlineStr"/>
-      <c r="V47" s="6" t="inlineStr"/>
-      <c r="W47" s="6" t="inlineStr"/>
-      <c r="X47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4282,10 +3373,10 @@
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="5" t="n">
-        <v>0.0005151765519970652</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>0.02976254778266307</v>
+        <v>0.029</v>
       </c>
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr"/>
@@ -4298,14 +3389,6 @@
       <c r="P48" s="5" t="n">
         <v>0.9705</v>
       </c>
-      <c r="Q48" s="6" t="inlineStr"/>
-      <c r="R48" s="6" t="inlineStr"/>
-      <c r="S48" s="6" t="inlineStr"/>
-      <c r="T48" s="6" t="inlineStr"/>
-      <c r="U48" s="6" t="inlineStr"/>
-      <c r="V48" s="6" t="inlineStr"/>
-      <c r="W48" s="6" t="inlineStr"/>
-      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4344,10 +3427,10 @@
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="5" t="n">
-        <v>0.004431688326278604</v>
+        <v>0.0044</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>0.002402426901614629</v>
+        <v>0.0032</v>
       </c>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
@@ -4360,14 +3443,6 @@
       <c r="P49" s="5" t="n">
         <v>0.9869</v>
       </c>
-      <c r="Q49" s="6" t="inlineStr"/>
-      <c r="R49" s="6" t="inlineStr"/>
-      <c r="S49" s="6" t="inlineStr"/>
-      <c r="T49" s="6" t="inlineStr"/>
-      <c r="U49" s="6" t="inlineStr"/>
-      <c r="V49" s="6" t="inlineStr"/>
-      <c r="W49" s="6" t="inlineStr"/>
-      <c r="X49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4406,10 +3481,10 @@
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="5" t="n">
-        <v>0.007044941110596614</v>
+        <v>0.0125</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0.01139050990981172</v>
+        <v>0.0136</v>
       </c>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
@@ -4422,14 +3497,6 @@
       <c r="P50" s="5" t="n">
         <v>0.9484</v>
       </c>
-      <c r="Q50" s="6" t="inlineStr"/>
-      <c r="R50" s="6" t="inlineStr"/>
-      <c r="S50" s="6" t="inlineStr"/>
-      <c r="T50" s="6" t="inlineStr"/>
-      <c r="U50" s="6" t="inlineStr"/>
-      <c r="V50" s="6" t="inlineStr"/>
-      <c r="W50" s="6" t="inlineStr"/>
-      <c r="X50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4468,10 +3535,10 @@
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="5" t="n">
-        <v>0.009046837819930542</v>
+        <v>0.0103</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>0.02399070794204605</v>
+        <v>0.0236</v>
       </c>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
@@ -4484,14 +3551,6 @@
       <c r="P51" s="5" t="n">
         <v>0.9664</v>
       </c>
-      <c r="Q51" s="6" t="inlineStr"/>
-      <c r="R51" s="6" t="inlineStr"/>
-      <c r="S51" s="6" t="inlineStr"/>
-      <c r="T51" s="6" t="inlineStr"/>
-      <c r="U51" s="6" t="inlineStr"/>
-      <c r="V51" s="6" t="inlineStr"/>
-      <c r="W51" s="6" t="inlineStr"/>
-      <c r="X51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4530,9 +3589,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="n">
-        <v>0.0264405736692952</v>
-      </c>
+      <c r="K52" s="5" t="inlineStr"/>
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="n">
@@ -4544,14 +3601,6 @@
       <c r="P52" s="5" t="n">
         <v>0.9727</v>
       </c>
-      <c r="Q52" s="6" t="inlineStr"/>
-      <c r="R52" s="6" t="inlineStr"/>
-      <c r="S52" s="6" t="inlineStr"/>
-      <c r="T52" s="6" t="inlineStr"/>
-      <c r="U52" s="6" t="inlineStr"/>
-      <c r="V52" s="6" t="inlineStr"/>
-      <c r="W52" s="6" t="inlineStr"/>
-      <c r="X52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4590,10 +3639,10 @@
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="5" t="n">
-        <v>0.02288629735304848</v>
+        <v>0.0247</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>0.039511765388348</v>
+        <v>0.0396</v>
       </c>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
@@ -4606,14 +3655,6 @@
       <c r="P53" s="5" t="n">
         <v>0.9451000000000001</v>
       </c>
-      <c r="Q53" s="6" t="inlineStr"/>
-      <c r="R53" s="6" t="inlineStr"/>
-      <c r="S53" s="6" t="inlineStr"/>
-      <c r="T53" s="6" t="inlineStr"/>
-      <c r="U53" s="6" t="inlineStr"/>
-      <c r="V53" s="6" t="inlineStr"/>
-      <c r="W53" s="6" t="inlineStr"/>
-      <c r="X53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4652,9 +3693,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="5" t="n">
-        <v>0.002002445296444888</v>
-      </c>
+      <c r="K54" s="5" t="inlineStr"/>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
       <c r="N54" s="5" t="n">
@@ -4666,14 +3705,6 @@
       <c r="P54" s="5" t="n">
         <v>0.9703000000000001</v>
       </c>
-      <c r="Q54" s="6" t="inlineStr"/>
-      <c r="R54" s="6" t="inlineStr"/>
-      <c r="S54" s="6" t="inlineStr"/>
-      <c r="T54" s="6" t="inlineStr"/>
-      <c r="U54" s="6" t="inlineStr"/>
-      <c r="V54" s="6" t="inlineStr"/>
-      <c r="W54" s="6" t="inlineStr"/>
-      <c r="X54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4724,14 +3755,6 @@
       <c r="P55" s="5" t="n">
         <v>1.01</v>
       </c>
-      <c r="Q55" s="6" t="inlineStr"/>
-      <c r="R55" s="6" t="inlineStr"/>
-      <c r="S55" s="6" t="inlineStr"/>
-      <c r="T55" s="6" t="inlineStr"/>
-      <c r="U55" s="6" t="inlineStr"/>
-      <c r="V55" s="6" t="inlineStr"/>
-      <c r="W55" s="6" t="inlineStr"/>
-      <c r="X55" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4744,7 +3767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W55"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4756,146 +3779,62 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY24-25</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="L1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2</t>
-        </is>
-      </c>
-      <c r="M1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="N1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3</t>
-        </is>
-      </c>
-      <c r="O1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="P1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_AVG</t>
-        </is>
-      </c>
-      <c r="Q1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1</t>
-        </is>
-      </c>
-      <c r="R1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="S1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2</t>
-        </is>
-      </c>
-      <c r="T1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="U1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3</t>
-        </is>
-      </c>
-      <c r="V1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="W1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_AVG</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>ALDGASF1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4910,57 +3849,17 @@
         <v>0.9029</v>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="n">
-        <v>7.689919976716642e-05</v>
-      </c>
+      <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>BAKING1</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4982,52 +3881,14 @@
       <c r="I3" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr"/>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="inlineStr"/>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>BARCSF1</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5045,52 +3906,14 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U4" s="5" t="inlineStr"/>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>BLUEGSF1</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5105,10 +3928,10 @@
         <v>0.9459</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.05651030523317557</v>
+        <v>0.0523</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.02317489340857803</v>
+        <v>0.0221</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0.233985863287972</v>
@@ -5116,68 +3939,14 @@
       <c r="I5" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="J5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>BRDDSF01</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5193,52 +3962,14 @@
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="inlineStr"/>
-      <c r="V6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>BUSF1</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5252,52 +3983,14 @@
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U7" s="5" t="inlineStr"/>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>CHILDSF1</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5312,10 +4005,10 @@
         <v>0.9566</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0</v>
+        <v>0.0033</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.122900063022655</v>
+        <v>0.1154</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0.218738210926131</v>
@@ -5323,68 +4016,14 @@
       <c r="I8" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="V8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W8" s="5" t="n">
-        <v>0.04666666666666667</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>CLARESF1</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5399,10 +4038,10 @@
         <v>0.885</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.3112377321785142</v>
+        <v>0.2171</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1871790685962398</v>
+        <v>0.1651</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>0.219557634008624</v>
@@ -5410,68 +4049,14 @@
       <c r="I9" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="J9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S9" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="T9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U9" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>CLERMSF1</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5486,10 +4071,10 @@
         <v>0.9009</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.03090932674773172</v>
+        <v>0.0251</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.01575629040469695</v>
+        <v>0.0201</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0.22576156415161</v>
@@ -5497,68 +4082,14 @@
       <c r="I10" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U10" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>CSPVPS1</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5573,10 +4104,10 @@
         <v>0.9016</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.002490729449382223</v>
+        <v>0.0067</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.001782948033825171</v>
+        <v>0.0057</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>0.221997464026796</v>
@@ -5584,68 +4115,14 @@
       <c r="I11" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="J11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S11" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U11" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W11" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>COLUMSF1</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5659,11 +4136,9 @@
       <c r="E12" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
-      <c r="F12" s="5" t="n">
-        <v>0.05764898548542752</v>
-      </c>
+      <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="n">
-        <v>0.02771241911937317</v>
+        <v>0.0264</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0.223370431255546</v>
@@ -5671,68 +4146,14 @@
       <c r="I12" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>DDSF1</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5747,10 +4168,10 @@
         <v>0.9798</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.004763767122036411</v>
+        <v>0.0047</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.009994495181866792</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>0.224633904533977</v>
@@ -5758,68 +4179,14 @@
       <c r="I13" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="J13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S13" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U13" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W13" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>DAYDSF1</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5834,10 +4201,10 @@
         <v>0.9006999999999999</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>0.0048</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.03755494542283377</v>
+        <v>0.0375</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0.221997464026796</v>
@@ -5845,68 +4212,14 @@
       <c r="I14" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S14" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>EDENVSF1</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5921,10 +4234,10 @@
         <v>0.9789</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.01359465836631391</v>
+        <v>0.0135</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.05809514889523315</v>
+        <v>0.053</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0.224633904533977</v>
@@ -5932,68 +4245,14 @@
       <c r="I15" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="J15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S15" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U15" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>EMERASF1</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6008,10 +4267,10 @@
         <v>0.8972</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.3527404105538041</v>
+        <v>0.3012</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>0.22576156415161</v>
@@ -6019,52 +4278,14 @@
       <c r="I16" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr"/>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="inlineStr"/>
-      <c r="T16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U16" s="5" t="inlineStr"/>
-      <c r="V16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>GANGARR1</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6079,10 +4300,10 @@
         <v>0.9918</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.02047314071674722</v>
+        <v>0.0217</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.192909506972327</v>
+        <v>0.1852</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0.224633904533977</v>
@@ -6090,68 +4311,14 @@
       <c r="I17" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="J17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S17" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U17" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>GUSF1</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6167,52 +4334,14 @@
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="inlineStr"/>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P18" s="5" t="inlineStr"/>
-      <c r="Q18" s="5" t="inlineStr"/>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="inlineStr"/>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U18" s="5" t="inlineStr"/>
-      <c r="V18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>HAMISF1</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6227,10 +4356,10 @@
         <v>0.8977000000000001</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.01101053258829965</v>
+        <v>0.016</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.07387293214728219</v>
+        <v>0.0682</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0.221997464026796</v>
@@ -6238,68 +4367,14 @@
       <c r="I19" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="J19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S19" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U19" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W19" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>HAUGHT11</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6314,10 +4389,10 @@
         <v>0.9094</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.1446613578781581</v>
+        <v>0.1235</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.08708169836578294</v>
+        <v>0.0743</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0.219557634008624</v>
@@ -6325,68 +4400,14 @@
       <c r="I20" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="J20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U20" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>HAYMSF1</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6401,10 +4422,10 @@
         <v>0.9006999999999999</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.08058042423286127</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.214852562805253</v>
+        <v>0.1862</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0.221997464026796</v>
@@ -6412,68 +4433,14 @@
       <c r="I21" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="J21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U21" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W21" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>HUGSF1</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6495,52 +4462,14 @@
       <c r="I22" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr"/>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="inlineStr"/>
-      <c r="T22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U22" s="5" t="inlineStr"/>
-      <c r="V22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>KEPSF1</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6555,10 +4484,10 @@
         <v>0.9664</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.1145472215423179</v>
+        <v>0.1091</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.09016405734660438</v>
+        <v>0.0888</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0.219557634008624</v>
@@ -6566,68 +4495,14 @@
       <c r="I23" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="J23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S23" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U23" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W23" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>KSP1</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6642,10 +4517,10 @@
         <v>0.918</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.09995898812172677</v>
+        <v>0.089</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.2351425176549525</v>
+        <v>0.1948</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0.219557634008624</v>
@@ -6653,68 +4528,14 @@
       <c r="I24" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="J24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S24" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U24" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W24" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>KINGASF1</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6729,61 +4550,21 @@
         <v>0.9789</v>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="n">
-        <v>0.1738300144702074</v>
-      </c>
+      <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr"/>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S25" s="5" t="inlineStr"/>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U25" s="5" t="inlineStr"/>
-      <c r="V25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>LILYSF1</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6798,10 +4579,10 @@
         <v>0.8953</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.09652176800628354</v>
+        <v>0.0851</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.102248508656513</v>
+        <v>0.0726</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>0.22576156415161</v>
@@ -6809,68 +4590,14 @@
       <c r="I26" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="J26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S26" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U26" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W26" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>LRSF1</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6892,52 +4619,14 @@
       <c r="I27" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr"/>
-      <c r="R27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S27" s="5" t="inlineStr"/>
-      <c r="T27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U27" s="5" t="inlineStr"/>
-      <c r="V27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>MARYRSF1</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6952,10 +4641,10 @@
         <v>0.9852</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.01537795020370658</v>
+        <v>0.0175</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.1155419791589952</v>
+        <v>0.1106</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0.23150076097273</v>
@@ -6963,68 +4652,14 @@
       <c r="I28" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="J28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S28" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U28" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W28" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>MIDDLSF1</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7039,59 +4674,21 @@
         <v>0.8972</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.03143429868117342</v>
+        <v>0.031</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.01995818642776526</v>
+        <v>0.0506</v>
       </c>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr"/>
-      <c r="R29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S29" s="5" t="inlineStr"/>
-      <c r="T29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U29" s="5" t="inlineStr"/>
-      <c r="V29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>MOUSF1</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7106,10 +4703,10 @@
         <v>0.8938</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.0163829695880453</v>
+        <v>0.0179</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.004168911693146149</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>0.216663358752891</v>
@@ -7117,68 +4714,14 @@
       <c r="I30" s="5" t="n">
         <v>0.0509815379375577</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S30" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U30" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W30" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>MUCRKSF1</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7194,52 +4737,14 @@
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr"/>
-      <c r="R31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S31" s="5" t="inlineStr"/>
-      <c r="T31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U31" s="5" t="inlineStr"/>
-      <c r="V31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>OAKEY1SF</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7254,10 +4759,10 @@
         <v>0.9838</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.2335656432170077</v>
+        <v>0.1688</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.3340540034648357</v>
+        <v>0.3056</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>0.23150076097273</v>
@@ -7265,68 +4770,14 @@
       <c r="I32" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="J32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S32" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U32" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W32" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>OAKEY2SF</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7341,10 +4792,10 @@
         <v>0.9838</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.1782243885346131</v>
+        <v>0.1152</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.09525946892443227</v>
+        <v>0.0897</v>
       </c>
       <c r="H33" s="5" t="n">
         <v>0.23150076097273</v>
@@ -7352,68 +4803,14 @@
       <c r="I33" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="J33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S33" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U33" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W33" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>RRSF1</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7428,10 +4825,10 @@
         <v>0.918</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.009262663851755781</v>
+        <v>0.0094</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.01087516384193066</v>
+        <v>0.0113</v>
       </c>
       <c r="H34" s="5" t="n">
         <v>0.219557634008624</v>
@@ -7439,68 +4836,14 @@
       <c r="I34" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="J34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S34" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="T34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U34" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W34" s="5" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>RUGBYR1</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7515,10 +4858,10 @@
         <v>0.9074</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.01089589162947968</v>
+        <v>0.0146</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.07855967434175215</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="H35" s="5" t="n">
         <v>0.22576156415161</v>
@@ -7526,68 +4869,14 @@
       <c r="I35" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="J35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S35" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U35" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W35" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>SMCSF1</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7602,10 +4891,10 @@
         <v>1.0181</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.01523671109204405</v>
+        <v>0.0197</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.1002926421719489</v>
+        <v>0.0959</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>0.219325121104852</v>
@@ -7613,68 +4902,14 @@
       <c r="I36" s="5" t="n">
         <v>0.0509806543175163</v>
       </c>
-      <c r="J36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S36" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U36" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W36" s="5" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>SRSF1</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7689,10 +4924,10 @@
         <v>0.9566</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.009670335187359713</v>
+        <v>0.012</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.1188651181441924</v>
+        <v>0.1111</v>
       </c>
       <c r="H37" s="5" t="n">
         <v>0.218738210926131</v>
@@ -7700,68 +4935,14 @@
       <c r="I37" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
-      <c r="J37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S37" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="T37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U37" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="V37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W37" s="5" t="n">
-        <v>0.04666666666666667</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>VALDORA1</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7783,52 +4964,14 @@
       <c r="I38" s="5" t="n">
         <v>0.0593284659737539</v>
       </c>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr"/>
-      <c r="R38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S38" s="5" t="inlineStr"/>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U38" s="5" t="inlineStr"/>
-      <c r="V38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>WANDSF1</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7843,10 +4986,10 @@
         <v>0.9915</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.1723317533761356</v>
+        <v>0.0743</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.1974440855337861</v>
+        <v>0.1905</v>
       </c>
       <c r="H39" s="5" t="n">
         <v>0.223370431255546</v>
@@ -7854,68 +4997,14 @@
       <c r="I39" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
-      <c r="J39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S39" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U39" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W39" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>WARWSF1</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7930,10 +5019,10 @@
         <v>0.9852</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.3233227782048679</v>
+        <v>0.245</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.390009749761537</v>
+        <v>0.3423</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>0.23150076097273</v>
@@ -7941,68 +5030,14 @@
       <c r="I40" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="J40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S40" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U40" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W40" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>WARWSF2</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8017,10 +5052,10 @@
         <v>0.9852</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.330054131916018</v>
+        <v>0.2443</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.3939618767807501</v>
+        <v>0.3471</v>
       </c>
       <c r="H41" s="5" t="n">
         <v>0.23150076097273</v>
@@ -8028,68 +5063,14 @@
       <c r="I41" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="J41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S41" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U41" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W41" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>WDGPH1</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8104,59 +5085,21 @@
         <v>0.9751</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.2114377575943847</v>
+        <v>0.1857</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.1744522911233145</v>
+        <v>0.1226</v>
       </c>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr"/>
-      <c r="R42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S42" s="5" t="inlineStr"/>
-      <c r="T42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U42" s="5" t="inlineStr"/>
-      <c r="V42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>WHITSF1</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8171,10 +5114,10 @@
         <v>0.899</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.3193219098685215</v>
+        <v>0.216</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.3037218764181746</v>
+        <v>0.2744</v>
       </c>
       <c r="H43" s="5" t="n">
         <v>0.221997464026796</v>
@@ -8182,68 +5125,14 @@
       <c r="I43" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="J43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S43" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U43" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W43" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>WOOLGSF1</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8258,10 +5147,10 @@
         <v>0.9611</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.1712244976544002</v>
+        <v>0.15</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.2353335402156503</v>
+        <v>0.1592</v>
       </c>
       <c r="H44" s="5" t="n">
         <v>0.23173278497921</v>
@@ -8269,68 +5158,14 @@
       <c r="I44" s="5" t="n">
         <v>0.0558256772551647</v>
       </c>
-      <c r="J44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S44" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="T44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U44" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="V44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W44" s="5" t="n">
-        <v>0.04666666666666667</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>YARANSF1</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8345,10 +5180,10 @@
         <v>0.9852</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.04412090427937254</v>
+        <v>0.0401</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.1370696895438673</v>
+        <v>0.1286</v>
       </c>
       <c r="H45" s="5" t="n">
         <v>0.23150076097273</v>
@@ -8356,68 +5191,14 @@
       <c r="I45" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="J45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S45" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W45" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>CLRKCWF1</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8432,57 +5213,17 @@
         <v>0.9326</v>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="n">
-        <v>0.00914999709266473</v>
-      </c>
+      <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr"/>
-      <c r="R46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S46" s="5" t="inlineStr"/>
-      <c r="T46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U46" s="5" t="inlineStr"/>
-      <c r="V46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>CLRKCWF2</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8497,57 +5238,17 @@
         <v>0.9326</v>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S47" s="5" t="inlineStr"/>
-      <c r="T47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U47" s="5" t="inlineStr"/>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>COOPGWF1</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8562,59 +5263,21 @@
         <v>0.9705</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.0005151765519970652</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.02976254778266307</v>
+        <v>0.029</v>
       </c>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P48" s="5" t="inlineStr"/>
-      <c r="Q48" s="5" t="inlineStr"/>
-      <c r="R48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S48" s="5" t="inlineStr"/>
-      <c r="T48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U48" s="5" t="inlineStr"/>
-      <c r="V48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>DULAWF1</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8629,59 +5292,21 @@
         <v>0.9869</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.004431688326278604</v>
+        <v>0.0044</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.002402426901614629</v>
+        <v>0.0032</v>
       </c>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr"/>
-      <c r="R49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S49" s="5" t="inlineStr"/>
-      <c r="T49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U49" s="5" t="inlineStr"/>
-      <c r="V49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>KABANWF1</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8696,59 +5321,21 @@
         <v>0.9484</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.007044941110596614</v>
+        <v>0.0125</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.01139050990981172</v>
+        <v>0.0136</v>
       </c>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr"/>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr"/>
-      <c r="R50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S50" s="5" t="inlineStr"/>
-      <c r="T50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U50" s="5" t="inlineStr"/>
-      <c r="V50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>KEPWF1</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8763,59 +5350,21 @@
         <v>0.9664</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.009046837819930542</v>
+        <v>0.0103</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.02399070794204605</v>
+        <v>0.0236</v>
       </c>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr"/>
-      <c r="M51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N51" s="5" t="inlineStr"/>
-      <c r="O51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr"/>
-      <c r="R51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S51" s="5" t="inlineStr"/>
-      <c r="T51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U51" s="5" t="inlineStr"/>
-      <c r="V51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>MCINTYR1</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8830,57 +5379,17 @@
         <v>0.9727</v>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="5" t="n">
-        <v>0.0264405736692952</v>
-      </c>
+      <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr"/>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N52" s="5" t="inlineStr"/>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P52" s="5" t="inlineStr"/>
-      <c r="Q52" s="5" t="inlineStr"/>
-      <c r="R52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S52" s="5" t="inlineStr"/>
-      <c r="T52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U52" s="5" t="inlineStr"/>
-      <c r="V52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>MEWF1</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8895,59 +5404,21 @@
         <v>0.9451000000000001</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.02288629735304848</v>
+        <v>0.0247</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.039511765388348</v>
+        <v>0.0396</v>
       </c>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr"/>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr"/>
-      <c r="M53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N53" s="5" t="inlineStr"/>
-      <c r="O53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr"/>
-      <c r="R53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S53" s="5" t="inlineStr"/>
-      <c r="T53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U53" s="5" t="inlineStr"/>
-      <c r="V53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>WAMBOWF1</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8962,57 +5433,17 @@
         <v>0.9703000000000001</v>
       </c>
       <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="5" t="n">
-        <v>0.002002445296444888</v>
-      </c>
+      <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="inlineStr"/>
-      <c r="M54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N54" s="5" t="inlineStr"/>
-      <c r="O54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P54" s="5" t="inlineStr"/>
-      <c r="Q54" s="5" t="inlineStr"/>
-      <c r="R54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S54" s="5" t="inlineStr"/>
-      <c r="T54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U54" s="5" t="inlineStr"/>
-      <c r="V54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>WHILL1</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -9030,44 +5461,6 @@
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr"/>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N55" s="5" t="inlineStr"/>
-      <c r="O55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="5" t="inlineStr"/>
-      <c r="R55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S55" s="5" t="inlineStr"/>
-      <c r="T55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U55" s="5" t="inlineStr"/>
-      <c r="V55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W55" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C55">
@@ -9154,174 +5547,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J55">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K55">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L55">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M55">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N55">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O55">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P55">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q55">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R55">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S55">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T55">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U55">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V55">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W55">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,6 +82,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -453,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -472,6 +475,14 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,6 +564,46 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>FY26-27 (Draft)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Curt Avg</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY2</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Offl Avg</t>
         </is>
       </c>
     </row>
@@ -605,6 +656,14 @@
       <c r="P2" s="5" t="n">
         <v>0.9029</v>
       </c>
+      <c r="Q2" s="6" t="inlineStr"/>
+      <c r="R2" s="6" t="inlineStr"/>
+      <c r="S2" s="6" t="inlineStr"/>
+      <c r="T2" s="6" t="inlineStr"/>
+      <c r="U2" s="6" t="inlineStr"/>
+      <c r="V2" s="6" t="inlineStr"/>
+      <c r="W2" s="6" t="inlineStr"/>
+      <c r="X2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -665,6 +724,14 @@
       <c r="P3" s="5" t="n">
         <v>0.9461000000000001</v>
       </c>
+      <c r="Q3" s="6" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr"/>
+      <c r="S3" s="6" t="inlineStr"/>
+      <c r="T3" s="6" t="inlineStr"/>
+      <c r="U3" s="6" t="inlineStr"/>
+      <c r="V3" s="6" t="inlineStr"/>
+      <c r="W3" s="6" t="inlineStr"/>
+      <c r="X3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -715,6 +782,14 @@
       <c r="P4" s="5" t="n">
         <v>0.9009</v>
       </c>
+      <c r="Q4" s="6" t="inlineStr"/>
+      <c r="R4" s="6" t="inlineStr"/>
+      <c r="S4" s="6" t="inlineStr"/>
+      <c r="T4" s="6" t="inlineStr"/>
+      <c r="U4" s="6" t="inlineStr"/>
+      <c r="V4" s="6" t="inlineStr"/>
+      <c r="W4" s="6" t="inlineStr"/>
+      <c r="X4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -778,6 +853,30 @@
       </c>
       <c r="P5" s="5" t="n">
         <v>0.9459</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W5" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X5" s="6" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -827,6 +926,14 @@
       <c r="P6" s="5" t="n">
         <v>0.9127</v>
       </c>
+      <c r="Q6" s="6" t="inlineStr"/>
+      <c r="R6" s="6" t="inlineStr"/>
+      <c r="S6" s="6" t="inlineStr"/>
+      <c r="T6" s="6" t="inlineStr"/>
+      <c r="U6" s="6" t="inlineStr"/>
+      <c r="V6" s="6" t="inlineStr"/>
+      <c r="W6" s="6" t="inlineStr"/>
+      <c r="X6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -873,6 +980,14 @@
         <v>0.9677</v>
       </c>
       <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="6" t="inlineStr"/>
+      <c r="R7" s="6" t="inlineStr"/>
+      <c r="S7" s="6" t="inlineStr"/>
+      <c r="T7" s="6" t="inlineStr"/>
+      <c r="U7" s="6" t="inlineStr"/>
+      <c r="V7" s="6" t="inlineStr"/>
+      <c r="W7" s="6" t="inlineStr"/>
+      <c r="X7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -937,6 +1052,30 @@
       <c r="P8" s="5" t="n">
         <v>0.9566</v>
       </c>
+      <c r="Q8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W8" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X8" s="6" t="n">
+        <v>0.04666666666666667</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1001,6 +1140,30 @@
       <c r="P9" s="5" t="n">
         <v>0.885</v>
       </c>
+      <c r="Q9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V9" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W9" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="X9" s="6" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1065,6 +1228,30 @@
       <c r="P10" s="5" t="n">
         <v>0.9009</v>
       </c>
+      <c r="Q10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V10" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W10" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X10" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1128,6 +1315,30 @@
       </c>
       <c r="P11" s="5" t="n">
         <v>0.9016</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W11" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X11" s="6" t="n">
+        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -1191,6 +1402,30 @@
       <c r="P12" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
+      <c r="Q12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V12" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W12" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X12" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1255,6 +1490,30 @@
       <c r="P13" s="5" t="n">
         <v>0.9798</v>
       </c>
+      <c r="Q13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V13" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W13" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X13" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1319,6 +1578,30 @@
       <c r="P14" s="5" t="n">
         <v>0.9006999999999999</v>
       </c>
+      <c r="Q14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V14" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W14" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X14" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1383,6 +1666,30 @@
       <c r="P15" s="5" t="n">
         <v>0.9789</v>
       </c>
+      <c r="Q15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V15" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W15" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X15" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1447,6 +1754,14 @@
       <c r="P16" s="5" t="n">
         <v>0.8972</v>
       </c>
+      <c r="Q16" s="6" t="inlineStr"/>
+      <c r="R16" s="6" t="inlineStr"/>
+      <c r="S16" s="6" t="inlineStr"/>
+      <c r="T16" s="6" t="inlineStr"/>
+      <c r="U16" s="6" t="inlineStr"/>
+      <c r="V16" s="6" t="inlineStr"/>
+      <c r="W16" s="6" t="inlineStr"/>
+      <c r="X16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1510,6 +1825,30 @@
       </c>
       <c r="P17" s="5" t="n">
         <v>0.9918</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V17" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W17" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X17" s="6" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -1559,6 +1898,14 @@
       <c r="P18" s="5" t="n">
         <v>0.98</v>
       </c>
+      <c r="Q18" s="6" t="inlineStr"/>
+      <c r="R18" s="6" t="inlineStr"/>
+      <c r="S18" s="6" t="inlineStr"/>
+      <c r="T18" s="6" t="inlineStr"/>
+      <c r="U18" s="6" t="inlineStr"/>
+      <c r="V18" s="6" t="inlineStr"/>
+      <c r="W18" s="6" t="inlineStr"/>
+      <c r="X18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1623,6 +1970,30 @@
       <c r="P19" s="5" t="n">
         <v>0.8977000000000001</v>
       </c>
+      <c r="Q19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V19" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W19" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X19" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1687,6 +2058,30 @@
       <c r="P20" s="5" t="n">
         <v>0.9094</v>
       </c>
+      <c r="Q20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V20" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W20" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="X20" s="6" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1750,6 +2145,30 @@
       </c>
       <c r="P21" s="5" t="n">
         <v>0.9006999999999999</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V21" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W21" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X21" s="6" t="n">
+        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="22">
@@ -1811,6 +2230,14 @@
       <c r="P22" s="5" t="n">
         <v>0.918</v>
       </c>
+      <c r="Q22" s="6" t="inlineStr"/>
+      <c r="R22" s="6" t="inlineStr"/>
+      <c r="S22" s="6" t="inlineStr"/>
+      <c r="T22" s="6" t="inlineStr"/>
+      <c r="U22" s="6" t="inlineStr"/>
+      <c r="V22" s="6" t="inlineStr"/>
+      <c r="W22" s="6" t="inlineStr"/>
+      <c r="X22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1875,6 +2302,30 @@
       <c r="P23" s="5" t="n">
         <v>0.9664</v>
       </c>
+      <c r="Q23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V23" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W23" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X23" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1938,6 +2389,30 @@
       </c>
       <c r="P24" s="5" t="n">
         <v>0.918</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V24" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W24" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X24" s="6" t="n">
+        <v>0.02666666666666667</v>
       </c>
     </row>
     <row r="25">
@@ -1999,6 +2474,14 @@
       <c r="P25" s="5" t="n">
         <v>0.9789</v>
       </c>
+      <c r="Q25" s="6" t="inlineStr"/>
+      <c r="R25" s="6" t="inlineStr"/>
+      <c r="S25" s="6" t="inlineStr"/>
+      <c r="T25" s="6" t="inlineStr"/>
+      <c r="U25" s="6" t="inlineStr"/>
+      <c r="V25" s="6" t="inlineStr"/>
+      <c r="W25" s="6" t="inlineStr"/>
+      <c r="X25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2062,6 +2545,30 @@
       </c>
       <c r="P26" s="5" t="n">
         <v>0.8953</v>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V26" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W26" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X26" s="6" t="n">
+        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -2123,6 +2630,14 @@
       <c r="P27" s="5" t="n">
         <v>0.9009</v>
       </c>
+      <c r="Q27" s="6" t="inlineStr"/>
+      <c r="R27" s="6" t="inlineStr"/>
+      <c r="S27" s="6" t="inlineStr"/>
+      <c r="T27" s="6" t="inlineStr"/>
+      <c r="U27" s="6" t="inlineStr"/>
+      <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
+      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2186,6 +2701,30 @@
       </c>
       <c r="P28" s="5" t="n">
         <v>0.9852</v>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V28" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W28" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X28" s="6" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="29">
@@ -2241,6 +2780,14 @@
       <c r="P29" s="5" t="n">
         <v>0.8972</v>
       </c>
+      <c r="Q29" s="6" t="inlineStr"/>
+      <c r="R29" s="6" t="inlineStr"/>
+      <c r="S29" s="6" t="inlineStr"/>
+      <c r="T29" s="6" t="inlineStr"/>
+      <c r="U29" s="6" t="inlineStr"/>
+      <c r="V29" s="6" t="inlineStr"/>
+      <c r="W29" s="6" t="inlineStr"/>
+      <c r="X29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2304,6 +2851,30 @@
       </c>
       <c r="P30" s="5" t="n">
         <v>0.8938</v>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V30" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W30" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X30" s="6" t="n">
+        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="31">
@@ -2353,6 +2924,14 @@
       <c r="P31" s="5" t="n">
         <v>0.9615</v>
       </c>
+      <c r="Q31" s="6" t="inlineStr"/>
+      <c r="R31" s="6" t="inlineStr"/>
+      <c r="S31" s="6" t="inlineStr"/>
+      <c r="T31" s="6" t="inlineStr"/>
+      <c r="U31" s="6" t="inlineStr"/>
+      <c r="V31" s="6" t="inlineStr"/>
+      <c r="W31" s="6" t="inlineStr"/>
+      <c r="X31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2417,6 +2996,30 @@
       <c r="P32" s="5" t="n">
         <v>0.9838</v>
       </c>
+      <c r="Q32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V32" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W32" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X32" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2481,6 +3084,30 @@
       <c r="P33" s="5" t="n">
         <v>0.9838</v>
       </c>
+      <c r="Q33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V33" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W33" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X33" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2545,6 +3172,30 @@
       <c r="P34" s="5" t="n">
         <v>0.918</v>
       </c>
+      <c r="Q34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V34" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W34" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="X34" s="6" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2609,6 +3260,30 @@
       <c r="P35" s="5" t="n">
         <v>0.9074</v>
       </c>
+      <c r="Q35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V35" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W35" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X35" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2673,6 +3348,30 @@
       <c r="P36" s="5" t="n">
         <v>1.0181</v>
       </c>
+      <c r="Q36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V36" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W36" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="X36" s="6" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2736,6 +3435,30 @@
       </c>
       <c r="P37" s="5" t="n">
         <v>0.9566</v>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V37" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W37" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X37" s="6" t="n">
+        <v>0.04666666666666667</v>
       </c>
     </row>
     <row r="38">
@@ -2797,6 +3520,14 @@
       <c r="P38" s="5" t="n">
         <v>1.0133</v>
       </c>
+      <c r="Q38" s="6" t="inlineStr"/>
+      <c r="R38" s="6" t="inlineStr"/>
+      <c r="S38" s="6" t="inlineStr"/>
+      <c r="T38" s="6" t="inlineStr"/>
+      <c r="U38" s="6" t="inlineStr"/>
+      <c r="V38" s="6" t="inlineStr"/>
+      <c r="W38" s="6" t="inlineStr"/>
+      <c r="X38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2861,6 +3592,30 @@
       <c r="P39" s="5" t="n">
         <v>0.9915</v>
       </c>
+      <c r="Q39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V39" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W39" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X39" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2925,6 +3680,30 @@
       <c r="P40" s="5" t="n">
         <v>0.9852</v>
       </c>
+      <c r="Q40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V40" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W40" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X40" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2988,6 +3767,30 @@
       </c>
       <c r="P41" s="5" t="n">
         <v>0.9852</v>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V41" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W41" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X41" s="6" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="42">
@@ -3043,6 +3846,14 @@
       <c r="P42" s="5" t="n">
         <v>0.9751</v>
       </c>
+      <c r="Q42" s="6" t="inlineStr"/>
+      <c r="R42" s="6" t="inlineStr"/>
+      <c r="S42" s="6" t="inlineStr"/>
+      <c r="T42" s="6" t="inlineStr"/>
+      <c r="U42" s="6" t="inlineStr"/>
+      <c r="V42" s="6" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
+      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3107,6 +3918,30 @@
       <c r="P43" s="5" t="n">
         <v>0.899</v>
       </c>
+      <c r="Q43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V43" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W43" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X43" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3171,6 +4006,30 @@
       <c r="P44" s="5" t="n">
         <v>0.9611</v>
       </c>
+      <c r="Q44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V44" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W44" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X44" s="6" t="n">
+        <v>0.04666666666666667</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3234,6 +4093,30 @@
       </c>
       <c r="P45" s="5" t="n">
         <v>0.9852</v>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V45" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W45" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X45" s="6" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="46">
@@ -3285,6 +4168,14 @@
       <c r="P46" s="5" t="n">
         <v>0.9326</v>
       </c>
+      <c r="Q46" s="6" t="inlineStr"/>
+      <c r="R46" s="6" t="inlineStr"/>
+      <c r="S46" s="6" t="inlineStr"/>
+      <c r="T46" s="6" t="inlineStr"/>
+      <c r="U46" s="6" t="inlineStr"/>
+      <c r="V46" s="6" t="inlineStr"/>
+      <c r="W46" s="6" t="inlineStr"/>
+      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3335,6 +4226,14 @@
       <c r="P47" s="5" t="n">
         <v>0.9326</v>
       </c>
+      <c r="Q47" s="6" t="inlineStr"/>
+      <c r="R47" s="6" t="inlineStr"/>
+      <c r="S47" s="6" t="inlineStr"/>
+      <c r="T47" s="6" t="inlineStr"/>
+      <c r="U47" s="6" t="inlineStr"/>
+      <c r="V47" s="6" t="inlineStr"/>
+      <c r="W47" s="6" t="inlineStr"/>
+      <c r="X47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3389,6 +4288,14 @@
       <c r="P48" s="5" t="n">
         <v>0.9705</v>
       </c>
+      <c r="Q48" s="6" t="inlineStr"/>
+      <c r="R48" s="6" t="inlineStr"/>
+      <c r="S48" s="6" t="inlineStr"/>
+      <c r="T48" s="6" t="inlineStr"/>
+      <c r="U48" s="6" t="inlineStr"/>
+      <c r="V48" s="6" t="inlineStr"/>
+      <c r="W48" s="6" t="inlineStr"/>
+      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3443,6 +4350,14 @@
       <c r="P49" s="5" t="n">
         <v>0.9869</v>
       </c>
+      <c r="Q49" s="6" t="inlineStr"/>
+      <c r="R49" s="6" t="inlineStr"/>
+      <c r="S49" s="6" t="inlineStr"/>
+      <c r="T49" s="6" t="inlineStr"/>
+      <c r="U49" s="6" t="inlineStr"/>
+      <c r="V49" s="6" t="inlineStr"/>
+      <c r="W49" s="6" t="inlineStr"/>
+      <c r="X49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3497,6 +4412,14 @@
       <c r="P50" s="5" t="n">
         <v>0.9484</v>
       </c>
+      <c r="Q50" s="6" t="inlineStr"/>
+      <c r="R50" s="6" t="inlineStr"/>
+      <c r="S50" s="6" t="inlineStr"/>
+      <c r="T50" s="6" t="inlineStr"/>
+      <c r="U50" s="6" t="inlineStr"/>
+      <c r="V50" s="6" t="inlineStr"/>
+      <c r="W50" s="6" t="inlineStr"/>
+      <c r="X50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3551,6 +4474,14 @@
       <c r="P51" s="5" t="n">
         <v>0.9664</v>
       </c>
+      <c r="Q51" s="6" t="inlineStr"/>
+      <c r="R51" s="6" t="inlineStr"/>
+      <c r="S51" s="6" t="inlineStr"/>
+      <c r="T51" s="6" t="inlineStr"/>
+      <c r="U51" s="6" t="inlineStr"/>
+      <c r="V51" s="6" t="inlineStr"/>
+      <c r="W51" s="6" t="inlineStr"/>
+      <c r="X51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3601,6 +4532,14 @@
       <c r="P52" s="5" t="n">
         <v>0.9727</v>
       </c>
+      <c r="Q52" s="6" t="inlineStr"/>
+      <c r="R52" s="6" t="inlineStr"/>
+      <c r="S52" s="6" t="inlineStr"/>
+      <c r="T52" s="6" t="inlineStr"/>
+      <c r="U52" s="6" t="inlineStr"/>
+      <c r="V52" s="6" t="inlineStr"/>
+      <c r="W52" s="6" t="inlineStr"/>
+      <c r="X52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3655,6 +4594,14 @@
       <c r="P53" s="5" t="n">
         <v>0.9451000000000001</v>
       </c>
+      <c r="Q53" s="6" t="inlineStr"/>
+      <c r="R53" s="6" t="inlineStr"/>
+      <c r="S53" s="6" t="inlineStr"/>
+      <c r="T53" s="6" t="inlineStr"/>
+      <c r="U53" s="6" t="inlineStr"/>
+      <c r="V53" s="6" t="inlineStr"/>
+      <c r="W53" s="6" t="inlineStr"/>
+      <c r="X53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3705,6 +4652,14 @@
       <c r="P54" s="5" t="n">
         <v>0.9703000000000001</v>
       </c>
+      <c r="Q54" s="6" t="inlineStr"/>
+      <c r="R54" s="6" t="inlineStr"/>
+      <c r="S54" s="6" t="inlineStr"/>
+      <c r="T54" s="6" t="inlineStr"/>
+      <c r="U54" s="6" t="inlineStr"/>
+      <c r="V54" s="6" t="inlineStr"/>
+      <c r="W54" s="6" t="inlineStr"/>
+      <c r="X54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3755,6 +4710,14 @@
       <c r="P55" s="5" t="n">
         <v>1.01</v>
       </c>
+      <c r="Q55" s="6" t="inlineStr"/>
+      <c r="R55" s="6" t="inlineStr"/>
+      <c r="S55" s="6" t="inlineStr"/>
+      <c r="T55" s="6" t="inlineStr"/>
+      <c r="U55" s="6" t="inlineStr"/>
+      <c r="V55" s="6" t="inlineStr"/>
+      <c r="W55" s="6" t="inlineStr"/>
+      <c r="X55" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3767,7 +4730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3779,62 +4742,146 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY24-25</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_AVG</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="W1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_AVG</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>ALDGASF1</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3852,14 +4899,52 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>BAKING1</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3881,14 +4966,52 @@
       <c r="I3" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>BARCSF1</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3906,14 +5029,52 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>BLUEGSF1</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3939,14 +5100,68 @@
       <c r="I5" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>BRDDSF01</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3962,14 +5177,52 @@
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>BUSF1</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3983,14 +5236,52 @@
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>CHILDSF1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4016,14 +5307,68 @@
       <c r="I8" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
+      <c r="J8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="n">
+        <v>0.04666666666666667</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>CLARESF1</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4049,14 +5394,68 @@
       <c r="I9" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>CLERMSF1</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4082,14 +5481,68 @@
       <c r="I10" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>CSPVPS1</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4115,14 +5568,68 @@
       <c r="I11" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>COLUMSF1</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4146,14 +5653,68 @@
       <c r="I12" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>DDSF1</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4179,14 +5740,68 @@
       <c r="I13" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
+      <c r="J13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>DAYDSF1</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4212,14 +5827,68 @@
       <c r="I14" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
+      <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>EDENVSF1</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4245,14 +5914,68 @@
       <c r="I15" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>EMERASF1</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4278,14 +6001,52 @@
       <c r="I16" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr"/>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>GANGARR1</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4311,14 +6072,68 @@
       <c r="I17" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
+      <c r="J17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>GUSF1</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4334,14 +6149,52 @@
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr"/>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr"/>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>HAMISF1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4367,14 +6220,68 @@
       <c r="I19" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>HAUGHT11</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4400,14 +6307,68 @@
       <c r="I20" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>HAYMSF1</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4433,14 +6394,68 @@
       <c r="I21" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
+      <c r="J21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>HUGSF1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4462,14 +6477,52 @@
       <c r="I22" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="inlineStr"/>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="inlineStr"/>
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>KEPSF1</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4495,14 +6548,68 @@
       <c r="I23" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
+      <c r="J23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S23" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W23" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>KSP1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4528,14 +6635,68 @@
       <c r="I24" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
+      <c r="J24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W24" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>KINGASF1</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4557,14 +6718,52 @@
       <c r="I25" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S25" s="5" t="inlineStr"/>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr"/>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>LILYSF1</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4590,14 +6789,68 @@
       <c r="I26" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
+      <c r="J26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S26" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U26" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W26" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>LRSF1</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4619,14 +6872,52 @@
       <c r="I27" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S27" s="5" t="inlineStr"/>
+      <c r="T27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U27" s="5" t="inlineStr"/>
+      <c r="V27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>MARYRSF1</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4652,14 +6943,68 @@
       <c r="I28" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S28" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W28" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>MIDDLSF1</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4681,14 +7026,52 @@
       </c>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S29" s="5" t="inlineStr"/>
+      <c r="T29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U29" s="5" t="inlineStr"/>
+      <c r="V29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>MOUSF1</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4714,14 +7097,68 @@
       <c r="I30" s="5" t="n">
         <v>0.0509815379375577</v>
       </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U30" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W30" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>MUCRKSF1</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4737,14 +7174,52 @@
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S31" s="5" t="inlineStr"/>
+      <c r="T31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U31" s="5" t="inlineStr"/>
+      <c r="V31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>OAKEY1SF</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4770,14 +7245,68 @@
       <c r="I32" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S32" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U32" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W32" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>OAKEY2SF</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4803,14 +7332,68 @@
       <c r="I33" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
+      <c r="J33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S33" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U33" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W33" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>RRSF1</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4836,14 +7419,68 @@
       <c r="I34" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="T34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U34" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>RUGBYR1</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4869,14 +7506,68 @@
       <c r="I35" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S35" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U35" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>SMCSF1</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4902,14 +7593,68 @@
       <c r="I36" s="5" t="n">
         <v>0.0509806543175163</v>
       </c>
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S36" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U36" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>SRSF1</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4935,14 +7680,68 @@
       <c r="I37" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
+      <c r="J37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S37" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="T37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U37" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W37" s="5" t="n">
+        <v>0.04666666666666667</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>VALDORA1</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4964,14 +7763,52 @@
       <c r="I38" s="5" t="n">
         <v>0.0593284659737539</v>
       </c>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr"/>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr"/>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S38" s="5" t="inlineStr"/>
+      <c r="T38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U38" s="5" t="inlineStr"/>
+      <c r="V38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>WANDSF1</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4997,14 +7834,68 @@
       <c r="I39" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
+      <c r="J39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S39" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U39" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W39" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>WARWSF1</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5030,14 +7921,68 @@
       <c r="I40" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
+      <c r="J40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S40" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U40" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W40" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>WARWSF2</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5063,14 +8008,68 @@
       <c r="I41" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
+      <c r="J41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S41" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U41" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W41" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>WDGPH1</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5092,14 +8091,52 @@
       </c>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr"/>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr"/>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr"/>
+      <c r="R42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S42" s="5" t="inlineStr"/>
+      <c r="T42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U42" s="5" t="inlineStr"/>
+      <c r="V42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>WHITSF1</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5125,14 +8162,68 @@
       <c r="I43" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
+      <c r="J43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S43" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U43" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W43" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>WOOLGSF1</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5158,14 +8249,68 @@
       <c r="I44" s="5" t="n">
         <v>0.0558256772551647</v>
       </c>
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S44" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="T44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U44" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W44" s="5" t="n">
+        <v>0.04666666666666667</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>YARANSF1</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5191,14 +8336,68 @@
       <c r="I45" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
+      <c r="J45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S45" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U45" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W45" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>CLRKCWF1</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5216,14 +8415,52 @@
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr"/>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr"/>
+      <c r="Q46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S46" s="5" t="inlineStr"/>
+      <c r="T46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U46" s="5" t="inlineStr"/>
+      <c r="V46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>CLRKCWF2</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5241,14 +8478,52 @@
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr"/>
+      <c r="R47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S47" s="5" t="inlineStr"/>
+      <c r="T47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U47" s="5" t="inlineStr"/>
+      <c r="V47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>COOPGWF1</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5270,14 +8545,52 @@
       </c>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr"/>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P48" s="5" t="inlineStr"/>
+      <c r="Q48" s="5" t="inlineStr"/>
+      <c r="R48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S48" s="5" t="inlineStr"/>
+      <c r="T48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U48" s="5" t="inlineStr"/>
+      <c r="V48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>DULAWF1</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5299,14 +8612,52 @@
       </c>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr"/>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N49" s="5" t="inlineStr"/>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr"/>
+      <c r="R49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S49" s="5" t="inlineStr"/>
+      <c r="T49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U49" s="5" t="inlineStr"/>
+      <c r="V49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>KABANWF1</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5328,14 +8679,52 @@
       </c>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N50" s="5" t="inlineStr"/>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P50" s="5" t="inlineStr"/>
+      <c r="Q50" s="5" t="inlineStr"/>
+      <c r="R50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S50" s="5" t="inlineStr"/>
+      <c r="T50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U50" s="5" t="inlineStr"/>
+      <c r="V50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>KEPWF1</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5357,14 +8746,52 @@
       </c>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr"/>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N51" s="5" t="inlineStr"/>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr"/>
+      <c r="R51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S51" s="5" t="inlineStr"/>
+      <c r="T51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U51" s="5" t="inlineStr"/>
+      <c r="V51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>MCINTYR1</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5382,14 +8809,52 @@
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N52" s="5" t="inlineStr"/>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P52" s="5" t="inlineStr"/>
+      <c r="Q52" s="5" t="inlineStr"/>
+      <c r="R52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S52" s="5" t="inlineStr"/>
+      <c r="T52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U52" s="5" t="inlineStr"/>
+      <c r="V52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>MEWF1</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5411,14 +8876,52 @@
       </c>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr"/>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N53" s="5" t="inlineStr"/>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P53" s="5" t="inlineStr"/>
+      <c r="Q53" s="5" t="inlineStr"/>
+      <c r="R53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S53" s="5" t="inlineStr"/>
+      <c r="T53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U53" s="5" t="inlineStr"/>
+      <c r="V53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>WAMBOWF1</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5436,14 +8939,52 @@
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr"/>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N54" s="5" t="inlineStr"/>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P54" s="5" t="inlineStr"/>
+      <c r="Q54" s="5" t="inlineStr"/>
+      <c r="R54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S54" s="5" t="inlineStr"/>
+      <c r="T54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U54" s="5" t="inlineStr"/>
+      <c r="V54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>WHILL1</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5461,6 +9002,44 @@
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="5" t="inlineStr"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N55" s="5" t="inlineStr"/>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P55" s="5" t="inlineStr"/>
+      <c r="Q55" s="5" t="inlineStr"/>
+      <c r="R55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S55" s="5" t="inlineStr"/>
+      <c r="T55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U55" s="5" t="inlineStr"/>
+      <c r="V55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W55" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C55">
@@ -5547,6 +9126,174 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J55">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K55">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L55">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M55">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N55">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O55">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P55">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q55">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R55">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S55">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T55">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U55">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V55">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W55">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X55"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -482,7 +482,6 @@
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,55 +552,50 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>FY24-25</t>
+          <t>FY25-26</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>FY25-26</t>
+          <t>FY26-27</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>FY26-27 (Draft)</t>
+          <t>Curt FY1</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Curt FY1</t>
+          <t>Curt FY2</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Curt FY2</t>
+          <t>Curt FY3</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Curt FY3</t>
+          <t>Curt Avg</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Curt Avg</t>
+          <t>Offl FY1</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Offl FY1</t>
+          <t>Offl FY2</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Offl FY2</t>
+          <t>Offl FY3</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY3</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
         </is>
@@ -648,14 +642,12 @@
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
       <c r="N2" s="5" t="n">
-        <v>0.9659</v>
+        <v>0.9318</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>0.9318</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0.9029</v>
-      </c>
+        <v>0.8948</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="6" t="inlineStr"/>
       <c r="R2" s="6" t="inlineStr"/>
       <c r="S2" s="6" t="inlineStr"/>
@@ -663,7 +655,6 @@
       <c r="U2" s="6" t="inlineStr"/>
       <c r="V2" s="6" t="inlineStr"/>
       <c r="W2" s="6" t="inlineStr"/>
-      <c r="X2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -716,14 +707,12 @@
         <v>0.0559828223482727</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>0.9442</v>
+        <v>0.9593</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>0.9593</v>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v>0.9461000000000001</v>
-      </c>
+        <v>0.9472</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr"/>
       <c r="S3" s="6" t="inlineStr"/>
@@ -731,7 +720,6 @@
       <c r="U3" s="6" t="inlineStr"/>
       <c r="V3" s="6" t="inlineStr"/>
       <c r="W3" s="6" t="inlineStr"/>
-      <c r="X3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -774,14 +762,12 @@
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>0.9009</v>
-      </c>
+        <v>0.8878</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="6" t="inlineStr"/>
       <c r="R4" s="6" t="inlineStr"/>
       <c r="S4" s="6" t="inlineStr"/>
@@ -789,7 +775,6 @@
       <c r="U4" s="6" t="inlineStr"/>
       <c r="V4" s="6" t="inlineStr"/>
       <c r="W4" s="6" t="inlineStr"/>
-      <c r="X4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -846,14 +831,14 @@
         <v>0.0559828223482727</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0.9433</v>
+        <v>0.9543</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.9543</v>
-      </c>
-      <c r="P5" s="5" t="n">
         <v>0.9459</v>
       </c>
+      <c r="P5" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
       </c>
@@ -864,18 +849,15 @@
         <v>0</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V5" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X5" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -919,13 +901,13 @@
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="n">
+        <v>0.929</v>
+      </c>
       <c r="O6" s="5" t="n">
-        <v>0.929</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0.9127</v>
-      </c>
+        <v>0.9247</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="6" t="inlineStr"/>
       <c r="R6" s="6" t="inlineStr"/>
       <c r="S6" s="6" t="inlineStr"/>
@@ -933,7 +915,6 @@
       <c r="U6" s="6" t="inlineStr"/>
       <c r="V6" s="6" t="inlineStr"/>
       <c r="W6" s="6" t="inlineStr"/>
-      <c r="X6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -975,11 +956,13 @@
       <c r="K7" s="5" t="inlineStr"/>
       <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="n">
+        <v>0.9677</v>
+      </c>
       <c r="O7" s="5" t="n">
-        <v>0.9677</v>
-      </c>
-      <c r="P7" s="5" t="inlineStr"/>
+        <v>0.9323</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr"/>
       <c r="Q7" s="6" t="inlineStr"/>
       <c r="R7" s="6" t="inlineStr"/>
       <c r="S7" s="6" t="inlineStr"/>
@@ -987,7 +970,6 @@
       <c r="U7" s="6" t="inlineStr"/>
       <c r="V7" s="6" t="inlineStr"/>
       <c r="W7" s="6" t="inlineStr"/>
-      <c r="X7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1044,13 +1026,13 @@
         <v>0.0522010106762296</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0.9828</v>
+        <v>0.9772</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>0.9772</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>0.9566</v>
+        <v>0.9523</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1062,18 +1044,15 @@
         <v>0</v>
       </c>
       <c r="T8" s="6" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="X8" s="6" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -1132,13 +1111,13 @@
         <v>0.0510095644706063</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0.9116</v>
+        <v>0.9363</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>0.9363</v>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v>0.885</v>
+        <v>0.8572</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1150,18 +1129,15 @@
         <v>0</v>
       </c>
       <c r="T9" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="V9" s="6" t="n">
         <v>0.04</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="X9" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -1220,13 +1196,13 @@
         <v>0.0531062553506225</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0.9009</v>
+        <v>0.8878</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1238,18 +1214,15 @@
         <v>0</v>
       </c>
       <c r="T10" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="V10" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X10" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -1308,13 +1281,13 @@
         <v>0.0524178948511446</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.9356</v>
+        <v>0.9413</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>0.9413</v>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>0.9016</v>
+        <v>0.8731</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1326,18 +1299,15 @@
         <v>0</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="V11" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X11" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -1394,13 +1364,13 @@
         <v>0.0519780465459995</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0.9718</v>
+        <v>0.9865</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>0.9865</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9831</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1412,18 +1382,15 @@
         <v>0</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V12" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X12" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -1482,13 +1449,13 @@
         <v>0.0520360014057779</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0.9755</v>
+        <v>0.9849</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>0.9849</v>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>0.9798</v>
+        <v>0.981</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1500,18 +1467,15 @@
         <v>0</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V13" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X13" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -1570,13 +1534,13 @@
         <v>0.0524178948511446</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.9306</v>
+        <v>0.9396</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>0.9396</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.8758</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1588,18 +1552,15 @@
         <v>0</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="V14" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X14" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -1658,13 +1619,13 @@
         <v>0.0520360014057779</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0.9707</v>
+        <v>0.9823</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>0.9823</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>0.9789</v>
+        <v>0.9797</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1676,18 +1637,15 @@
         <v>0</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V15" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="W15" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X15" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -1746,14 +1704,12 @@
         <v>0.0531062553506225</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0.9331</v>
+        <v>0.9381</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>0.9381</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0.8972</v>
-      </c>
+        <v>0.8854</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="6" t="inlineStr"/>
       <c r="R16" s="6" t="inlineStr"/>
       <c r="S16" s="6" t="inlineStr"/>
@@ -1761,7 +1717,6 @@
       <c r="U16" s="6" t="inlineStr"/>
       <c r="V16" s="6" t="inlineStr"/>
       <c r="W16" s="6" t="inlineStr"/>
-      <c r="X16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1818,14 +1773,14 @@
         <v>0.0520360014057779</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.9788</v>
+        <v>0.9977</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.9977</v>
-      </c>
-      <c r="P17" s="5" t="n">
         <v>0.9918</v>
       </c>
+      <c r="P17" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
       </c>
@@ -1836,18 +1791,15 @@
         <v>0</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V17" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X17" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -1891,13 +1843,13 @@
       <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr"/>
-      <c r="N18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="n">
+        <v>0.9836</v>
+      </c>
       <c r="O18" s="5" t="n">
-        <v>0.9836</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0.98</v>
-      </c>
+        <v>0.9827</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="6" t="inlineStr"/>
       <c r="R18" s="6" t="inlineStr"/>
       <c r="S18" s="6" t="inlineStr"/>
@@ -1905,7 +1857,6 @@
       <c r="U18" s="6" t="inlineStr"/>
       <c r="V18" s="6" t="inlineStr"/>
       <c r="W18" s="6" t="inlineStr"/>
-      <c r="X18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1962,13 +1913,13 @@
         <v>0.0524178948511446</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.9305</v>
+        <v>0.9385</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.9385</v>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.872</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -1980,18 +1931,15 @@
         <v>0</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="V19" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X19" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -2050,13 +1998,13 @@
         <v>0.0510095644706063</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.9332</v>
+        <v>0.9475</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.9475</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0.9094</v>
+        <v>0.8766</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2068,18 +2016,15 @@
         <v>0</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="V20" s="6" t="n">
         <v>0.04</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="X20" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -2138,13 +2083,13 @@
         <v>0.0524178948511446</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.9306</v>
+        <v>0.9396</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0.9396</v>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.8758</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2156,18 +2101,15 @@
         <v>0</v>
       </c>
       <c r="T21" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="V21" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X21" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -2222,14 +2164,12 @@
         <v>0.0510095644706063</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0.9385</v>
+        <v>0.9516</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0.9516</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0.918</v>
-      </c>
+        <v>0.8832</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="6" t="inlineStr"/>
       <c r="R22" s="6" t="inlineStr"/>
       <c r="S22" s="6" t="inlineStr"/>
@@ -2237,7 +2177,6 @@
       <c r="U22" s="6" t="inlineStr"/>
       <c r="V22" s="6" t="inlineStr"/>
       <c r="W22" s="6" t="inlineStr"/>
-      <c r="X22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2294,13 +2233,13 @@
         <v>0.0510095644706063</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9813</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>0.9813</v>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>0.9664</v>
+        <v>0.9574</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2312,18 +2251,15 @@
         <v>0</v>
       </c>
       <c r="T23" s="6" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="V23" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X23" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
     </row>
@@ -2382,13 +2318,13 @@
         <v>0.0510095644706063</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>0.9385</v>
+        <v>0.9516</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>0.9516</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0.918</v>
+        <v>0.8832</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2400,18 +2336,15 @@
         <v>0</v>
       </c>
       <c r="T24" s="6" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="V24" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X24" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
     </row>
@@ -2466,14 +2399,12 @@
         <v>0.0559828223482727</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>0.9775</v>
+        <v>0.9795</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>0.9795</v>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+        <v>0.9791</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr"/>
       <c r="Q25" s="6" t="inlineStr"/>
       <c r="R25" s="6" t="inlineStr"/>
       <c r="S25" s="6" t="inlineStr"/>
@@ -2481,7 +2412,6 @@
       <c r="U25" s="6" t="inlineStr"/>
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="6" t="inlineStr"/>
-      <c r="X25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2538,13 +2468,13 @@
         <v>0.0531062553506225</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>0.9295</v>
+        <v>0.9379</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>0.9379</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>0.8953</v>
+        <v>0.8824</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2556,18 +2486,15 @@
         <v>0</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="V26" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X26" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -2622,14 +2549,12 @@
         <v>0.0531062553506225</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="P27" s="5" t="n">
-        <v>0.9009</v>
-      </c>
+        <v>0.8878</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr"/>
       <c r="Q27" s="6" t="inlineStr"/>
       <c r="R27" s="6" t="inlineStr"/>
       <c r="S27" s="6" t="inlineStr"/>
@@ -2637,7 +2562,6 @@
       <c r="U27" s="6" t="inlineStr"/>
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="6" t="inlineStr"/>
-      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2694,13 +2618,13 @@
         <v>0.0544394673584698</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.9888</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>0.9888</v>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.987</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2712,18 +2636,15 @@
         <v>0</v>
       </c>
       <c r="T28" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V28" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X28" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -2772,14 +2693,12 @@
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="n">
-        <v>0.9331</v>
+        <v>0.9381</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>0.9381</v>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v>0.8972</v>
-      </c>
+        <v>0.8854</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr"/>
       <c r="Q29" s="6" t="inlineStr"/>
       <c r="R29" s="6" t="inlineStr"/>
       <c r="S29" s="6" t="inlineStr"/>
@@ -2787,7 +2706,6 @@
       <c r="U29" s="6" t="inlineStr"/>
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="6" t="inlineStr"/>
-      <c r="X29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2844,13 +2762,13 @@
         <v>0.0509815379375577</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>0.9319</v>
+        <v>0.9328</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>0.9328</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0.8938</v>
+        <v>0.885</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2862,18 +2780,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X30" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -2917,13 +2832,13 @@
       <c r="K31" s="5" t="inlineStr"/>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="n">
+        <v>0.9759</v>
+      </c>
       <c r="O31" s="5" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="P31" s="5" t="n">
-        <v>0.9615</v>
-      </c>
+        <v>0.9579</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="6" t="inlineStr"/>
       <c r="R31" s="6" t="inlineStr"/>
       <c r="S31" s="6" t="inlineStr"/>
@@ -2931,7 +2846,6 @@
       <c r="U31" s="6" t="inlineStr"/>
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="6" t="inlineStr"/>
-      <c r="X31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2988,13 +2902,13 @@
         <v>0.0544394673584698</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>0.981</v>
+        <v>0.9852</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>0.9852</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0.9838</v>
+        <v>0.9856</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -3006,18 +2920,15 @@
         <v>0</v>
       </c>
       <c r="T32" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V32" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X32" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -3076,13 +2987,13 @@
         <v>0.0544394673584698</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>0.981</v>
+        <v>0.9852</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>0.9852</v>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v>0.9838</v>
+        <v>0.9856</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -3094,18 +3005,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U33" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V33" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="W33" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X33" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -3164,13 +3072,13 @@
         <v>0.0510095644706063</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>0.9385</v>
+        <v>0.9516</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>0.9516</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>0.918</v>
+        <v>0.8832</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3182,18 +3090,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U34" s="6" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="V34" s="6" t="n">
         <v>0.04</v>
       </c>
       <c r="W34" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="X34" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -3252,13 +3157,13 @@
         <v>0.0531062553506225</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>0.9397</v>
+        <v>0.9463</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>0.9463</v>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v>0.9074</v>
+        <v>0.8932</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3270,18 +3175,15 @@
         <v>0</v>
       </c>
       <c r="T35" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U35" s="6" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="V35" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="W35" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X35" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -3340,13 +3242,13 @@
         <v>0.0509806543175163</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>1.0159</v>
+        <v>1.0151</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>1.0151</v>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>1.0181</v>
+        <v>1.0179</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3358,18 +3260,15 @@
         <v>0</v>
       </c>
       <c r="T36" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U36" s="6" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="V36" s="6" t="n">
         <v>0.04</v>
       </c>
       <c r="W36" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="X36" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -3428,13 +3327,13 @@
         <v>0.0522010106762296</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>0.9828</v>
+        <v>0.9772</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>0.9772</v>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v>0.9566</v>
+        <v>0.9523</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3446,18 +3345,15 @@
         <v>0</v>
       </c>
       <c r="T37" s="6" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="U37" s="6" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="V37" s="6" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="W37" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="X37" s="6" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -3512,14 +3408,12 @@
         <v>0.0593284659737539</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>1.0145</v>
+        <v>1.0144</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>1.0144</v>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v>1.0133</v>
-      </c>
+        <v>1.0132</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr"/>
       <c r="Q38" s="6" t="inlineStr"/>
       <c r="R38" s="6" t="inlineStr"/>
       <c r="S38" s="6" t="inlineStr"/>
@@ -3527,7 +3421,6 @@
       <c r="U38" s="6" t="inlineStr"/>
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="6" t="inlineStr"/>
-      <c r="X38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3584,13 +3477,13 @@
         <v>0.0519780465459995</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>0.9785</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="P39" s="5" t="n">
-        <v>0.9915</v>
+        <v>0.9903999999999999</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3602,18 +3495,15 @@
         <v>0</v>
       </c>
       <c r="T39" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U39" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V39" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="W39" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X39" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -3672,13 +3562,13 @@
         <v>0.0544394673584698</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.9888</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>0.9888</v>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.987</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3690,18 +3580,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U40" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V40" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="W40" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X40" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -3760,13 +3647,13 @@
         <v>0.0544394673584698</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.9888</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>0.9888</v>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.987</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3778,18 +3665,15 @@
         <v>0</v>
       </c>
       <c r="T41" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U41" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V41" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="W41" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X41" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -3838,14 +3722,12 @@
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
       <c r="N42" s="5" t="n">
-        <v>0.9701</v>
+        <v>0.9767</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>0.9767</v>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v>0.9751</v>
-      </c>
+        <v>0.9761</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr"/>
       <c r="Q42" s="6" t="inlineStr"/>
       <c r="R42" s="6" t="inlineStr"/>
       <c r="S42" s="6" t="inlineStr"/>
@@ -3853,7 +3735,6 @@
       <c r="U42" s="6" t="inlineStr"/>
       <c r="V42" s="6" t="inlineStr"/>
       <c r="W42" s="6" t="inlineStr"/>
-      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3910,13 +3791,13 @@
         <v>0.0524178948511446</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>0.9204</v>
+        <v>0.9398</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>0.9398</v>
-      </c>
-      <c r="P43" s="5" t="n">
-        <v>0.899</v>
+        <v>0.8736</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3928,18 +3809,15 @@
         <v>0</v>
       </c>
       <c r="T43" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U43" s="6" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="V43" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="W43" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X43" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -3998,13 +3876,13 @@
         <v>0.0558256772551647</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>0.985</v>
+        <v>0.9787</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>0.9787</v>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v>0.9611</v>
+        <v>0.9568</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -4016,18 +3894,15 @@
         <v>0</v>
       </c>
       <c r="T44" s="6" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="W44" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="X44" s="6" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -4086,13 +3961,13 @@
         <v>0.0544394673584698</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.9888</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0.9888</v>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.987</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -4104,18 +3979,15 @@
         <v>0</v>
       </c>
       <c r="T45" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U45" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V45" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="W45" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X45" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -4160,14 +4032,12 @@
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="n">
-        <v>0.9497</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>0.9429999999999999</v>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v>0.9326</v>
-      </c>
+        <v>0.9313</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr"/>
       <c r="Q46" s="6" t="inlineStr"/>
       <c r="R46" s="6" t="inlineStr"/>
       <c r="S46" s="6" t="inlineStr"/>
@@ -4175,7 +4045,6 @@
       <c r="U46" s="6" t="inlineStr"/>
       <c r="V46" s="6" t="inlineStr"/>
       <c r="W46" s="6" t="inlineStr"/>
-      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4218,14 +4087,12 @@
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="n">
-        <v>0.9497</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>0.9429999999999999</v>
-      </c>
-      <c r="P47" s="5" t="n">
-        <v>0.9326</v>
-      </c>
+        <v>0.9313</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr"/>
       <c r="Q47" s="6" t="inlineStr"/>
       <c r="R47" s="6" t="inlineStr"/>
       <c r="S47" s="6" t="inlineStr"/>
@@ -4233,7 +4100,6 @@
       <c r="U47" s="6" t="inlineStr"/>
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="6" t="inlineStr"/>
-      <c r="X47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4280,14 +4146,12 @@
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr"/>
       <c r="N48" s="5" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9691</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>0.9691</v>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v>0.9705</v>
-      </c>
+        <v>0.9704</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr"/>
       <c r="Q48" s="6" t="inlineStr"/>
       <c r="R48" s="6" t="inlineStr"/>
       <c r="S48" s="6" t="inlineStr"/>
@@ -4295,7 +4159,6 @@
       <c r="U48" s="6" t="inlineStr"/>
       <c r="V48" s="6" t="inlineStr"/>
       <c r="W48" s="6" t="inlineStr"/>
-      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4342,14 +4205,12 @@
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
       <c r="N49" s="5" t="n">
-        <v>0.977</v>
+        <v>0.9853</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>0.9853</v>
-      </c>
-      <c r="P49" s="5" t="n">
-        <v>0.9869</v>
-      </c>
+        <v>0.987</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr"/>
       <c r="Q49" s="6" t="inlineStr"/>
       <c r="R49" s="6" t="inlineStr"/>
       <c r="S49" s="6" t="inlineStr"/>
@@ -4357,7 +4218,6 @@
       <c r="U49" s="6" t="inlineStr"/>
       <c r="V49" s="6" t="inlineStr"/>
       <c r="W49" s="6" t="inlineStr"/>
-      <c r="X49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4404,14 +4264,12 @@
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
       <c r="N50" s="5" t="n">
-        <v>0.9605</v>
+        <v>0.9696</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>0.9696</v>
-      </c>
-      <c r="P50" s="5" t="n">
-        <v>0.9484</v>
-      </c>
+        <v>0.9442</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr"/>
       <c r="Q50" s="6" t="inlineStr"/>
       <c r="R50" s="6" t="inlineStr"/>
       <c r="S50" s="6" t="inlineStr"/>
@@ -4419,7 +4277,6 @@
       <c r="U50" s="6" t="inlineStr"/>
       <c r="V50" s="6" t="inlineStr"/>
       <c r="W50" s="6" t="inlineStr"/>
-      <c r="X50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4466,14 +4323,12 @@
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
       <c r="N51" s="5" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9813</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>0.9813</v>
-      </c>
-      <c r="P51" s="5" t="n">
-        <v>0.9664</v>
-      </c>
+        <v>0.9574</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr"/>
       <c r="Q51" s="6" t="inlineStr"/>
       <c r="R51" s="6" t="inlineStr"/>
       <c r="S51" s="6" t="inlineStr"/>
@@ -4481,7 +4336,6 @@
       <c r="U51" s="6" t="inlineStr"/>
       <c r="V51" s="6" t="inlineStr"/>
       <c r="W51" s="6" t="inlineStr"/>
-      <c r="X51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4524,14 +4378,12 @@
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="n">
-        <v>0.9734</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>0.9723000000000001</v>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v>0.9727</v>
-      </c>
+        <v>0.9729</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr"/>
       <c r="Q52" s="6" t="inlineStr"/>
       <c r="R52" s="6" t="inlineStr"/>
       <c r="S52" s="6" t="inlineStr"/>
@@ -4539,7 +4391,6 @@
       <c r="U52" s="6" t="inlineStr"/>
       <c r="V52" s="6" t="inlineStr"/>
       <c r="W52" s="6" t="inlineStr"/>
-      <c r="X52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4586,14 +4437,12 @@
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
       <c r="N53" s="5" t="n">
-        <v>0.9527</v>
+        <v>0.9649</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>0.9649</v>
-      </c>
-      <c r="P53" s="5" t="n">
-        <v>0.9451000000000001</v>
-      </c>
+        <v>0.9396</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr"/>
       <c r="Q53" s="6" t="inlineStr"/>
       <c r="R53" s="6" t="inlineStr"/>
       <c r="S53" s="6" t="inlineStr"/>
@@ -4601,7 +4450,6 @@
       <c r="U53" s="6" t="inlineStr"/>
       <c r="V53" s="6" t="inlineStr"/>
       <c r="W53" s="6" t="inlineStr"/>
-      <c r="X53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4644,14 +4492,12 @@
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
       <c r="N54" s="5" t="n">
-        <v>0.9698</v>
+        <v>0.967</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>0.967</v>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v>0.9703000000000001</v>
-      </c>
+        <v>0.9701</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr"/>
       <c r="Q54" s="6" t="inlineStr"/>
       <c r="R54" s="6" t="inlineStr"/>
       <c r="S54" s="6" t="inlineStr"/>
@@ -4659,7 +4505,6 @@
       <c r="U54" s="6" t="inlineStr"/>
       <c r="V54" s="6" t="inlineStr"/>
       <c r="W54" s="6" t="inlineStr"/>
-      <c r="X54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4702,14 +4547,12 @@
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="n">
-        <v>1.0142</v>
+        <v>1.0128</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>1.0128</v>
-      </c>
-      <c r="P55" s="5" t="n">
-        <v>1.01</v>
-      </c>
+        <v>1.013</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr"/>
       <c r="Q55" s="6" t="inlineStr"/>
       <c r="R55" s="6" t="inlineStr"/>
       <c r="S55" s="6" t="inlineStr"/>
@@ -4717,7 +4560,6 @@
       <c r="U55" s="6" t="inlineStr"/>
       <c r="V55" s="6" t="inlineStr"/>
       <c r="W55" s="6" t="inlineStr"/>
-      <c r="X55" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4730,7 +4572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W55"/>
+  <dimension ref="A1:V55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4755,7 +4597,6 @@
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4771,105 +4612,100 @@
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>MLF_FY24-25</t>
+          <t>MLF_FY25-26</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>MLF_FY25-26</t>
+          <t>MLF_FY26-27</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>MLF_FY26-27 (Draft)</t>
+          <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY23-24</t>
+          <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY24-25</t>
+          <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
       <c r="H1" s="7" t="inlineStr">
         <is>
-          <t>ELI_CURTAILMENT_NEAR</t>
+          <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
       <c r="I1" s="7" t="inlineStr">
         <is>
-          <t>ELI_CURTAILMENT_MED</t>
+          <t>ISP_CURTAILMENT_FY1</t>
         </is>
       </c>
       <c r="J1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY1</t>
+          <t>ISP_CURTAILMENT_FY1_LABEL</t>
         </is>
       </c>
       <c r="K1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY1_LABEL</t>
+          <t>ISP_CURTAILMENT_FY2</t>
         </is>
       </c>
       <c r="L1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY2</t>
+          <t>ISP_CURTAILMENT_FY2_LABEL</t>
         </is>
       </c>
       <c r="M1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY2_LABEL</t>
+          <t>ISP_CURTAILMENT_FY3</t>
         </is>
       </c>
       <c r="N1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY3</t>
+          <t>ISP_CURTAILMENT_FY3_LABEL</t>
         </is>
       </c>
       <c r="O1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY3_LABEL</t>
+          <t>ISP_CURTAILMENT_AVG</t>
         </is>
       </c>
       <c r="P1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_AVG</t>
+          <t>ISP_OFFLOADING_FY1</t>
         </is>
       </c>
       <c r="Q1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY1</t>
+          <t>ISP_OFFLOADING_FY1_LABEL</t>
         </is>
       </c>
       <c r="R1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY1_LABEL</t>
+          <t>ISP_OFFLOADING_FY2</t>
         </is>
       </c>
       <c r="S1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY2</t>
+          <t>ISP_OFFLOADING_FY2_LABEL</t>
         </is>
       </c>
       <c r="T1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY2_LABEL</t>
+          <t>ISP_OFFLOADING_FY3</t>
         </is>
       </c>
       <c r="U1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY3</t>
+          <t>ISP_OFFLOADING_FY3_LABEL</t>
         </is>
       </c>
       <c r="V1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_AVG</t>
         </is>
@@ -4887,56 +4723,53 @@
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.9659</v>
+        <v>0.9318</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.9318</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>0.9029</v>
-      </c>
+        <v>0.8948</v>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr"/>
       <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -4950,60 +4783,57 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.9442</v>
+        <v>0.9593</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.9593</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0.9461000000000001</v>
-      </c>
+        <v>0.9472</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="n">
+        <v>0.233985863287972</v>
+      </c>
       <c r="H3" s="5" t="n">
-        <v>0.233985863287972</v>
-      </c>
-      <c r="I3" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr"/>
       <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr"/>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="inlineStr"/>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -5017,56 +4847,53 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0.9009</v>
-      </c>
+        <v>0.8878</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U4" s="5" t="inlineStr"/>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -5080,78 +4907,75 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.9433</v>
+        <v>0.9543</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.9543</v>
+        <v>0.9459</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.9459</v>
+        <v>0.0523</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0523</v>
+        <v>0.0221</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0221</v>
+        <v>0.233985863287972</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.233985863287972</v>
+        <v>0.0559828223482727</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.0559828223482727</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="n">
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="n">
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="n">
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -5166,55 +4990,54 @@
           <t>Solar</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>0.929</v>
+      </c>
       <c r="D6" s="5" t="n">
-        <v>0.929</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0.9127</v>
-      </c>
+        <v>0.9247</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="inlineStr"/>
-      <c r="V6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -5227,53 +5050,54 @@
           <t>Solar</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="n">
+        <v>0.9677</v>
+      </c>
       <c r="D7" s="5" t="n">
-        <v>0.9677</v>
+        <v>0.9323</v>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr"/>
       <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U7" s="5" t="inlineStr"/>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -5287,78 +5111,75 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.9828</v>
+        <v>0.9772</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.9772</v>
+        <v>0.9523</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.9566</v>
+        <v>0.0033</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.1154</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1154</v>
+        <v>0.218738210926131</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.218738210926131</v>
+        <v>0.0522010106762296</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.0522010106762296</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="n">
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="n">
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="V8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W8" s="5" t="n">
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -5374,78 +5195,75 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.9116</v>
+        <v>0.9363</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.9363</v>
+        <v>0.8572</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.885</v>
+        <v>0.2171</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.2171</v>
+        <v>0.1651</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1651</v>
+        <v>0.219557634008624</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.219557634008624</v>
+        <v>0.0510095644706063</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.0510095644706063</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S9" s="5" t="n">
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="T9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U9" s="5" t="n">
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="V9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="n">
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -5461,78 +5279,75 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.8878</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.9009</v>
+        <v>0.0251</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.0251</v>
+        <v>0.0201</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0201</v>
+        <v>0.22576156415161</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.22576156415161</v>
+        <v>0.0531062553506225</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.0531062553506225</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S10" s="5" t="n">
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U10" s="5" t="n">
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="V10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="n">
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -5548,78 +5363,75 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.9356</v>
+        <v>0.9413</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.9413</v>
+        <v>0.8731</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.9016</v>
+        <v>0.0067</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.0067</v>
+        <v>0.0057</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.221997464026796</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.221997464026796</v>
+        <v>0.0524178948511446</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.0524178948511446</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S11" s="5" t="n">
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="T11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U11" s="5" t="n">
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="V11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W11" s="5" t="n">
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -5635,76 +5447,73 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.9718</v>
+        <v>0.9865</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.9865</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0.9824000000000001</v>
-      </c>
-      <c r="F12" s="5" t="inlineStr"/>
+        <v>0.9831</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="n">
+        <v>0.0264</v>
+      </c>
       <c r="G12" s="5" t="n">
-        <v>0.0264</v>
+        <v>0.223370431255546</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.223370431255546</v>
+        <v>0.0519780465459995</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.0519780465459995</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S12" s="5" t="n">
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="n">
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="V12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="n">
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -5720,78 +5529,75 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.9755</v>
+        <v>0.9849</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.9849</v>
+        <v>0.981</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.9798</v>
+        <v>0.0047</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.224633904533977</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.224633904533977</v>
+        <v>0.0520360014057779</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.0520360014057779</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S13" s="5" t="n">
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="T13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U13" s="5" t="n">
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="V13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W13" s="5" t="n">
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -5807,78 +5613,75 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.9306</v>
+        <v>0.9396</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.9396</v>
+        <v>0.8758</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.0048</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0375</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0375</v>
+        <v>0.221997464026796</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.221997464026796</v>
+        <v>0.0524178948511446</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.0524178948511446</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S14" s="5" t="n">
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="n">
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="n">
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -5894,78 +5697,75 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.9707</v>
+        <v>0.9823</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.9823</v>
+        <v>0.9797</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.9789</v>
+        <v>0.0135</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.0135</v>
+        <v>0.053</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.053</v>
+        <v>0.224633904533977</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.224633904533977</v>
+        <v>0.0520360014057779</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.0520360014057779</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S15" s="5" t="n">
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="T15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U15" s="5" t="n">
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="n">
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -5981,64 +5781,61 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.9331</v>
+        <v>0.9381</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.9381</v>
+        <v>0.8854</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.8972</v>
+        <v>0.3012</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.3012</v>
+        <v>0.004</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.004</v>
+        <v>0.22576156415161</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.22576156415161</v>
-      </c>
-      <c r="I16" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr"/>
       <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr"/>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="inlineStr"/>
-      <c r="T16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U16" s="5" t="inlineStr"/>
-      <c r="V16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr"/>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr"/>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -6052,78 +5849,75 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.9788</v>
+        <v>0.9977</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.9977</v>
+        <v>0.9918</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.0217</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.0217</v>
+        <v>0.1852</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.1852</v>
+        <v>0.224633904533977</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.224633904533977</v>
+        <v>0.0520360014057779</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.0520360014057779</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S17" s="5" t="n">
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="T17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U17" s="5" t="n">
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="V17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="n">
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -6138,55 +5932,54 @@
           <t>Solar</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>0.9836</v>
+      </c>
       <c r="D18" s="5" t="n">
-        <v>0.9836</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>0.98</v>
-      </c>
+        <v>0.9827</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="inlineStr"/>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="5" t="inlineStr"/>
-      <c r="Q18" s="5" t="inlineStr"/>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="inlineStr"/>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U18" s="5" t="inlineStr"/>
-      <c r="V18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr"/>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr"/>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -6200,78 +5993,75 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.9305</v>
+        <v>0.9385</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.9385</v>
+        <v>0.872</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.016</v>
+        <v>0.0682</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0682</v>
+        <v>0.221997464026796</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.221997464026796</v>
+        <v>0.0524178948511446</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.0524178948511446</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S19" s="5" t="n">
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U19" s="5" t="n">
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W19" s="5" t="n">
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -6287,78 +6077,75 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.9332</v>
+        <v>0.9475</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.9475</v>
+        <v>0.8766</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.9094</v>
+        <v>0.1235</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.1235</v>
+        <v>0.0743</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0743</v>
+        <v>0.219557634008624</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.219557634008624</v>
+        <v>0.0510095644706063</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.0510095644706063</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="n">
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U20" s="5" t="n">
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="V20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="n">
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -6374,78 +6161,75 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.9306</v>
+        <v>0.9396</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.9396</v>
+        <v>0.8758</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.1862</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.1862</v>
+        <v>0.221997464026796</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.221997464026796</v>
+        <v>0.0524178948511446</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.0524178948511446</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="n">
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="T21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U21" s="5" t="n">
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="V21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W21" s="5" t="n">
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -6461,60 +6245,57 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.9385</v>
+        <v>0.9516</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.9516</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>0.918</v>
-      </c>
+        <v>0.8832</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="n">
+        <v>0.219557634008624</v>
+      </c>
       <c r="H22" s="5" t="n">
-        <v>0.219557634008624</v>
-      </c>
-      <c r="I22" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr"/>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="inlineStr"/>
-      <c r="T22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U22" s="5" t="inlineStr"/>
-      <c r="V22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr"/>
+      <c r="S22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr"/>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -6528,78 +6309,75 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9813</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.9813</v>
+        <v>0.9574</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.9664</v>
+        <v>0.1091</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.1091</v>
+        <v>0.0888</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0888</v>
+        <v>0.219557634008624</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.219557634008624</v>
+        <v>0.0510095644706063</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.0510095644706063</v>
-      </c>
-      <c r="J23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S23" s="5" t="n">
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="T23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U23" s="5" t="n">
+      <c r="S23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="V23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W23" s="5" t="n">
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="n">
         <v>0.02666666666666667</v>
       </c>
     </row>
@@ -6615,78 +6393,75 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.9385</v>
+        <v>0.9516</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.9516</v>
+        <v>0.8832</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.918</v>
+        <v>0.089</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.089</v>
+        <v>0.1948</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.1948</v>
+        <v>0.219557634008624</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.219557634008624</v>
+        <v>0.0510095644706063</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.0510095644706063</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S24" s="5" t="n">
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="T24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U24" s="5" t="n">
+      <c r="S24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="V24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W24" s="5" t="n">
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="n">
         <v>0.02666666666666667</v>
       </c>
     </row>
@@ -6702,60 +6477,57 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.9775</v>
+        <v>0.9795</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0.9795</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+        <v>0.9791</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="n">
+        <v>0.233985863287972</v>
+      </c>
       <c r="H25" s="5" t="n">
-        <v>0.233985863287972</v>
-      </c>
-      <c r="I25" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr"/>
       <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr"/>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S25" s="5" t="inlineStr"/>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U25" s="5" t="inlineStr"/>
-      <c r="V25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr"/>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -6769,78 +6541,75 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>0.9295</v>
+        <v>0.9379</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.9379</v>
+        <v>0.8824</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.8953</v>
+        <v>0.0851</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.0851</v>
+        <v>0.0726</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0726</v>
+        <v>0.22576156415161</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0.22576156415161</v>
+        <v>0.0531062553506225</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0.0531062553506225</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S26" s="5" t="n">
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U26" s="5" t="n">
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="V26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W26" s="5" t="n">
+      <c r="U26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V26" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -6856,60 +6625,57 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0.9009</v>
-      </c>
+        <v>0.8878</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="n">
+        <v>0.22576156415161</v>
+      </c>
       <c r="H27" s="5" t="n">
-        <v>0.22576156415161</v>
-      </c>
-      <c r="I27" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr"/>
       <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr"/>
-      <c r="R27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S27" s="5" t="inlineStr"/>
-      <c r="T27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U27" s="5" t="inlineStr"/>
-      <c r="V27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr"/>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -6923,78 +6689,75 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.9888</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.987</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.0175</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.1106</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.1106</v>
+        <v>0.23150076097273</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.23150076097273</v>
+        <v>0.0544394673584698</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0.0544394673584698</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S28" s="5" t="n">
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U28" s="5" t="n">
+      <c r="S28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="V28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W28" s="5" t="n">
+      <c r="U28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V28" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -7010,60 +6773,57 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0.9331</v>
+        <v>0.9381</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0.9381</v>
+        <v>0.8854</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.8972</v>
+        <v>0.031</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="G29" s="5" t="n">
         <v>0.0506</v>
       </c>
+      <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr"/>
       <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr"/>
-      <c r="R29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S29" s="5" t="inlineStr"/>
-      <c r="T29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U29" s="5" t="inlineStr"/>
-      <c r="V29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="inlineStr"/>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -7077,78 +6837,75 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>0.9319</v>
+        <v>0.9328</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>0.9328</v>
+        <v>0.885</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.8938</v>
+        <v>0.0179</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.216663358752891</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0.216663358752891</v>
+        <v>0.0509815379375577</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0.0509815379375577</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S30" s="5" t="n">
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U30" s="5" t="n">
+      <c r="S30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="V30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W30" s="5" t="n">
+      <c r="U30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -7163,55 +6920,54 @@
           <t>Solar</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="n">
+        <v>0.9759</v>
+      </c>
       <c r="D31" s="5" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0.9615</v>
-      </c>
+        <v>0.9579</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr"/>
       <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr"/>
-      <c r="R31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S31" s="5" t="inlineStr"/>
-      <c r="T31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U31" s="5" t="inlineStr"/>
-      <c r="V31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="inlineStr"/>
+      <c r="S31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T31" s="5" t="inlineStr"/>
+      <c r="U31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -7225,78 +6981,75 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>0.981</v>
+        <v>0.9852</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.9856</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.9838</v>
+        <v>0.1688</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.1688</v>
+        <v>0.3056</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.3056</v>
+        <v>0.23150076097273</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.23150076097273</v>
+        <v>0.0544394673584698</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.0544394673584698</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S32" s="5" t="n">
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="T32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U32" s="5" t="n">
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="V32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W32" s="5" t="n">
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -7312,78 +7065,75 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>0.981</v>
+        <v>0.9852</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.9856</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.9838</v>
+        <v>0.1152</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.1152</v>
+        <v>0.0897</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0897</v>
+        <v>0.23150076097273</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.23150076097273</v>
+        <v>0.0544394673584698</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>0.0544394673584698</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S33" s="5" t="n">
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U33" s="5" t="n">
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="V33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W33" s="5" t="n">
+      <c r="U33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -7399,78 +7149,75 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>0.9385</v>
+        <v>0.9516</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>0.9516</v>
+        <v>0.8832</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.918</v>
+        <v>0.0094</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.0113</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.219557634008624</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0.219557634008624</v>
+        <v>0.0510095644706063</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.0510095644706063</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S34" s="5" t="n">
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="T34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U34" s="5" t="n">
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="V34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W34" s="5" t="n">
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -7486,78 +7233,75 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>0.9397</v>
+        <v>0.9463</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>0.9463</v>
+        <v>0.8932</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.9074</v>
+        <v>0.0146</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.22576156415161</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0.22576156415161</v>
+        <v>0.0531062553506225</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>0.0531062553506225</v>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S35" s="5" t="n">
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="T35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U35" s="5" t="n">
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="V35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W35" s="5" t="n">
+      <c r="U35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -7573,78 +7317,75 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>1.0159</v>
+        <v>1.0151</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1.0151</v>
+        <v>1.0179</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1.0181</v>
+        <v>0.0197</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.0197</v>
+        <v>0.0959</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0959</v>
+        <v>0.219325121104852</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.219325121104852</v>
+        <v>0.0509806543175163</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>0.0509806543175163</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S36" s="5" t="n">
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U36" s="5" t="n">
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="V36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W36" s="5" t="n">
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -7660,78 +7401,75 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>0.9828</v>
+        <v>0.9772</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>0.9772</v>
+        <v>0.9523</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.9566</v>
+        <v>0.012</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.012</v>
+        <v>0.1111</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.1111</v>
+        <v>0.218738210926131</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.218738210926131</v>
+        <v>0.0522010106762296</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>0.0522010106762296</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="R37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S37" s="5" t="n">
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="T37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U37" s="5" t="n">
+      <c r="S37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T37" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="V37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W37" s="5" t="n">
+      <c r="U37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V37" s="5" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -7747,60 +7485,57 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>1.0145</v>
+        <v>1.0144</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1.0144</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>1.0133</v>
-      </c>
+        <v>1.0132</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="n">
+        <v>0.240575567460725</v>
+      </c>
       <c r="H38" s="5" t="n">
-        <v>0.240575567460725</v>
-      </c>
-      <c r="I38" s="5" t="n">
         <v>0.0593284659737539</v>
       </c>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr"/>
       <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr"/>
-      <c r="R38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S38" s="5" t="inlineStr"/>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U38" s="5" t="inlineStr"/>
-      <c r="V38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W38" s="5" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="inlineStr"/>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T38" s="5" t="inlineStr"/>
+      <c r="U38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -7814,78 +7549,75 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>0.9785</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.9915</v>
+        <v>0.0743</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.0743</v>
+        <v>0.1905</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.1905</v>
+        <v>0.223370431255546</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>0.223370431255546</v>
+        <v>0.0519780465459995</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>0.0519780465459995</v>
-      </c>
-      <c r="J39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S39" s="5" t="n">
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="T39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U39" s="5" t="n">
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T39" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="V39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W39" s="5" t="n">
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -7901,78 +7633,75 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.9888</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.987</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.245</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.245</v>
+        <v>0.3423</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.3423</v>
+        <v>0.23150076097273</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0.23150076097273</v>
+        <v>0.0544394673584698</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0.0544394673584698</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S40" s="5" t="n">
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="T40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U40" s="5" t="n">
+      <c r="S40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="V40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W40" s="5" t="n">
+      <c r="U40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V40" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -7988,78 +7717,75 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.9888</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.987</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.2443</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.2443</v>
+        <v>0.3471</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.3471</v>
+        <v>0.23150076097273</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0.23150076097273</v>
+        <v>0.0544394673584698</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>0.0544394673584698</v>
-      </c>
-      <c r="J41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S41" s="5" t="n">
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="T41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U41" s="5" t="n">
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T41" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="V41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W41" s="5" t="n">
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -8075,60 +7801,57 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>0.9701</v>
+        <v>0.9767</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>0.9767</v>
+        <v>0.9761</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.9751</v>
+        <v>0.1857</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.1857</v>
-      </c>
-      <c r="G42" s="5" t="n">
         <v>0.1226</v>
       </c>
+      <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr"/>
       <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr"/>
-      <c r="R42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S42" s="5" t="inlineStr"/>
-      <c r="T42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U42" s="5" t="inlineStr"/>
-      <c r="V42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="inlineStr"/>
+      <c r="S42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T42" s="5" t="inlineStr"/>
+      <c r="U42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -8142,78 +7865,75 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>0.9204</v>
+        <v>0.9398</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>0.9398</v>
+        <v>0.8736</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.899</v>
+        <v>0.216</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.216</v>
+        <v>0.2744</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.2744</v>
+        <v>0.221997464026796</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>0.221997464026796</v>
+        <v>0.0524178948511446</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>0.0524178948511446</v>
-      </c>
-      <c r="J43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S43" s="5" t="n">
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="T43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U43" s="5" t="n">
+      <c r="S43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T43" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="V43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W43" s="5" t="n">
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V43" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -8229,78 +7949,75 @@
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>0.985</v>
+        <v>0.9787</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>0.9787</v>
+        <v>0.9568</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.9611</v>
+        <v>0.15</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.15</v>
+        <v>0.1592</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.1592</v>
+        <v>0.23173278497921</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.23173278497921</v>
+        <v>0.0558256772551647</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>0.0558256772551647</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="R44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S44" s="5" t="n">
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="T44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U44" s="5" t="n">
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="V44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W44" s="5" t="n">
+      <c r="U44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -8316,78 +8033,75 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.9888</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.987</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.0401</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.0401</v>
+        <v>0.1286</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.1286</v>
+        <v>0.23150076097273</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.23150076097273</v>
+        <v>0.0544394673584698</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>0.0544394673584698</v>
-      </c>
-      <c r="J45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S45" s="5" t="n">
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="T45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="n">
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T45" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W45" s="5" t="n">
+      <c r="U45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V45" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -8403,56 +8117,53 @@
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>0.9497</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>0.9429999999999999</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>0.9326</v>
-      </c>
+        <v>0.9313</v>
+      </c>
+      <c r="E46" s="5" t="inlineStr"/>
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr"/>
       <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr"/>
-      <c r="R46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S46" s="5" t="inlineStr"/>
-      <c r="T46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U46" s="5" t="inlineStr"/>
-      <c r="V46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W46" s="5" t="inlineStr"/>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="inlineStr"/>
+      <c r="S46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T46" s="5" t="inlineStr"/>
+      <c r="U46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -8466,56 +8177,53 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>0.9497</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>0.9429999999999999</v>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>0.9326</v>
-      </c>
+        <v>0.9313</v>
+      </c>
+      <c r="E47" s="5" t="inlineStr"/>
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr"/>
       <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S47" s="5" t="inlineStr"/>
-      <c r="T47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U47" s="5" t="inlineStr"/>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="inlineStr"/>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T47" s="5" t="inlineStr"/>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -8529,60 +8237,57 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9691</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>0.9691</v>
+        <v>0.9704</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.9705</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="G48" s="5" t="n">
         <v>0.029</v>
       </c>
+      <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr"/>
       <c r="P48" s="5" t="inlineStr"/>
-      <c r="Q48" s="5" t="inlineStr"/>
-      <c r="R48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S48" s="5" t="inlineStr"/>
-      <c r="T48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U48" s="5" t="inlineStr"/>
-      <c r="V48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W48" s="5" t="inlineStr"/>
+      <c r="Q48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R48" s="5" t="inlineStr"/>
+      <c r="S48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T48" s="5" t="inlineStr"/>
+      <c r="U48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -8596,60 +8301,57 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>0.977</v>
+        <v>0.9853</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>0.9853</v>
+        <v>0.987</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.9869</v>
+        <v>0.0044</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="G49" s="5" t="n">
         <v>0.0032</v>
       </c>
+      <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr"/>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr"/>
       <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr"/>
-      <c r="R49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S49" s="5" t="inlineStr"/>
-      <c r="T49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U49" s="5" t="inlineStr"/>
-      <c r="V49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="inlineStr"/>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T49" s="5" t="inlineStr"/>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -8663,60 +8365,57 @@
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>0.9605</v>
+        <v>0.9696</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>0.9696</v>
+        <v>0.9442</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.9484</v>
+        <v>0.0125</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="G50" s="5" t="n">
         <v>0.0136</v>
       </c>
+      <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr"/>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr"/>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr"/>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr"/>
       <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr"/>
-      <c r="R50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S50" s="5" t="inlineStr"/>
-      <c r="T50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U50" s="5" t="inlineStr"/>
-      <c r="V50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W50" s="5" t="inlineStr"/>
+      <c r="Q50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="inlineStr"/>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T50" s="5" t="inlineStr"/>
+      <c r="U50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -8730,60 +8429,57 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9813</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>0.9813</v>
+        <v>0.9574</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.9664</v>
+        <v>0.0103</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.0103</v>
-      </c>
-      <c r="G51" s="5" t="n">
         <v>0.0236</v>
       </c>
+      <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr"/>
-      <c r="M51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N51" s="5" t="inlineStr"/>
-      <c r="O51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr"/>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr"/>
       <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr"/>
-      <c r="R51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S51" s="5" t="inlineStr"/>
-      <c r="T51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U51" s="5" t="inlineStr"/>
-      <c r="V51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R51" s="5" t="inlineStr"/>
+      <c r="S51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T51" s="5" t="inlineStr"/>
+      <c r="U51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -8797,56 +8493,53 @@
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>0.9734</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>0.9723000000000001</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>0.9727</v>
-      </c>
+        <v>0.9729</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr"/>
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr"/>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N52" s="5" t="inlineStr"/>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr"/>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr"/>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr"/>
       <c r="P52" s="5" t="inlineStr"/>
-      <c r="Q52" s="5" t="inlineStr"/>
-      <c r="R52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S52" s="5" t="inlineStr"/>
-      <c r="T52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U52" s="5" t="inlineStr"/>
-      <c r="V52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W52" s="5" t="inlineStr"/>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="inlineStr"/>
+      <c r="S52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T52" s="5" t="inlineStr"/>
+      <c r="U52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -8860,60 +8553,57 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>0.9527</v>
+        <v>0.9649</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>0.9649</v>
+        <v>0.9396</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.0247</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.0247</v>
-      </c>
-      <c r="G53" s="5" t="n">
         <v>0.0396</v>
       </c>
+      <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr"/>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr"/>
-      <c r="M53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N53" s="5" t="inlineStr"/>
-      <c r="O53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr"/>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr"/>
       <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr"/>
-      <c r="R53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S53" s="5" t="inlineStr"/>
-      <c r="T53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U53" s="5" t="inlineStr"/>
-      <c r="V53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W53" s="5" t="inlineStr"/>
+      <c r="Q53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R53" s="5" t="inlineStr"/>
+      <c r="S53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T53" s="5" t="inlineStr"/>
+      <c r="U53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -8927,56 +8617,53 @@
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>0.9698</v>
+        <v>0.967</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>0.967</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>0.9703000000000001</v>
-      </c>
+        <v>0.9701</v>
+      </c>
+      <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="inlineStr"/>
-      <c r="M54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N54" s="5" t="inlineStr"/>
-      <c r="O54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr"/>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="inlineStr"/>
       <c r="P54" s="5" t="inlineStr"/>
-      <c r="Q54" s="5" t="inlineStr"/>
-      <c r="R54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S54" s="5" t="inlineStr"/>
-      <c r="T54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U54" s="5" t="inlineStr"/>
-      <c r="V54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W54" s="5" t="inlineStr"/>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="inlineStr"/>
+      <c r="S54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T54" s="5" t="inlineStr"/>
+      <c r="U54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -8990,56 +8677,53 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>1.0142</v>
+        <v>1.0128</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>1.0128</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>1.01</v>
-      </c>
+        <v>1.013</v>
+      </c>
+      <c r="E55" s="5" t="inlineStr"/>
       <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr"/>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N55" s="5" t="inlineStr"/>
-      <c r="O55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr"/>
       <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="5" t="inlineStr"/>
-      <c r="R55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S55" s="5" t="inlineStr"/>
-      <c r="T55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U55" s="5" t="inlineStr"/>
-      <c r="V55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W55" s="5" t="inlineStr"/>
+      <c r="Q55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R55" s="5" t="inlineStr"/>
+      <c r="S55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T55" s="5" t="inlineStr"/>
+      <c r="U55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V55" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C55">
@@ -9072,9 +8756,9 @@
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
         <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -9282,18 +8966,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W55">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,9 +82,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W55"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,14 +471,6 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -558,46 +547,6 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>FY26-27</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY1</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY2</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY3</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Curt Avg</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY1</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY2</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY3</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Offl Avg</t>
         </is>
       </c>
     </row>
@@ -647,14 +596,6 @@
       <c r="O2" s="5" t="n">
         <v>0.8948</v>
       </c>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="6" t="inlineStr"/>
-      <c r="R2" s="6" t="inlineStr"/>
-      <c r="S2" s="6" t="inlineStr"/>
-      <c r="T2" s="6" t="inlineStr"/>
-      <c r="U2" s="6" t="inlineStr"/>
-      <c r="V2" s="6" t="inlineStr"/>
-      <c r="W2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -712,14 +653,6 @@
       <c r="O3" s="5" t="n">
         <v>0.9472</v>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
-      <c r="V3" s="6" t="inlineStr"/>
-      <c r="W3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -767,14 +700,6 @@
       <c r="O4" s="5" t="n">
         <v>0.8878</v>
       </c>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr"/>
-      <c r="S4" s="6" t="inlineStr"/>
-      <c r="T4" s="6" t="inlineStr"/>
-      <c r="U4" s="6" t="inlineStr"/>
-      <c r="V4" s="6" t="inlineStr"/>
-      <c r="W4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -835,30 +760,6 @@
       </c>
       <c r="O5" s="5" t="n">
         <v>0.9459</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U5" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V5" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W5" s="6" t="n">
-        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -907,14 +808,6 @@
       <c r="O6" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="P6" s="6" t="inlineStr"/>
-      <c r="Q6" s="6" t="inlineStr"/>
-      <c r="R6" s="6" t="inlineStr"/>
-      <c r="S6" s="6" t="inlineStr"/>
-      <c r="T6" s="6" t="inlineStr"/>
-      <c r="U6" s="6" t="inlineStr"/>
-      <c r="V6" s="6" t="inlineStr"/>
-      <c r="W6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -962,14 +855,6 @@
       <c r="O7" s="5" t="n">
         <v>0.9323</v>
       </c>
-      <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="6" t="inlineStr"/>
-      <c r="R7" s="6" t="inlineStr"/>
-      <c r="S7" s="6" t="inlineStr"/>
-      <c r="T7" s="6" t="inlineStr"/>
-      <c r="U7" s="6" t="inlineStr"/>
-      <c r="V7" s="6" t="inlineStr"/>
-      <c r="W7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1031,30 +916,6 @@
       <c r="O8" s="5" t="n">
         <v>0.9523</v>
       </c>
-      <c r="P8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U8" s="6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="V8" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="W8" s="6" t="n">
-        <v>0.04666666666666667</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1116,30 +977,6 @@
       <c r="O9" s="5" t="n">
         <v>0.8572</v>
       </c>
-      <c r="P9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U9" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V9" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="W9" s="6" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1201,30 +1038,6 @@
       <c r="O10" s="5" t="n">
         <v>0.8878</v>
       </c>
-      <c r="P10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U10" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V10" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W10" s="6" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1285,30 +1098,6 @@
       </c>
       <c r="O11" s="5" t="n">
         <v>0.8731</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U11" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V11" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W11" s="6" t="n">
-        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -1369,30 +1158,6 @@
       <c r="O12" s="5" t="n">
         <v>0.9831</v>
       </c>
-      <c r="P12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U12" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V12" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W12" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1454,30 +1219,6 @@
       <c r="O13" s="5" t="n">
         <v>0.981</v>
       </c>
-      <c r="P13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U13" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V13" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W13" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1539,30 +1280,6 @@
       <c r="O14" s="5" t="n">
         <v>0.8758</v>
       </c>
-      <c r="P14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U14" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V14" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W14" s="6" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1624,30 +1341,6 @@
       <c r="O15" s="5" t="n">
         <v>0.9797</v>
       </c>
-      <c r="P15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U15" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V15" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W15" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1709,14 +1402,6 @@
       <c r="O16" s="5" t="n">
         <v>0.8854</v>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="6" t="inlineStr"/>
-      <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="6" t="inlineStr"/>
-      <c r="T16" s="6" t="inlineStr"/>
-      <c r="U16" s="6" t="inlineStr"/>
-      <c r="V16" s="6" t="inlineStr"/>
-      <c r="W16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1777,30 +1462,6 @@
       </c>
       <c r="O17" s="5" t="n">
         <v>0.9918</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U17" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V17" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W17" s="6" t="n">
-        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -1849,14 +1510,6 @@
       <c r="O18" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="P18" s="6" t="inlineStr"/>
-      <c r="Q18" s="6" t="inlineStr"/>
-      <c r="R18" s="6" t="inlineStr"/>
-      <c r="S18" s="6" t="inlineStr"/>
-      <c r="T18" s="6" t="inlineStr"/>
-      <c r="U18" s="6" t="inlineStr"/>
-      <c r="V18" s="6" t="inlineStr"/>
-      <c r="W18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1918,30 +1571,6 @@
       <c r="O19" s="5" t="n">
         <v>0.872</v>
       </c>
-      <c r="P19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U19" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V19" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W19" s="6" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2003,30 +1632,6 @@
       <c r="O20" s="5" t="n">
         <v>0.8766</v>
       </c>
-      <c r="P20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U20" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V20" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="W20" s="6" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2087,30 +1692,6 @@
       </c>
       <c r="O21" s="5" t="n">
         <v>0.8758</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U21" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V21" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W21" s="6" t="n">
-        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="22">
@@ -2169,14 +1750,6 @@
       <c r="O22" s="5" t="n">
         <v>0.8832</v>
       </c>
-      <c r="P22" s="6" t="inlineStr"/>
-      <c r="Q22" s="6" t="inlineStr"/>
-      <c r="R22" s="6" t="inlineStr"/>
-      <c r="S22" s="6" t="inlineStr"/>
-      <c r="T22" s="6" t="inlineStr"/>
-      <c r="U22" s="6" t="inlineStr"/>
-      <c r="V22" s="6" t="inlineStr"/>
-      <c r="W22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2238,30 +1811,6 @@
       <c r="O23" s="5" t="n">
         <v>0.9574</v>
       </c>
-      <c r="P23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U23" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V23" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W23" s="6" t="n">
-        <v>0.02666666666666667</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2322,30 +1871,6 @@
       </c>
       <c r="O24" s="5" t="n">
         <v>0.8832</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U24" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V24" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W24" s="6" t="n">
-        <v>0.02666666666666667</v>
       </c>
     </row>
     <row r="25">
@@ -2404,14 +1929,6 @@
       <c r="O25" s="5" t="n">
         <v>0.9791</v>
       </c>
-      <c r="P25" s="6" t="inlineStr"/>
-      <c r="Q25" s="6" t="inlineStr"/>
-      <c r="R25" s="6" t="inlineStr"/>
-      <c r="S25" s="6" t="inlineStr"/>
-      <c r="T25" s="6" t="inlineStr"/>
-      <c r="U25" s="6" t="inlineStr"/>
-      <c r="V25" s="6" t="inlineStr"/>
-      <c r="W25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2472,30 +1989,6 @@
       </c>
       <c r="O26" s="5" t="n">
         <v>0.8824</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U26" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V26" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W26" s="6" t="n">
-        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -2554,14 +2047,6 @@
       <c r="O27" s="5" t="n">
         <v>0.8878</v>
       </c>
-      <c r="P27" s="6" t="inlineStr"/>
-      <c r="Q27" s="6" t="inlineStr"/>
-      <c r="R27" s="6" t="inlineStr"/>
-      <c r="S27" s="6" t="inlineStr"/>
-      <c r="T27" s="6" t="inlineStr"/>
-      <c r="U27" s="6" t="inlineStr"/>
-      <c r="V27" s="6" t="inlineStr"/>
-      <c r="W27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2622,30 +2107,6 @@
       </c>
       <c r="O28" s="5" t="n">
         <v>0.987</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U28" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V28" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W28" s="6" t="n">
-        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="29">
@@ -2698,14 +2159,6 @@
       <c r="O29" s="5" t="n">
         <v>0.8854</v>
       </c>
-      <c r="P29" s="6" t="inlineStr"/>
-      <c r="Q29" s="6" t="inlineStr"/>
-      <c r="R29" s="6" t="inlineStr"/>
-      <c r="S29" s="6" t="inlineStr"/>
-      <c r="T29" s="6" t="inlineStr"/>
-      <c r="U29" s="6" t="inlineStr"/>
-      <c r="V29" s="6" t="inlineStr"/>
-      <c r="W29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2766,30 +2219,6 @@
       </c>
       <c r="O30" s="5" t="n">
         <v>0.885</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U30" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V30" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W30" s="6" t="n">
-        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="31">
@@ -2838,14 +2267,6 @@
       <c r="O31" s="5" t="n">
         <v>0.9579</v>
       </c>
-      <c r="P31" s="6" t="inlineStr"/>
-      <c r="Q31" s="6" t="inlineStr"/>
-      <c r="R31" s="6" t="inlineStr"/>
-      <c r="S31" s="6" t="inlineStr"/>
-      <c r="T31" s="6" t="inlineStr"/>
-      <c r="U31" s="6" t="inlineStr"/>
-      <c r="V31" s="6" t="inlineStr"/>
-      <c r="W31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2907,30 +2328,6 @@
       <c r="O32" s="5" t="n">
         <v>0.9856</v>
       </c>
-      <c r="P32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U32" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V32" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W32" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2992,30 +2389,6 @@
       <c r="O33" s="5" t="n">
         <v>0.9856</v>
       </c>
-      <c r="P33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U33" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V33" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W33" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3077,30 +2450,6 @@
       <c r="O34" s="5" t="n">
         <v>0.8832</v>
       </c>
-      <c r="P34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U34" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V34" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="W34" s="6" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3162,30 +2511,6 @@
       <c r="O35" s="5" t="n">
         <v>0.8932</v>
       </c>
-      <c r="P35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U35" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V35" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W35" s="6" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3247,30 +2572,6 @@
       <c r="O36" s="5" t="n">
         <v>1.0179</v>
       </c>
-      <c r="P36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U36" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V36" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="W36" s="6" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3331,30 +2632,6 @@
       </c>
       <c r="O37" s="5" t="n">
         <v>0.9523</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U37" s="6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="V37" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="W37" s="6" t="n">
-        <v>0.04666666666666667</v>
       </c>
     </row>
     <row r="38">
@@ -3413,14 +2690,6 @@
       <c r="O38" s="5" t="n">
         <v>1.0132</v>
       </c>
-      <c r="P38" s="6" t="inlineStr"/>
-      <c r="Q38" s="6" t="inlineStr"/>
-      <c r="R38" s="6" t="inlineStr"/>
-      <c r="S38" s="6" t="inlineStr"/>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" s="6" t="inlineStr"/>
-      <c r="V38" s="6" t="inlineStr"/>
-      <c r="W38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3482,30 +2751,6 @@
       <c r="O39" s="5" t="n">
         <v>0.9903999999999999</v>
       </c>
-      <c r="P39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U39" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V39" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W39" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3567,30 +2812,6 @@
       <c r="O40" s="5" t="n">
         <v>0.987</v>
       </c>
-      <c r="P40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U40" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V40" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W40" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3651,30 +2872,6 @@
       </c>
       <c r="O41" s="5" t="n">
         <v>0.987</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U41" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V41" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W41" s="6" t="n">
-        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="42">
@@ -3727,14 +2924,6 @@
       <c r="O42" s="5" t="n">
         <v>0.9761</v>
       </c>
-      <c r="P42" s="6" t="inlineStr"/>
-      <c r="Q42" s="6" t="inlineStr"/>
-      <c r="R42" s="6" t="inlineStr"/>
-      <c r="S42" s="6" t="inlineStr"/>
-      <c r="T42" s="6" t="inlineStr"/>
-      <c r="U42" s="6" t="inlineStr"/>
-      <c r="V42" s="6" t="inlineStr"/>
-      <c r="W42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3796,30 +2985,6 @@
       <c r="O43" s="5" t="n">
         <v>0.8736</v>
       </c>
-      <c r="P43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U43" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V43" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W43" s="6" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3881,30 +3046,6 @@
       <c r="O44" s="5" t="n">
         <v>0.9568</v>
       </c>
-      <c r="P44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U44" s="6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="V44" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="W44" s="6" t="n">
-        <v>0.04666666666666667</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3965,30 +3106,6 @@
       </c>
       <c r="O45" s="5" t="n">
         <v>0.987</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U45" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V45" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W45" s="6" t="n">
-        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="46">
@@ -4037,14 +3154,6 @@
       <c r="O46" s="5" t="n">
         <v>0.9313</v>
       </c>
-      <c r="P46" s="6" t="inlineStr"/>
-      <c r="Q46" s="6" t="inlineStr"/>
-      <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="6" t="inlineStr"/>
-      <c r="T46" s="6" t="inlineStr"/>
-      <c r="U46" s="6" t="inlineStr"/>
-      <c r="V46" s="6" t="inlineStr"/>
-      <c r="W46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4092,14 +3201,6 @@
       <c r="O47" s="5" t="n">
         <v>0.9313</v>
       </c>
-      <c r="P47" s="6" t="inlineStr"/>
-      <c r="Q47" s="6" t="inlineStr"/>
-      <c r="R47" s="6" t="inlineStr"/>
-      <c r="S47" s="6" t="inlineStr"/>
-      <c r="T47" s="6" t="inlineStr"/>
-      <c r="U47" s="6" t="inlineStr"/>
-      <c r="V47" s="6" t="inlineStr"/>
-      <c r="W47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4151,14 +3252,6 @@
       <c r="O48" s="5" t="n">
         <v>0.9704</v>
       </c>
-      <c r="P48" s="6" t="inlineStr"/>
-      <c r="Q48" s="6" t="inlineStr"/>
-      <c r="R48" s="6" t="inlineStr"/>
-      <c r="S48" s="6" t="inlineStr"/>
-      <c r="T48" s="6" t="inlineStr"/>
-      <c r="U48" s="6" t="inlineStr"/>
-      <c r="V48" s="6" t="inlineStr"/>
-      <c r="W48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4210,14 +3303,6 @@
       <c r="O49" s="5" t="n">
         <v>0.987</v>
       </c>
-      <c r="P49" s="6" t="inlineStr"/>
-      <c r="Q49" s="6" t="inlineStr"/>
-      <c r="R49" s="6" t="inlineStr"/>
-      <c r="S49" s="6" t="inlineStr"/>
-      <c r="T49" s="6" t="inlineStr"/>
-      <c r="U49" s="6" t="inlineStr"/>
-      <c r="V49" s="6" t="inlineStr"/>
-      <c r="W49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4269,14 +3354,6 @@
       <c r="O50" s="5" t="n">
         <v>0.9442</v>
       </c>
-      <c r="P50" s="6" t="inlineStr"/>
-      <c r="Q50" s="6" t="inlineStr"/>
-      <c r="R50" s="6" t="inlineStr"/>
-      <c r="S50" s="6" t="inlineStr"/>
-      <c r="T50" s="6" t="inlineStr"/>
-      <c r="U50" s="6" t="inlineStr"/>
-      <c r="V50" s="6" t="inlineStr"/>
-      <c r="W50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4328,14 +3405,6 @@
       <c r="O51" s="5" t="n">
         <v>0.9574</v>
       </c>
-      <c r="P51" s="6" t="inlineStr"/>
-      <c r="Q51" s="6" t="inlineStr"/>
-      <c r="R51" s="6" t="inlineStr"/>
-      <c r="S51" s="6" t="inlineStr"/>
-      <c r="T51" s="6" t="inlineStr"/>
-      <c r="U51" s="6" t="inlineStr"/>
-      <c r="V51" s="6" t="inlineStr"/>
-      <c r="W51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4383,14 +3452,6 @@
       <c r="O52" s="5" t="n">
         <v>0.9729</v>
       </c>
-      <c r="P52" s="6" t="inlineStr"/>
-      <c r="Q52" s="6" t="inlineStr"/>
-      <c r="R52" s="6" t="inlineStr"/>
-      <c r="S52" s="6" t="inlineStr"/>
-      <c r="T52" s="6" t="inlineStr"/>
-      <c r="U52" s="6" t="inlineStr"/>
-      <c r="V52" s="6" t="inlineStr"/>
-      <c r="W52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4442,14 +3503,6 @@
       <c r="O53" s="5" t="n">
         <v>0.9396</v>
       </c>
-      <c r="P53" s="6" t="inlineStr"/>
-      <c r="Q53" s="6" t="inlineStr"/>
-      <c r="R53" s="6" t="inlineStr"/>
-      <c r="S53" s="6" t="inlineStr"/>
-      <c r="T53" s="6" t="inlineStr"/>
-      <c r="U53" s="6" t="inlineStr"/>
-      <c r="V53" s="6" t="inlineStr"/>
-      <c r="W53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4497,24 +3550,16 @@
       <c r="O54" s="5" t="n">
         <v>0.9701</v>
       </c>
-      <c r="P54" s="6" t="inlineStr"/>
-      <c r="Q54" s="6" t="inlineStr"/>
-      <c r="R54" s="6" t="inlineStr"/>
-      <c r="S54" s="6" t="inlineStr"/>
-      <c r="T54" s="6" t="inlineStr"/>
-      <c r="U54" s="6" t="inlineStr"/>
-      <c r="V54" s="6" t="inlineStr"/>
-      <c r="W54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>WHILL1</t>
+          <t>WAMBOWF2</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Windy Hill Wind Farm</t>
+          <t>Wambo Wind Farm 2</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4539,27 +3584,62 @@
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>12</v>
+        <v>254</v>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr"/>
       <c r="K55" s="5" t="inlineStr"/>
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
-      <c r="N55" s="5" t="n">
+      <c r="N55" s="5" t="inlineStr"/>
+      <c r="O55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>WHILL1</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Windy Hill Wind Farm</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Non-REZ</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr"/>
+      <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="5" t="inlineStr"/>
+      <c r="N56" s="5" t="n">
         <v>1.0128</v>
       </c>
-      <c r="O55" s="5" t="n">
+      <c r="O56" s="5" t="n">
         <v>1.013</v>
       </c>
-      <c r="P55" s="6" t="inlineStr"/>
-      <c r="Q55" s="6" t="inlineStr"/>
-      <c r="R55" s="6" t="inlineStr"/>
-      <c r="S55" s="6" t="inlineStr"/>
-      <c r="T55" s="6" t="inlineStr"/>
-      <c r="U55" s="6" t="inlineStr"/>
-      <c r="V55" s="6" t="inlineStr"/>
-      <c r="W55" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4572,7 +3652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4583,141 +3663,57 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY26-27</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1</t>
-        </is>
-      </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2</t>
-        </is>
-      </c>
-      <c r="L1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="M1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3</t>
-        </is>
-      </c>
-      <c r="N1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="O1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_AVG</t>
-        </is>
-      </c>
-      <c r="P1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1</t>
-        </is>
-      </c>
-      <c r="Q1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="R1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2</t>
-        </is>
-      </c>
-      <c r="S1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="T1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3</t>
-        </is>
-      </c>
-      <c r="U1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="V1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_AVG</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>ALDGASF1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4732,52 +3728,14 @@
       <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr"/>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="inlineStr"/>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R2" s="5" t="inlineStr"/>
-      <c r="S2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>BAKING1</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4796,52 +3754,14 @@
       <c r="H3" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr"/>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>BARCSF1</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4856,52 +3776,14 @@
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>BLUEGSF1</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4924,68 +3806,14 @@
       <c r="H5" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R5" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T5" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V5" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>BRDDSF01</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5000,52 +3828,14 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>BUSF1</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5060,52 +3850,14 @@
       <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr"/>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R7" s="5" t="inlineStr"/>
-      <c r="S7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>CHILDSF1</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5128,68 +3880,14 @@
       <c r="H8" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
-      <c r="I8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R8" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="S8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T8" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="U8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V8" s="5" t="n">
-        <v>0.04666666666666667</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>CLARESF1</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5212,68 +3910,14 @@
       <c r="H9" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="I9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R9" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="S9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T9" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="U9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V9" s="5" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>CLERMSF1</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5296,68 +3940,14 @@
       <c r="H10" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="I10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V10" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>CSPVPS1</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5380,68 +3970,14 @@
       <c r="H11" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R11" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T11" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V11" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>COLUMSF1</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5462,68 +3998,14 @@
       <c r="H12" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
-      <c r="I12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V12" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>DDSF1</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5546,68 +4028,14 @@
       <c r="H13" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T13" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V13" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>DAYDSF1</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5630,68 +4058,14 @@
       <c r="H14" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R14" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V14" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>EDENVSF1</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5714,68 +4088,14 @@
       <c r="H15" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R15" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T15" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V15" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>EMERASF1</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5798,52 +4118,14 @@
       <c r="H16" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr"/>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr"/>
-      <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R16" s="5" t="inlineStr"/>
-      <c r="S16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T16" s="5" t="inlineStr"/>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>GANGARR1</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5866,68 +4148,14 @@
       <c r="H17" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="I17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R17" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T17" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V17" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>GUSF1</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5942,52 +4170,14 @@
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr"/>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O18" s="5" t="inlineStr"/>
-      <c r="P18" s="5" t="inlineStr"/>
-      <c r="Q18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R18" s="5" t="inlineStr"/>
-      <c r="S18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T18" s="5" t="inlineStr"/>
-      <c r="U18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>HAMISF1</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6010,68 +4200,14 @@
       <c r="H19" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="I19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R19" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T19" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V19" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>HAUGHT11</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6094,68 +4230,14 @@
       <c r="H20" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="I20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T20" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="U20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V20" s="5" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>HAYMSF1</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6178,68 +4260,14 @@
       <c r="H21" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="I21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R21" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T21" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V21" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>HUGSF1</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6258,52 +4286,14 @@
       <c r="H22" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R22" s="5" t="inlineStr"/>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T22" s="5" t="inlineStr"/>
-      <c r="U22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>KEPSF1</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6326,68 +4316,14 @@
       <c r="H23" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="I23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R23" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T23" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V23" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>KSP1</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6410,68 +4346,14 @@
       <c r="H24" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="I24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R24" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T24" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V24" s="5" t="n">
-        <v>0.02666666666666667</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>KINGASF1</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6490,52 +4372,14 @@
       <c r="H25" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr"/>
-      <c r="N25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O25" s="5" t="inlineStr"/>
-      <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R25" s="5" t="inlineStr"/>
-      <c r="S25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T25" s="5" t="inlineStr"/>
-      <c r="U25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>LILYSF1</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6558,68 +4402,14 @@
       <c r="H26" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="I26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R26" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T26" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V26" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>LRSF1</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6638,52 +4428,14 @@
       <c r="H27" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O27" s="5" t="inlineStr"/>
-      <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R27" s="5" t="inlineStr"/>
-      <c r="S27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T27" s="5" t="inlineStr"/>
-      <c r="U27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>MARYRSF1</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6706,68 +4458,14 @@
       <c r="H28" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="I28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R28" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T28" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V28" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>MIDDLSF1</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6786,52 +4484,14 @@
       </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O29" s="5" t="inlineStr"/>
-      <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R29" s="5" t="inlineStr"/>
-      <c r="S29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T29" s="5" t="inlineStr"/>
-      <c r="U29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>MOUSF1</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6854,68 +4514,14 @@
       <c r="H30" s="5" t="n">
         <v>0.0509815379375577</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R30" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="S30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V30" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>MUCRKSF1</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6930,52 +4536,14 @@
       <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O31" s="5" t="inlineStr"/>
-      <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R31" s="5" t="inlineStr"/>
-      <c r="S31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T31" s="5" t="inlineStr"/>
-      <c r="U31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>OAKEY1SF</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6998,68 +4566,14 @@
       <c r="H32" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="I32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R32" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T32" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V32" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>OAKEY2SF</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7082,68 +4596,14 @@
       <c r="H33" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="I33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R33" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T33" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V33" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>RRSF1</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7166,68 +4626,14 @@
       <c r="H34" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="I34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R34" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="S34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T34" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="U34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V34" s="5" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>RUGBYR1</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7250,68 +4656,14 @@
       <c r="H35" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="I35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R35" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T35" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V35" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>SMCSF1</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7334,68 +4686,14 @@
       <c r="H36" s="5" t="n">
         <v>0.0509806543175163</v>
       </c>
-      <c r="I36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R36" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="S36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T36" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="U36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V36" s="5" t="n">
-        <v>0.03</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>SRSF1</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7418,68 +4716,14 @@
       <c r="H37" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
-      <c r="I37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Q37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R37" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="S37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T37" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="U37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V37" s="5" t="n">
-        <v>0.04666666666666667</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>VALDORA1</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7498,52 +4742,14 @@
       <c r="H38" s="5" t="n">
         <v>0.0593284659737539</v>
       </c>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr"/>
-      <c r="N38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O38" s="5" t="inlineStr"/>
-      <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R38" s="5" t="inlineStr"/>
-      <c r="S38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T38" s="5" t="inlineStr"/>
-      <c r="U38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>WANDSF1</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7566,68 +4772,14 @@
       <c r="H39" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
-      <c r="I39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R39" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T39" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V39" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>WARWSF1</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7650,68 +4802,14 @@
       <c r="H40" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="I40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R40" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T40" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V40" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>WARWSF2</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7734,68 +4832,14 @@
       <c r="H41" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="I41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R41" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T41" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V41" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>WDGPH1</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7814,52 +4858,14 @@
       </c>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr"/>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M42" s="5" t="inlineStr"/>
-      <c r="N42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O42" s="5" t="inlineStr"/>
-      <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R42" s="5" t="inlineStr"/>
-      <c r="S42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T42" s="5" t="inlineStr"/>
-      <c r="U42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>WHITSF1</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7882,68 +4888,14 @@
       <c r="H43" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="I43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R43" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T43" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V43" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>WOOLGSF1</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7966,68 +4918,14 @@
       <c r="H44" s="5" t="n">
         <v>0.0558256772551647</v>
       </c>
-      <c r="I44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Q44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R44" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="S44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T44" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="U44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V44" s="5" t="n">
-        <v>0.04666666666666667</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>YARANSF1</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8050,68 +4948,14 @@
       <c r="H45" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="I45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R45" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T45" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V45" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>CLRKCWF1</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8126,52 +4970,14 @@
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M46" s="5" t="inlineStr"/>
-      <c r="N46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O46" s="5" t="inlineStr"/>
-      <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R46" s="5" t="inlineStr"/>
-      <c r="S46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T46" s="5" t="inlineStr"/>
-      <c r="U46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>CLRKCWF2</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8186,52 +4992,14 @@
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O47" s="5" t="inlineStr"/>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T47" s="5" t="inlineStr"/>
-      <c r="U47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>COOPGWF1</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8250,52 +5018,14 @@
       </c>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr"/>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M48" s="5" t="inlineStr"/>
-      <c r="N48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O48" s="5" t="inlineStr"/>
-      <c r="P48" s="5" t="inlineStr"/>
-      <c r="Q48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R48" s="5" t="inlineStr"/>
-      <c r="S48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T48" s="5" t="inlineStr"/>
-      <c r="U48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>DULAWF1</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8314,52 +5044,14 @@
       </c>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M49" s="5" t="inlineStr"/>
-      <c r="N49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O49" s="5" t="inlineStr"/>
-      <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R49" s="5" t="inlineStr"/>
-      <c r="S49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T49" s="5" t="inlineStr"/>
-      <c r="U49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>KABANWF1</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8378,52 +5070,14 @@
       </c>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M50" s="5" t="inlineStr"/>
-      <c r="N50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O50" s="5" t="inlineStr"/>
-      <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R50" s="5" t="inlineStr"/>
-      <c r="S50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T50" s="5" t="inlineStr"/>
-      <c r="U50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>KEPWF1</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8442,52 +5096,14 @@
       </c>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr"/>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M51" s="5" t="inlineStr"/>
-      <c r="N51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O51" s="5" t="inlineStr"/>
-      <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R51" s="5" t="inlineStr"/>
-      <c r="S51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T51" s="5" t="inlineStr"/>
-      <c r="U51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>MCINTYR1</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8502,52 +5118,14 @@
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr"/>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M52" s="5" t="inlineStr"/>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O52" s="5" t="inlineStr"/>
-      <c r="P52" s="5" t="inlineStr"/>
-      <c r="Q52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R52" s="5" t="inlineStr"/>
-      <c r="S52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T52" s="5" t="inlineStr"/>
-      <c r="U52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>MEWF1</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8566,52 +5144,14 @@
       </c>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr"/>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M53" s="5" t="inlineStr"/>
-      <c r="N53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O53" s="5" t="inlineStr"/>
-      <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R53" s="5" t="inlineStr"/>
-      <c r="S53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T53" s="5" t="inlineStr"/>
-      <c r="U53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>WAMBOWF1</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -8626,107 +5166,49 @@
       <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr"/>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M54" s="5" t="inlineStr"/>
-      <c r="N54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O54" s="5" t="inlineStr"/>
-      <c r="P54" s="5" t="inlineStr"/>
-      <c r="Q54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R54" s="5" t="inlineStr"/>
-      <c r="S54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T54" s="5" t="inlineStr"/>
-      <c r="U54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>WHILL1</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>WAMBOWF2</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
-        <v>1.0128</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>1.013</v>
-      </c>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr"/>
       <c r="E55" s="5" t="inlineStr"/>
       <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr"/>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M55" s="5" t="inlineStr"/>
-      <c r="N55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O55" s="5" t="inlineStr"/>
-      <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R55" s="5" t="inlineStr"/>
-      <c r="S55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T55" s="5" t="inlineStr"/>
-      <c r="U55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>WHILL1</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>1.0128</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C55">
+  <conditionalFormatting sqref="C2:C56">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -8738,7 +5220,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D55">
+  <conditionalFormatting sqref="D2:D56">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -8750,7 +5232,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E55">
+  <conditionalFormatting sqref="E2:E56">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -8762,7 +5244,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F55">
+  <conditionalFormatting sqref="F2:F56">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -8774,7 +5256,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G55">
+  <conditionalFormatting sqref="G2:G56">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -8786,176 +5268,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H55">
+  <conditionalFormatting sqref="H2:H56">
     <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I55">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J55">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K55">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L55">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M55">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N55">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O55">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P55">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q55">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R55">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S55">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T55">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U55">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V55">
-    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,6 +82,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -453,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:W56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,6 +474,14 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -547,6 +558,46 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>FY26-27</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Curt Avg</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Offl Avg</t>
         </is>
       </c>
     </row>
@@ -596,6 +647,14 @@
       <c r="O2" s="5" t="n">
         <v>0.8948</v>
       </c>
+      <c r="P2" s="6" t="inlineStr"/>
+      <c r="Q2" s="6" t="inlineStr"/>
+      <c r="R2" s="6" t="inlineStr"/>
+      <c r="S2" s="6" t="inlineStr"/>
+      <c r="T2" s="6" t="inlineStr"/>
+      <c r="U2" s="6" t="inlineStr"/>
+      <c r="V2" s="6" t="inlineStr"/>
+      <c r="W2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -653,6 +712,14 @@
       <c r="O3" s="5" t="n">
         <v>0.9472</v>
       </c>
+      <c r="P3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr"/>
+      <c r="S3" s="6" t="inlineStr"/>
+      <c r="T3" s="6" t="inlineStr"/>
+      <c r="U3" s="6" t="inlineStr"/>
+      <c r="V3" s="6" t="inlineStr"/>
+      <c r="W3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -700,6 +767,14 @@
       <c r="O4" s="5" t="n">
         <v>0.8878</v>
       </c>
+      <c r="P4" s="6" t="inlineStr"/>
+      <c r="Q4" s="6" t="inlineStr"/>
+      <c r="R4" s="6" t="inlineStr"/>
+      <c r="S4" s="6" t="inlineStr"/>
+      <c r="T4" s="6" t="inlineStr"/>
+      <c r="U4" s="6" t="inlineStr"/>
+      <c r="V4" s="6" t="inlineStr"/>
+      <c r="W4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -760,6 +835,30 @@
       </c>
       <c r="O5" s="5" t="n">
         <v>0.9459</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W5" s="6" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -808,6 +907,14 @@
       <c r="O6" s="5" t="n">
         <v>0.9247</v>
       </c>
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="6" t="inlineStr"/>
+      <c r="R6" s="6" t="inlineStr"/>
+      <c r="S6" s="6" t="inlineStr"/>
+      <c r="T6" s="6" t="inlineStr"/>
+      <c r="U6" s="6" t="inlineStr"/>
+      <c r="V6" s="6" t="inlineStr"/>
+      <c r="W6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -855,6 +962,14 @@
       <c r="O7" s="5" t="n">
         <v>0.9323</v>
       </c>
+      <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="6" t="inlineStr"/>
+      <c r="R7" s="6" t="inlineStr"/>
+      <c r="S7" s="6" t="inlineStr"/>
+      <c r="T7" s="6" t="inlineStr"/>
+      <c r="U7" s="6" t="inlineStr"/>
+      <c r="V7" s="6" t="inlineStr"/>
+      <c r="W7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -916,6 +1031,30 @@
       <c r="O8" s="5" t="n">
         <v>0.9523</v>
       </c>
+      <c r="P8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U8" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="W8" s="6" t="n">
+        <v>0.04666666666666667</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -977,6 +1116,30 @@
       <c r="O9" s="5" t="n">
         <v>0.8572</v>
       </c>
+      <c r="P9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U9" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V9" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W9" s="6" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1038,6 +1201,30 @@
       <c r="O10" s="5" t="n">
         <v>0.8878</v>
       </c>
+      <c r="P10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U10" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V10" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W10" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1098,6 +1285,30 @@
       </c>
       <c r="O11" s="5" t="n">
         <v>0.8731</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U11" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W11" s="6" t="n">
+        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -1158,6 +1369,30 @@
       <c r="O12" s="5" t="n">
         <v>0.9831</v>
       </c>
+      <c r="P12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U12" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V12" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W12" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1219,6 +1454,30 @@
       <c r="O13" s="5" t="n">
         <v>0.981</v>
       </c>
+      <c r="P13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U13" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V13" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W13" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1280,6 +1539,30 @@
       <c r="O14" s="5" t="n">
         <v>0.8758</v>
       </c>
+      <c r="P14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U14" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V14" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W14" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1341,6 +1624,30 @@
       <c r="O15" s="5" t="n">
         <v>0.9797</v>
       </c>
+      <c r="P15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U15" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V15" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W15" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1402,6 +1709,14 @@
       <c r="O16" s="5" t="n">
         <v>0.8854</v>
       </c>
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="6" t="inlineStr"/>
+      <c r="R16" s="6" t="inlineStr"/>
+      <c r="S16" s="6" t="inlineStr"/>
+      <c r="T16" s="6" t="inlineStr"/>
+      <c r="U16" s="6" t="inlineStr"/>
+      <c r="V16" s="6" t="inlineStr"/>
+      <c r="W16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1462,6 +1777,30 @@
       </c>
       <c r="O17" s="5" t="n">
         <v>0.9918</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U17" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V17" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W17" s="6" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -1510,6 +1849,14 @@
       <c r="O18" s="5" t="n">
         <v>0.9827</v>
       </c>
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="6" t="inlineStr"/>
+      <c r="R18" s="6" t="inlineStr"/>
+      <c r="S18" s="6" t="inlineStr"/>
+      <c r="T18" s="6" t="inlineStr"/>
+      <c r="U18" s="6" t="inlineStr"/>
+      <c r="V18" s="6" t="inlineStr"/>
+      <c r="W18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1571,6 +1918,30 @@
       <c r="O19" s="5" t="n">
         <v>0.872</v>
       </c>
+      <c r="P19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U19" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V19" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W19" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1632,6 +2003,30 @@
       <c r="O20" s="5" t="n">
         <v>0.8766</v>
       </c>
+      <c r="P20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U20" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V20" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W20" s="6" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1692,6 +2087,30 @@
       </c>
       <c r="O21" s="5" t="n">
         <v>0.8758</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U21" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V21" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W21" s="6" t="n">
+        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="22">
@@ -1750,6 +2169,14 @@
       <c r="O22" s="5" t="n">
         <v>0.8832</v>
       </c>
+      <c r="P22" s="6" t="inlineStr"/>
+      <c r="Q22" s="6" t="inlineStr"/>
+      <c r="R22" s="6" t="inlineStr"/>
+      <c r="S22" s="6" t="inlineStr"/>
+      <c r="T22" s="6" t="inlineStr"/>
+      <c r="U22" s="6" t="inlineStr"/>
+      <c r="V22" s="6" t="inlineStr"/>
+      <c r="W22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1811,6 +2238,30 @@
       <c r="O23" s="5" t="n">
         <v>0.9574</v>
       </c>
+      <c r="P23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U23" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V23" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W23" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1871,6 +2322,30 @@
       </c>
       <c r="O24" s="5" t="n">
         <v>0.8832</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U24" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V24" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W24" s="6" t="n">
+        <v>0.02666666666666667</v>
       </c>
     </row>
     <row r="25">
@@ -1929,6 +2404,14 @@
       <c r="O25" s="5" t="n">
         <v>0.9791</v>
       </c>
+      <c r="P25" s="6" t="inlineStr"/>
+      <c r="Q25" s="6" t="inlineStr"/>
+      <c r="R25" s="6" t="inlineStr"/>
+      <c r="S25" s="6" t="inlineStr"/>
+      <c r="T25" s="6" t="inlineStr"/>
+      <c r="U25" s="6" t="inlineStr"/>
+      <c r="V25" s="6" t="inlineStr"/>
+      <c r="W25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1989,6 +2472,30 @@
       </c>
       <c r="O26" s="5" t="n">
         <v>0.8824</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U26" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V26" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W26" s="6" t="n">
+        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -2047,6 +2554,14 @@
       <c r="O27" s="5" t="n">
         <v>0.8878</v>
       </c>
+      <c r="P27" s="6" t="inlineStr"/>
+      <c r="Q27" s="6" t="inlineStr"/>
+      <c r="R27" s="6" t="inlineStr"/>
+      <c r="S27" s="6" t="inlineStr"/>
+      <c r="T27" s="6" t="inlineStr"/>
+      <c r="U27" s="6" t="inlineStr"/>
+      <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2107,6 +2622,30 @@
       </c>
       <c r="O28" s="5" t="n">
         <v>0.987</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U28" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V28" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W28" s="6" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="29">
@@ -2159,6 +2698,14 @@
       <c r="O29" s="5" t="n">
         <v>0.8854</v>
       </c>
+      <c r="P29" s="6" t="inlineStr"/>
+      <c r="Q29" s="6" t="inlineStr"/>
+      <c r="R29" s="6" t="inlineStr"/>
+      <c r="S29" s="6" t="inlineStr"/>
+      <c r="T29" s="6" t="inlineStr"/>
+      <c r="U29" s="6" t="inlineStr"/>
+      <c r="V29" s="6" t="inlineStr"/>
+      <c r="W29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2219,6 +2766,30 @@
       </c>
       <c r="O30" s="5" t="n">
         <v>0.885</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U30" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V30" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W30" s="6" t="n">
+        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="31">
@@ -2267,6 +2838,14 @@
       <c r="O31" s="5" t="n">
         <v>0.9579</v>
       </c>
+      <c r="P31" s="6" t="inlineStr"/>
+      <c r="Q31" s="6" t="inlineStr"/>
+      <c r="R31" s="6" t="inlineStr"/>
+      <c r="S31" s="6" t="inlineStr"/>
+      <c r="T31" s="6" t="inlineStr"/>
+      <c r="U31" s="6" t="inlineStr"/>
+      <c r="V31" s="6" t="inlineStr"/>
+      <c r="W31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2328,6 +2907,30 @@
       <c r="O32" s="5" t="n">
         <v>0.9856</v>
       </c>
+      <c r="P32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U32" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V32" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W32" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2389,6 +2992,30 @@
       <c r="O33" s="5" t="n">
         <v>0.9856</v>
       </c>
+      <c r="P33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U33" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V33" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W33" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2450,6 +3077,30 @@
       <c r="O34" s="5" t="n">
         <v>0.8832</v>
       </c>
+      <c r="P34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U34" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V34" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W34" s="6" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2511,6 +3162,30 @@
       <c r="O35" s="5" t="n">
         <v>0.8932</v>
       </c>
+      <c r="P35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U35" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V35" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W35" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2572,6 +3247,30 @@
       <c r="O36" s="5" t="n">
         <v>1.0179</v>
       </c>
+      <c r="P36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U36" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V36" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W36" s="6" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2632,6 +3331,30 @@
       </c>
       <c r="O37" s="5" t="n">
         <v>0.9523</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U37" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V37" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="W37" s="6" t="n">
+        <v>0.04666666666666667</v>
       </c>
     </row>
     <row r="38">
@@ -2690,6 +3413,14 @@
       <c r="O38" s="5" t="n">
         <v>1.0132</v>
       </c>
+      <c r="P38" s="6" t="inlineStr"/>
+      <c r="Q38" s="6" t="inlineStr"/>
+      <c r="R38" s="6" t="inlineStr"/>
+      <c r="S38" s="6" t="inlineStr"/>
+      <c r="T38" s="6" t="inlineStr"/>
+      <c r="U38" s="6" t="inlineStr"/>
+      <c r="V38" s="6" t="inlineStr"/>
+      <c r="W38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2751,6 +3482,30 @@
       <c r="O39" s="5" t="n">
         <v>0.9903999999999999</v>
       </c>
+      <c r="P39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U39" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V39" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W39" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2812,6 +3567,30 @@
       <c r="O40" s="5" t="n">
         <v>0.987</v>
       </c>
+      <c r="P40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U40" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V40" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W40" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2872,6 +3651,30 @@
       </c>
       <c r="O41" s="5" t="n">
         <v>0.987</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U41" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V41" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W41" s="6" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="42">
@@ -2924,6 +3727,14 @@
       <c r="O42" s="5" t="n">
         <v>0.9761</v>
       </c>
+      <c r="P42" s="6" t="inlineStr"/>
+      <c r="Q42" s="6" t="inlineStr"/>
+      <c r="R42" s="6" t="inlineStr"/>
+      <c r="S42" s="6" t="inlineStr"/>
+      <c r="T42" s="6" t="inlineStr"/>
+      <c r="U42" s="6" t="inlineStr"/>
+      <c r="V42" s="6" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2985,6 +3796,30 @@
       <c r="O43" s="5" t="n">
         <v>0.8736</v>
       </c>
+      <c r="P43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U43" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V43" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W43" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3046,6 +3881,30 @@
       <c r="O44" s="5" t="n">
         <v>0.9568</v>
       </c>
+      <c r="P44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U44" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V44" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="W44" s="6" t="n">
+        <v>0.04666666666666667</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3106,6 +3965,30 @@
       </c>
       <c r="O45" s="5" t="n">
         <v>0.987</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U45" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V45" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W45" s="6" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="46">
@@ -3154,6 +4037,14 @@
       <c r="O46" s="5" t="n">
         <v>0.9313</v>
       </c>
+      <c r="P46" s="6" t="inlineStr"/>
+      <c r="Q46" s="6" t="inlineStr"/>
+      <c r="R46" s="6" t="inlineStr"/>
+      <c r="S46" s="6" t="inlineStr"/>
+      <c r="T46" s="6" t="inlineStr"/>
+      <c r="U46" s="6" t="inlineStr"/>
+      <c r="V46" s="6" t="inlineStr"/>
+      <c r="W46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3201,6 +4092,14 @@
       <c r="O47" s="5" t="n">
         <v>0.9313</v>
       </c>
+      <c r="P47" s="6" t="inlineStr"/>
+      <c r="Q47" s="6" t="inlineStr"/>
+      <c r="R47" s="6" t="inlineStr"/>
+      <c r="S47" s="6" t="inlineStr"/>
+      <c r="T47" s="6" t="inlineStr"/>
+      <c r="U47" s="6" t="inlineStr"/>
+      <c r="V47" s="6" t="inlineStr"/>
+      <c r="W47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3252,6 +4151,14 @@
       <c r="O48" s="5" t="n">
         <v>0.9704</v>
       </c>
+      <c r="P48" s="6" t="inlineStr"/>
+      <c r="Q48" s="6" t="inlineStr"/>
+      <c r="R48" s="6" t="inlineStr"/>
+      <c r="S48" s="6" t="inlineStr"/>
+      <c r="T48" s="6" t="inlineStr"/>
+      <c r="U48" s="6" t="inlineStr"/>
+      <c r="V48" s="6" t="inlineStr"/>
+      <c r="W48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3303,6 +4210,14 @@
       <c r="O49" s="5" t="n">
         <v>0.987</v>
       </c>
+      <c r="P49" s="6" t="inlineStr"/>
+      <c r="Q49" s="6" t="inlineStr"/>
+      <c r="R49" s="6" t="inlineStr"/>
+      <c r="S49" s="6" t="inlineStr"/>
+      <c r="T49" s="6" t="inlineStr"/>
+      <c r="U49" s="6" t="inlineStr"/>
+      <c r="V49" s="6" t="inlineStr"/>
+      <c r="W49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3354,6 +4269,14 @@
       <c r="O50" s="5" t="n">
         <v>0.9442</v>
       </c>
+      <c r="P50" s="6" t="inlineStr"/>
+      <c r="Q50" s="6" t="inlineStr"/>
+      <c r="R50" s="6" t="inlineStr"/>
+      <c r="S50" s="6" t="inlineStr"/>
+      <c r="T50" s="6" t="inlineStr"/>
+      <c r="U50" s="6" t="inlineStr"/>
+      <c r="V50" s="6" t="inlineStr"/>
+      <c r="W50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3405,6 +4328,14 @@
       <c r="O51" s="5" t="n">
         <v>0.9574</v>
       </c>
+      <c r="P51" s="6" t="inlineStr"/>
+      <c r="Q51" s="6" t="inlineStr"/>
+      <c r="R51" s="6" t="inlineStr"/>
+      <c r="S51" s="6" t="inlineStr"/>
+      <c r="T51" s="6" t="inlineStr"/>
+      <c r="U51" s="6" t="inlineStr"/>
+      <c r="V51" s="6" t="inlineStr"/>
+      <c r="W51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3452,6 +4383,14 @@
       <c r="O52" s="5" t="n">
         <v>0.9729</v>
       </c>
+      <c r="P52" s="6" t="inlineStr"/>
+      <c r="Q52" s="6" t="inlineStr"/>
+      <c r="R52" s="6" t="inlineStr"/>
+      <c r="S52" s="6" t="inlineStr"/>
+      <c r="T52" s="6" t="inlineStr"/>
+      <c r="U52" s="6" t="inlineStr"/>
+      <c r="V52" s="6" t="inlineStr"/>
+      <c r="W52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3503,6 +4442,14 @@
       <c r="O53" s="5" t="n">
         <v>0.9396</v>
       </c>
+      <c r="P53" s="6" t="inlineStr"/>
+      <c r="Q53" s="6" t="inlineStr"/>
+      <c r="R53" s="6" t="inlineStr"/>
+      <c r="S53" s="6" t="inlineStr"/>
+      <c r="T53" s="6" t="inlineStr"/>
+      <c r="U53" s="6" t="inlineStr"/>
+      <c r="V53" s="6" t="inlineStr"/>
+      <c r="W53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3550,6 +4497,14 @@
       <c r="O54" s="5" t="n">
         <v>0.9701</v>
       </c>
+      <c r="P54" s="6" t="inlineStr"/>
+      <c r="Q54" s="6" t="inlineStr"/>
+      <c r="R54" s="6" t="inlineStr"/>
+      <c r="S54" s="6" t="inlineStr"/>
+      <c r="T54" s="6" t="inlineStr"/>
+      <c r="U54" s="6" t="inlineStr"/>
+      <c r="V54" s="6" t="inlineStr"/>
+      <c r="W54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3593,6 +4548,14 @@
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="inlineStr"/>
       <c r="O55" s="5" t="inlineStr"/>
+      <c r="P55" s="6" t="inlineStr"/>
+      <c r="Q55" s="6" t="inlineStr"/>
+      <c r="R55" s="6" t="inlineStr"/>
+      <c r="S55" s="6" t="inlineStr"/>
+      <c r="T55" s="6" t="inlineStr"/>
+      <c r="U55" s="6" t="inlineStr"/>
+      <c r="V55" s="6" t="inlineStr"/>
+      <c r="W55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3640,6 +4603,14 @@
       <c r="O56" s="5" t="n">
         <v>1.013</v>
       </c>
+      <c r="P56" s="6" t="inlineStr"/>
+      <c r="Q56" s="6" t="inlineStr"/>
+      <c r="R56" s="6" t="inlineStr"/>
+      <c r="S56" s="6" t="inlineStr"/>
+      <c r="T56" s="6" t="inlineStr"/>
+      <c r="U56" s="6" t="inlineStr"/>
+      <c r="V56" s="6" t="inlineStr"/>
+      <c r="W56" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3652,7 +4623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3663,57 +4634,141 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY26-27</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_AVG</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3</t>
+        </is>
+      </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_AVG</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>ALDGASF1</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3728,14 +4783,52 @@
       <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>BAKING1</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3754,14 +4847,52 @@
       <c r="H3" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>BARCSF1</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3776,14 +4907,52 @@
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>BLUEGSF1</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3806,14 +4975,68 @@
       <c r="H5" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>BRDDSF01</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3828,14 +5051,52 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>BUSF1</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3850,14 +5111,52 @@
       <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>CHILDSF1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3880,14 +5179,68 @@
       <c r="H8" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="n">
+        <v>0.04666666666666667</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>CLARESF1</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3910,14 +5263,68 @@
       <c r="H9" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>CLERMSF1</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3940,14 +5347,68 @@
       <c r="H10" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>CSPVPS1</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3970,14 +5431,68 @@
       <c r="H11" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
+      <c r="I11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>COLUMSF1</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3998,14 +5513,68 @@
       <c r="H12" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>DDSF1</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4028,14 +5597,68 @@
       <c r="H13" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
+      <c r="I13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>DAYDSF1</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4058,14 +5681,68 @@
       <c r="H14" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
+      <c r="I14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>EDENVSF1</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4088,14 +5765,68 @@
       <c r="H15" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
+      <c r="I15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>EMERASF1</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4118,14 +5849,52 @@
       <c r="H16" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr"/>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr"/>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>GANGARR1</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4148,14 +5917,68 @@
       <c r="H17" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>GUSF1</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4170,14 +5993,52 @@
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr"/>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr"/>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>HAMISF1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4200,14 +6061,68 @@
       <c r="H19" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
+      <c r="I19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>HAUGHT11</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4230,14 +6145,68 @@
       <c r="H20" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>HAYMSF1</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4260,14 +6229,68 @@
       <c r="H21" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
+      <c r="I21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>HUGSF1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4286,14 +6309,52 @@
       <c r="H22" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr"/>
+      <c r="S22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr"/>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>KEPSF1</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4316,14 +6377,68 @@
       <c r="H23" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
+      <c r="I23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>KSP1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4346,14 +6461,68 @@
       <c r="H24" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
+      <c r="I24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>KINGASF1</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4372,14 +6541,52 @@
       <c r="H25" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr"/>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>LILYSF1</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4402,14 +6609,68 @@
       <c r="H26" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
+      <c r="I26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V26" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>LRSF1</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4428,14 +6689,52 @@
       <c r="H27" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr"/>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>MARYRSF1</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4458,14 +6757,68 @@
       <c r="H28" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
+      <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V28" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>MIDDLSF1</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4484,14 +6837,52 @@
       </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="inlineStr"/>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>MOUSF1</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4514,14 +6905,68 @@
       <c r="H30" s="5" t="n">
         <v>0.0509815379375577</v>
       </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>MUCRKSF1</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4536,14 +6981,52 @@
       <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="inlineStr"/>
+      <c r="S31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T31" s="5" t="inlineStr"/>
+      <c r="U31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>OAKEY1SF</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4566,14 +7049,68 @@
       <c r="H32" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>OAKEY2SF</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4596,14 +7133,68 @@
       <c r="H33" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
+      <c r="I33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>RRSF1</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4626,14 +7217,68 @@
       <c r="H34" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>RUGBYR1</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4656,14 +7301,68 @@
       <c r="H35" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
+      <c r="I35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>SMCSF1</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4686,14 +7385,68 @@
       <c r="H36" s="5" t="n">
         <v>0.0509806543175163</v>
       </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>SRSF1</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4716,14 +7469,68 @@
       <c r="H37" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
+      <c r="I37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T37" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V37" s="5" t="n">
+        <v>0.04666666666666667</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>VALDORA1</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4742,14 +7549,52 @@
       <c r="H38" s="5" t="n">
         <v>0.0593284659737539</v>
       </c>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr"/>
+      <c r="P38" s="5" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="inlineStr"/>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T38" s="5" t="inlineStr"/>
+      <c r="U38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>WANDSF1</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4772,14 +7617,68 @@
       <c r="H39" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
+      <c r="I39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T39" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>WARWSF1</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4802,14 +7701,68 @@
       <c r="H40" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V40" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>WARWSF2</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4832,14 +7785,68 @@
       <c r="H41" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
+      <c r="I41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T41" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>WDGPH1</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4858,14 +7865,52 @@
       </c>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr"/>
+      <c r="P42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="inlineStr"/>
+      <c r="S42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T42" s="5" t="inlineStr"/>
+      <c r="U42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>WHITSF1</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4888,14 +7933,68 @@
       <c r="H43" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
+      <c r="I43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T43" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V43" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>WOOLGSF1</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4918,14 +8017,68 @@
       <c r="H44" s="5" t="n">
         <v>0.0558256772551647</v>
       </c>
+      <c r="I44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="n">
+        <v>0.04666666666666667</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>YARANSF1</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4948,14 +8101,68 @@
       <c r="H45" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
+      <c r="I45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T45" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V45" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>CLRKCWF1</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4970,14 +8177,52 @@
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr"/>
+      <c r="P46" s="5" t="inlineStr"/>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="inlineStr"/>
+      <c r="S46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T46" s="5" t="inlineStr"/>
+      <c r="U46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>CLRKCWF2</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4992,14 +8237,52 @@
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr"/>
+      <c r="P47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="inlineStr"/>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T47" s="5" t="inlineStr"/>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>COOPGWF1</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5018,14 +8301,52 @@
       </c>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr"/>
+      <c r="P48" s="5" t="inlineStr"/>
+      <c r="Q48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R48" s="5" t="inlineStr"/>
+      <c r="S48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T48" s="5" t="inlineStr"/>
+      <c r="U48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>DULAWF1</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5044,14 +8365,52 @@
       </c>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr"/>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr"/>
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="inlineStr"/>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T49" s="5" t="inlineStr"/>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>KABANWF1</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5070,14 +8429,52 @@
       </c>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr"/>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr"/>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr"/>
+      <c r="P50" s="5" t="inlineStr"/>
+      <c r="Q50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="inlineStr"/>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T50" s="5" t="inlineStr"/>
+      <c r="U50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>KEPWF1</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5096,14 +8493,52 @@
       </c>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr"/>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr"/>
+      <c r="P51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R51" s="5" t="inlineStr"/>
+      <c r="S51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T51" s="5" t="inlineStr"/>
+      <c r="U51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>MCINTYR1</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5118,14 +8553,52 @@
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr"/>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr"/>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr"/>
+      <c r="P52" s="5" t="inlineStr"/>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="inlineStr"/>
+      <c r="S52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T52" s="5" t="inlineStr"/>
+      <c r="U52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>MEWF1</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5144,14 +8617,52 @@
       </c>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr"/>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr"/>
+      <c r="P53" s="5" t="inlineStr"/>
+      <c r="Q53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R53" s="5" t="inlineStr"/>
+      <c r="S53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T53" s="5" t="inlineStr"/>
+      <c r="U53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>WAMBOWF1</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5166,14 +8677,52 @@
       <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr"/>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="inlineStr"/>
+      <c r="P54" s="5" t="inlineStr"/>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="inlineStr"/>
+      <c r="S54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T54" s="5" t="inlineStr"/>
+      <c r="U54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>WAMBOWF2</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5184,14 +8733,52 @@
       <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr"/>
+      <c r="P55" s="5" t="inlineStr"/>
+      <c r="Q55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R55" s="5" t="inlineStr"/>
+      <c r="S55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T55" s="5" t="inlineStr"/>
+      <c r="U55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>WHILL1</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5206,6 +8793,44 @@
       <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr"/>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr"/>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="inlineStr"/>
+      <c r="P56" s="5" t="inlineStr"/>
+      <c r="Q56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R56" s="5" t="inlineStr"/>
+      <c r="S56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T56" s="5" t="inlineStr"/>
+      <c r="U56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V56" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C56">
@@ -5280,6 +8905,174 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I56">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J56">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K56">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L56">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M56">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N56">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O56">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P56">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q56">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R56">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S56">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T56">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U56">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V56">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -532,12 +532,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Actual FY23-24</t>
+          <t>Actual FY24-25</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Actual FY24-25</t>
+          <t>Actual FY25-26</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -819,11 +819,9 @@
         <v>132</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.0523</v>
-      </c>
-      <c r="K5" s="5" t="n">
         <v>0.0221</v>
       </c>
+      <c r="K5" s="5" t="inlineStr"/>
       <c r="L5" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
@@ -1014,11 +1012,9 @@
         <v>132</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="K8" s="5" t="n">
         <v>0.1154</v>
       </c>
+      <c r="K8" s="5" t="inlineStr"/>
       <c r="L8" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
@@ -1099,11 +1095,9 @@
         <v>132</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.2171</v>
-      </c>
-      <c r="K9" s="5" t="n">
         <v>0.1651</v>
       </c>
+      <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -1184,11 +1178,9 @@
         <v>132</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.0251</v>
-      </c>
-      <c r="K10" s="5" t="n">
         <v>0.0201</v>
       </c>
+      <c r="K10" s="5" t="inlineStr"/>
       <c r="L10" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -1269,11 +1261,9 @@
         <v>33</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="K11" s="5" t="n">
         <v>0.0057</v>
       </c>
+      <c r="K11" s="5" t="inlineStr"/>
       <c r="L11" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -1353,10 +1343,10 @@
       <c r="I12" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="n">
+      <c r="J12" s="5" t="n">
         <v>0.0264</v>
       </c>
+      <c r="K12" s="5" t="inlineStr"/>
       <c r="L12" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
@@ -1437,11 +1427,9 @@
         <v>275</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.0047</v>
-      </c>
-      <c r="K13" s="5" t="n">
         <v>0.009900000000000001</v>
       </c>
+      <c r="K13" s="5" t="inlineStr"/>
       <c r="L13" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
@@ -1522,11 +1510,9 @@
         <v>33</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="K14" s="5" t="n">
         <v>0.0375</v>
       </c>
+      <c r="K14" s="5" t="inlineStr"/>
       <c r="L14" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -1607,11 +1593,9 @@
         <v>275</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.0135</v>
-      </c>
-      <c r="K15" s="5" t="n">
         <v>0.053</v>
       </c>
+      <c r="K15" s="5" t="inlineStr"/>
       <c r="L15" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
@@ -1692,11 +1676,9 @@
         <v>66</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.3012</v>
-      </c>
-      <c r="K16" s="5" t="n">
         <v>0.004</v>
       </c>
+      <c r="K16" s="5" t="inlineStr"/>
       <c r="L16" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -1761,11 +1743,9 @@
         <v>132</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.0217</v>
-      </c>
-      <c r="K17" s="5" t="n">
         <v>0.1852</v>
       </c>
+      <c r="K17" s="5" t="inlineStr"/>
       <c r="L17" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
@@ -1901,11 +1881,9 @@
         <v>33</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="K19" s="5" t="n">
         <v>0.0682</v>
       </c>
+      <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -1986,11 +1964,9 @@
         <v>275</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.1235</v>
-      </c>
-      <c r="K20" s="5" t="n">
         <v>0.0743</v>
       </c>
+      <c r="K20" s="5" t="inlineStr"/>
       <c r="L20" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -2071,11 +2047,9 @@
         <v>33</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.07969999999999999</v>
-      </c>
-      <c r="K21" s="5" t="n">
         <v>0.1862</v>
       </c>
+      <c r="K21" s="5" t="inlineStr"/>
       <c r="L21" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -2221,11 +2195,9 @@
         <v>132</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.1091</v>
-      </c>
-      <c r="K23" s="5" t="n">
         <v>0.0888</v>
       </c>
+      <c r="K23" s="5" t="inlineStr"/>
       <c r="L23" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -2306,11 +2278,9 @@
         <v>132</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="K24" s="5" t="n">
         <v>0.1948</v>
       </c>
+      <c r="K24" s="5" t="inlineStr"/>
       <c r="L24" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -2456,11 +2426,9 @@
         <v>33</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>0.0851</v>
-      </c>
-      <c r="K26" s="5" t="n">
         <v>0.0726</v>
       </c>
+      <c r="K26" s="5" t="inlineStr"/>
       <c r="L26" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -2606,11 +2574,9 @@
         <v>110</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="K28" s="5" t="n">
         <v>0.1106</v>
       </c>
+      <c r="K28" s="5" t="inlineStr"/>
       <c r="L28" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -2685,11 +2651,9 @@
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="K29" s="5" t="n">
         <v>0.0506</v>
       </c>
+      <c r="K29" s="5" t="inlineStr"/>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="n">
@@ -2750,11 +2714,9 @@
         <v>132</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="K30" s="5" t="n">
         <v>0.007900000000000001</v>
       </c>
+      <c r="K30" s="5" t="inlineStr"/>
       <c r="L30" s="5" t="n">
         <v>0.216663358752891</v>
       </c>
@@ -2890,11 +2852,9 @@
         <v>110</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>0.1688</v>
-      </c>
-      <c r="K32" s="5" t="n">
         <v>0.3056</v>
       </c>
+      <c r="K32" s="5" t="inlineStr"/>
       <c r="L32" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -2975,11 +2935,9 @@
         <v>110</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>0.1152</v>
-      </c>
-      <c r="K33" s="5" t="n">
         <v>0.0897</v>
       </c>
+      <c r="K33" s="5" t="inlineStr"/>
       <c r="L33" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -3060,11 +3018,9 @@
         <v>132</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>0.0094</v>
-      </c>
-      <c r="K34" s="5" t="n">
         <v>0.0113</v>
       </c>
+      <c r="K34" s="5" t="inlineStr"/>
       <c r="L34" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -3145,11 +3101,9 @@
         <v>132</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="K35" s="5" t="n">
         <v>0.07539999999999999</v>
       </c>
+      <c r="K35" s="5" t="inlineStr"/>
       <c r="L35" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -3230,11 +3184,9 @@
         <v>132</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>0.0197</v>
-      </c>
-      <c r="K36" s="5" t="n">
         <v>0.0959</v>
       </c>
+      <c r="K36" s="5" t="inlineStr"/>
       <c r="L36" s="5" t="n">
         <v>0.219325121104852</v>
       </c>
@@ -3315,11 +3267,9 @@
         <v>132</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K37" s="5" t="n">
         <v>0.1111</v>
       </c>
+      <c r="K37" s="5" t="inlineStr"/>
       <c r="L37" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
@@ -3465,11 +3415,9 @@
         <v>275</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>0.0743</v>
-      </c>
-      <c r="K39" s="5" t="n">
         <v>0.1905</v>
       </c>
+      <c r="K39" s="5" t="inlineStr"/>
       <c r="L39" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
@@ -3550,11 +3498,9 @@
         <v>110</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="K40" s="5" t="n">
         <v>0.3423</v>
       </c>
+      <c r="K40" s="5" t="inlineStr"/>
       <c r="L40" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -3635,11 +3581,9 @@
         <v>110</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>0.2443</v>
-      </c>
-      <c r="K41" s="5" t="n">
         <v>0.3471</v>
       </c>
+      <c r="K41" s="5" t="inlineStr"/>
       <c r="L41" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -3714,11 +3658,9 @@
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="5" t="n">
-        <v>0.1857</v>
-      </c>
-      <c r="K42" s="5" t="n">
         <v>0.1226</v>
       </c>
+      <c r="K42" s="5" t="inlineStr"/>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
       <c r="N42" s="5" t="n">
@@ -3779,11 +3721,9 @@
         <v>33</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="K43" s="5" t="n">
         <v>0.2744</v>
       </c>
+      <c r="K43" s="5" t="inlineStr"/>
       <c r="L43" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -3864,11 +3804,9 @@
         <v>132</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K44" s="5" t="n">
         <v>0.1592</v>
       </c>
+      <c r="K44" s="5" t="inlineStr"/>
       <c r="L44" s="5" t="n">
         <v>0.23173278497921</v>
       </c>
@@ -3949,11 +3887,9 @@
         <v>110</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>0.0401</v>
-      </c>
-      <c r="K45" s="5" t="n">
         <v>0.1286</v>
       </c>
+      <c r="K45" s="5" t="inlineStr"/>
       <c r="L45" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -4138,11 +4074,9 @@
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="5" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="K48" s="5" t="n">
         <v>0.029</v>
       </c>
+      <c r="K48" s="5" t="inlineStr"/>
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr"/>
       <c r="N48" s="5" t="n">
@@ -4197,11 +4131,9 @@
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="5" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="K49" s="5" t="n">
         <v>0.0032</v>
       </c>
+      <c r="K49" s="5" t="inlineStr"/>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
       <c r="N49" s="5" t="n">
@@ -4256,11 +4188,9 @@
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="5" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="K50" s="5" t="n">
         <v>0.0136</v>
       </c>
+      <c r="K50" s="5" t="inlineStr"/>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
       <c r="N50" s="5" t="n">
@@ -4315,11 +4245,9 @@
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="5" t="n">
-        <v>0.0103</v>
-      </c>
-      <c r="K51" s="5" t="n">
         <v>0.0236</v>
       </c>
+      <c r="K51" s="5" t="inlineStr"/>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
       <c r="N51" s="5" t="n">
@@ -4429,11 +4357,9 @@
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="5" t="n">
-        <v>0.0247</v>
-      </c>
-      <c r="K53" s="5" t="n">
         <v>0.0396</v>
       </c>
+      <c r="K53" s="5" t="inlineStr"/>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
       <c r="N53" s="5" t="n">
@@ -4673,12 +4599,12 @@
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY23-24</t>
+          <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY24-25</t>
+          <t>CURTAILMENT_ACTUAL_FY25-26</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
@@ -4964,11 +4890,9 @@
         <v>0.9459</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.0523</v>
-      </c>
-      <c r="F5" s="5" t="n">
         <v>0.0221</v>
       </c>
+      <c r="F5" s="5" t="inlineStr"/>
       <c r="G5" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
@@ -5168,11 +5092,9 @@
         <v>0.9523</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="F8" s="5" t="n">
         <v>0.1154</v>
       </c>
+      <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
@@ -5252,11 +5174,9 @@
         <v>0.8572</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.2171</v>
-      </c>
-      <c r="F9" s="5" t="n">
         <v>0.1651</v>
       </c>
+      <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -5336,11 +5256,9 @@
         <v>0.8878</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.0251</v>
-      </c>
-      <c r="F10" s="5" t="n">
         <v>0.0201</v>
       </c>
+      <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -5420,11 +5338,9 @@
         <v>0.8731</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="F11" s="5" t="n">
         <v>0.0057</v>
       </c>
+      <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -5503,10 +5419,10 @@
       <c r="D12" s="5" t="n">
         <v>0.9831</v>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="n">
+      <c r="E12" s="5" t="n">
         <v>0.0264</v>
       </c>
+      <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
@@ -5586,11 +5502,9 @@
         <v>0.981</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.0047</v>
-      </c>
-      <c r="F13" s="5" t="n">
         <v>0.009900000000000001</v>
       </c>
+      <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
@@ -5670,11 +5584,9 @@
         <v>0.8758</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="F14" s="5" t="n">
         <v>0.0375</v>
       </c>
+      <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -5754,11 +5666,9 @@
         <v>0.9797</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.0135</v>
-      </c>
-      <c r="F15" s="5" t="n">
         <v>0.053</v>
       </c>
+      <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
@@ -5838,11 +5748,9 @@
         <v>0.8854</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.3012</v>
-      </c>
-      <c r="F16" s="5" t="n">
         <v>0.004</v>
       </c>
+      <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -5906,11 +5814,9 @@
         <v>0.9918</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.0217</v>
-      </c>
-      <c r="F17" s="5" t="n">
         <v>0.1852</v>
       </c>
+      <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
@@ -6050,11 +5956,9 @@
         <v>0.872</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="F19" s="5" t="n">
         <v>0.0682</v>
       </c>
+      <c r="F19" s="5" t="inlineStr"/>
       <c r="G19" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -6134,11 +6038,9 @@
         <v>0.8766</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.1235</v>
-      </c>
-      <c r="F20" s="5" t="n">
         <v>0.0743</v>
       </c>
+      <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -6218,11 +6120,9 @@
         <v>0.8758</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.07969999999999999</v>
-      </c>
-      <c r="F21" s="5" t="n">
         <v>0.1862</v>
       </c>
+      <c r="F21" s="5" t="inlineStr"/>
       <c r="G21" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -6366,11 +6266,9 @@
         <v>0.9574</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.1091</v>
-      </c>
-      <c r="F23" s="5" t="n">
         <v>0.0888</v>
       </c>
+      <c r="F23" s="5" t="inlineStr"/>
       <c r="G23" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -6450,11 +6348,9 @@
         <v>0.8832</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="F24" s="5" t="n">
         <v>0.1948</v>
       </c>
+      <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -6598,11 +6494,9 @@
         <v>0.8824</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.0851</v>
-      </c>
-      <c r="F26" s="5" t="n">
         <v>0.0726</v>
       </c>
+      <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -6746,11 +6640,9 @@
         <v>0.987</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="F28" s="5" t="n">
         <v>0.1106</v>
       </c>
+      <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -6830,11 +6722,9 @@
         <v>0.8854</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="F29" s="5" t="n">
         <v>0.0506</v>
       </c>
+      <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
@@ -6894,11 +6784,9 @@
         <v>0.885</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="F30" s="5" t="n">
         <v>0.007900000000000001</v>
       </c>
+      <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="n">
         <v>0.216663358752891</v>
       </c>
@@ -7038,11 +6926,9 @@
         <v>0.9856</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.1688</v>
-      </c>
-      <c r="F32" s="5" t="n">
         <v>0.3056</v>
       </c>
+      <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -7122,11 +7008,9 @@
         <v>0.9856</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.1152</v>
-      </c>
-      <c r="F33" s="5" t="n">
         <v>0.0897</v>
       </c>
+      <c r="F33" s="5" t="inlineStr"/>
       <c r="G33" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -7206,11 +7090,9 @@
         <v>0.8832</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.0094</v>
-      </c>
-      <c r="F34" s="5" t="n">
         <v>0.0113</v>
       </c>
+      <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -7290,11 +7172,9 @@
         <v>0.8932</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="F35" s="5" t="n">
         <v>0.07539999999999999</v>
       </c>
+      <c r="F35" s="5" t="inlineStr"/>
       <c r="G35" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -7374,11 +7254,9 @@
         <v>1.0179</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.0197</v>
-      </c>
-      <c r="F36" s="5" t="n">
         <v>0.0959</v>
       </c>
+      <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="n">
         <v>0.219325121104852</v>
       </c>
@@ -7458,11 +7336,9 @@
         <v>0.9523</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="F37" s="5" t="n">
         <v>0.1111</v>
       </c>
+      <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
@@ -7606,11 +7482,9 @@
         <v>0.9903999999999999</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.0743</v>
-      </c>
-      <c r="F39" s="5" t="n">
         <v>0.1905</v>
       </c>
+      <c r="F39" s="5" t="inlineStr"/>
       <c r="G39" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
@@ -7690,11 +7564,9 @@
         <v>0.987</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="F40" s="5" t="n">
         <v>0.3423</v>
       </c>
+      <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -7774,11 +7646,9 @@
         <v>0.987</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.2443</v>
-      </c>
-      <c r="F41" s="5" t="n">
         <v>0.3471</v>
       </c>
+      <c r="F41" s="5" t="inlineStr"/>
       <c r="G41" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -7858,11 +7728,9 @@
         <v>0.9761</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.1857</v>
-      </c>
-      <c r="F42" s="5" t="n">
         <v>0.1226</v>
       </c>
+      <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
@@ -7922,11 +7790,9 @@
         <v>0.8736</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="F43" s="5" t="n">
         <v>0.2744</v>
       </c>
+      <c r="F43" s="5" t="inlineStr"/>
       <c r="G43" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -8006,11 +7872,9 @@
         <v>0.9568</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F44" s="5" t="n">
         <v>0.1592</v>
       </c>
+      <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="5" t="n">
         <v>0.23173278497921</v>
       </c>
@@ -8090,11 +7954,9 @@
         <v>0.987</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.0401</v>
-      </c>
-      <c r="F45" s="5" t="n">
         <v>0.1286</v>
       </c>
+      <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -8294,11 +8156,9 @@
         <v>0.9704</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="F48" s="5" t="n">
         <v>0.029</v>
       </c>
+      <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
@@ -8358,11 +8218,9 @@
         <v>0.987</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="F49" s="5" t="n">
         <v>0.0032</v>
       </c>
+      <c r="F49" s="5" t="inlineStr"/>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
@@ -8422,11 +8280,9 @@
         <v>0.9442</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="F50" s="5" t="n">
         <v>0.0136</v>
       </c>
+      <c r="F50" s="5" t="inlineStr"/>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
@@ -8486,11 +8342,9 @@
         <v>0.9574</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.0103</v>
-      </c>
-      <c r="F51" s="5" t="n">
         <v>0.0236</v>
       </c>
+      <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
@@ -8610,11 +8464,9 @@
         <v>0.9396</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.0247</v>
-      </c>
-      <c r="F53" s="5" t="n">
         <v>0.0396</v>
       </c>
+      <c r="F53" s="5" t="inlineStr"/>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>

--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -638,7 +638,9 @@
       </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="n">
+        <v>0.1085</v>
+      </c>
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
       <c r="N2" s="5" t="n">
@@ -821,7 +823,9 @@
       <c r="J5" s="5" t="n">
         <v>0.0221</v>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="n">
+        <v>0.0123</v>
+      </c>
       <c r="L5" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
@@ -1014,7 +1018,9 @@
       <c r="J8" s="5" t="n">
         <v>0.1154</v>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="n">
+        <v>0.247</v>
+      </c>
       <c r="L8" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
@@ -1097,7 +1103,9 @@
       <c r="J9" s="5" t="n">
         <v>0.1651</v>
       </c>
-      <c r="K9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="n">
+        <v>0.246</v>
+      </c>
       <c r="L9" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -1180,7 +1188,9 @@
       <c r="J10" s="5" t="n">
         <v>0.0201</v>
       </c>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="n">
+        <v>0.0699</v>
+      </c>
       <c r="L10" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -1263,7 +1273,9 @@
       <c r="J11" s="5" t="n">
         <v>0.0057</v>
       </c>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="n">
+        <v>0.0349</v>
+      </c>
       <c r="L11" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -1346,7 +1358,9 @@
       <c r="J12" s="5" t="n">
         <v>0.0264</v>
       </c>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="n">
+        <v>0.0025</v>
+      </c>
       <c r="L12" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
@@ -1429,7 +1443,9 @@
       <c r="J13" s="5" t="n">
         <v>0.009900000000000001</v>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="n">
+        <v>0.0107</v>
+      </c>
       <c r="L13" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
@@ -1512,7 +1528,9 @@
       <c r="J14" s="5" t="n">
         <v>0.0375</v>
       </c>
-      <c r="K14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="n">
+        <v>0.1631</v>
+      </c>
       <c r="L14" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -1595,7 +1613,9 @@
       <c r="J15" s="5" t="n">
         <v>0.053</v>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="n">
+        <v>0.1078</v>
+      </c>
       <c r="L15" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
@@ -1678,7 +1698,9 @@
       <c r="J16" s="5" t="n">
         <v>0.004</v>
       </c>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="n">
+        <v>0.0116</v>
+      </c>
       <c r="L16" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -1745,7 +1767,9 @@
       <c r="J17" s="5" t="n">
         <v>0.1852</v>
       </c>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="n">
+        <v>0.2878</v>
+      </c>
       <c r="L17" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
@@ -1883,7 +1907,9 @@
       <c r="J19" s="5" t="n">
         <v>0.0682</v>
       </c>
-      <c r="K19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="n">
+        <v>0.2172</v>
+      </c>
       <c r="L19" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -1966,7 +1992,9 @@
       <c r="J20" s="5" t="n">
         <v>0.0743</v>
       </c>
-      <c r="K20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="n">
+        <v>0.0356</v>
+      </c>
       <c r="L20" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -2049,7 +2077,9 @@
       <c r="J21" s="5" t="n">
         <v>0.1862</v>
       </c>
-      <c r="K21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="n">
+        <v>0.2762</v>
+      </c>
       <c r="L21" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -2197,7 +2227,9 @@
       <c r="J23" s="5" t="n">
         <v>0.0888</v>
       </c>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="n">
+        <v>0.0722</v>
+      </c>
       <c r="L23" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -2280,7 +2312,9 @@
       <c r="J24" s="5" t="n">
         <v>0.1948</v>
       </c>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="n">
+        <v>0.2924</v>
+      </c>
       <c r="L24" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -2361,7 +2395,9 @@
         <v>66</v>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="n">
+        <v>0.1903</v>
+      </c>
       <c r="L25" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
@@ -2428,7 +2464,9 @@
       <c r="J26" s="5" t="n">
         <v>0.0726</v>
       </c>
-      <c r="K26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="n">
+        <v>0.036</v>
+      </c>
       <c r="L26" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -2576,7 +2614,9 @@
       <c r="J28" s="5" t="n">
         <v>0.1106</v>
       </c>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="n">
+        <v>0.3019</v>
+      </c>
       <c r="L28" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -2653,7 +2693,9 @@
       <c r="J29" s="5" t="n">
         <v>0.0506</v>
       </c>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="n">
+        <v>0.2329</v>
+      </c>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="n">
@@ -2716,7 +2758,9 @@
       <c r="J30" s="5" t="n">
         <v>0.007900000000000001</v>
       </c>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="n">
+        <v>0.0236</v>
+      </c>
       <c r="L30" s="5" t="n">
         <v>0.216663358752891</v>
       </c>
@@ -2854,7 +2898,9 @@
       <c r="J32" s="5" t="n">
         <v>0.3056</v>
       </c>
-      <c r="K32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="n">
+        <v>0.2647</v>
+      </c>
       <c r="L32" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -2937,7 +2983,9 @@
       <c r="J33" s="5" t="n">
         <v>0.0897</v>
       </c>
-      <c r="K33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="n">
+        <v>0.2016</v>
+      </c>
       <c r="L33" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -3020,7 +3068,9 @@
       <c r="J34" s="5" t="n">
         <v>0.0113</v>
       </c>
-      <c r="K34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="n">
+        <v>0.028</v>
+      </c>
       <c r="L34" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -3103,7 +3153,9 @@
       <c r="J35" s="5" t="n">
         <v>0.07539999999999999</v>
       </c>
-      <c r="K35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="n">
+        <v>0.2026</v>
+      </c>
       <c r="L35" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -3186,7 +3238,9 @@
       <c r="J36" s="5" t="n">
         <v>0.0959</v>
       </c>
-      <c r="K36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="n">
+        <v>0.1819</v>
+      </c>
       <c r="L36" s="5" t="n">
         <v>0.219325121104852</v>
       </c>
@@ -3269,7 +3323,9 @@
       <c r="J37" s="5" t="n">
         <v>0.1111</v>
       </c>
-      <c r="K37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="n">
+        <v>0.2397</v>
+      </c>
       <c r="L37" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
@@ -3417,7 +3473,9 @@
       <c r="J39" s="5" t="n">
         <v>0.1905</v>
       </c>
-      <c r="K39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="n">
+        <v>0.3104</v>
+      </c>
       <c r="L39" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
@@ -3500,7 +3558,9 @@
       <c r="J40" s="5" t="n">
         <v>0.3423</v>
       </c>
-      <c r="K40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="n">
+        <v>0.3946</v>
+      </c>
       <c r="L40" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -3583,7 +3643,9 @@
       <c r="J41" s="5" t="n">
         <v>0.3471</v>
       </c>
-      <c r="K41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="n">
+        <v>0.3901</v>
+      </c>
       <c r="L41" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -3660,7 +3722,9 @@
       <c r="J42" s="5" t="n">
         <v>0.1226</v>
       </c>
-      <c r="K42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="n">
+        <v>0.0295</v>
+      </c>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
       <c r="N42" s="5" t="n">
@@ -3723,7 +3787,9 @@
       <c r="J43" s="5" t="n">
         <v>0.2744</v>
       </c>
-      <c r="K43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="n">
+        <v>0.2787</v>
+      </c>
       <c r="L43" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -3806,7 +3872,9 @@
       <c r="J44" s="5" t="n">
         <v>0.1592</v>
       </c>
-      <c r="K44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="n">
+        <v>0.0599</v>
+      </c>
       <c r="L44" s="5" t="n">
         <v>0.23173278497921</v>
       </c>
@@ -3889,7 +3957,9 @@
       <c r="J45" s="5" t="n">
         <v>0.1286</v>
       </c>
-      <c r="K45" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="n">
+        <v>0.177</v>
+      </c>
       <c r="L45" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -3964,7 +4034,9 @@
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="n">
+        <v>0.0416</v>
+      </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="n">
@@ -4019,7 +4091,9 @@
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="n">
+        <v>0.0284</v>
+      </c>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="n">
@@ -4076,7 +4150,9 @@
       <c r="J48" s="5" t="n">
         <v>0.029</v>
       </c>
-      <c r="K48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="n">
+        <v>0.0516</v>
+      </c>
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr"/>
       <c r="N48" s="5" t="n">
@@ -4133,7 +4209,9 @@
       <c r="J49" s="5" t="n">
         <v>0.0032</v>
       </c>
-      <c r="K49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
       <c r="N49" s="5" t="n">
@@ -4190,7 +4268,9 @@
       <c r="J50" s="5" t="n">
         <v>0.0136</v>
       </c>
-      <c r="K50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="n">
+        <v>0.0726</v>
+      </c>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
       <c r="N50" s="5" t="n">
@@ -4247,7 +4327,9 @@
       <c r="J51" s="5" t="n">
         <v>0.0236</v>
       </c>
-      <c r="K51" s="5" t="inlineStr"/>
+      <c r="K51" s="5" t="n">
+        <v>0.0135</v>
+      </c>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
       <c r="N51" s="5" t="n">
@@ -4302,7 +4384,9 @@
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="n">
+        <v>0.0035</v>
+      </c>
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="n">
@@ -4359,7 +4443,9 @@
       <c r="J53" s="5" t="n">
         <v>0.0396</v>
       </c>
-      <c r="K53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="n">
+        <v>0.0188</v>
+      </c>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
       <c r="N53" s="5" t="n">
@@ -4414,7 +4500,9 @@
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="n">
+        <v>0.0038</v>
+      </c>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
       <c r="N54" s="5" t="n">
@@ -4706,7 +4794,9 @@
         <v>0.8948</v>
       </c>
       <c r="E2" s="5" t="inlineStr"/>
-      <c r="F2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="n">
+        <v>0.1085</v>
+      </c>
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
@@ -4892,7 +4982,9 @@
       <c r="E5" s="5" t="n">
         <v>0.0221</v>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>0.0123</v>
+      </c>
       <c r="G5" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
@@ -5094,7 +5186,9 @@
       <c r="E8" s="5" t="n">
         <v>0.1154</v>
       </c>
-      <c r="F8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="n">
+        <v>0.247</v>
+      </c>
       <c r="G8" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
@@ -5176,7 +5270,9 @@
       <c r="E9" s="5" t="n">
         <v>0.1651</v>
       </c>
-      <c r="F9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="n">
+        <v>0.246</v>
+      </c>
       <c r="G9" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -5258,7 +5354,9 @@
       <c r="E10" s="5" t="n">
         <v>0.0201</v>
       </c>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="n">
+        <v>0.0699</v>
+      </c>
       <c r="G10" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -5340,7 +5438,9 @@
       <c r="E11" s="5" t="n">
         <v>0.0057</v>
       </c>
-      <c r="F11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="n">
+        <v>0.0349</v>
+      </c>
       <c r="G11" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -5422,7 +5522,9 @@
       <c r="E12" s="5" t="n">
         <v>0.0264</v>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="n">
+        <v>0.0025</v>
+      </c>
       <c r="G12" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
@@ -5504,7 +5606,9 @@
       <c r="E13" s="5" t="n">
         <v>0.009900000000000001</v>
       </c>
-      <c r="F13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="n">
+        <v>0.0107</v>
+      </c>
       <c r="G13" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
@@ -5586,7 +5690,9 @@
       <c r="E14" s="5" t="n">
         <v>0.0375</v>
       </c>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="n">
+        <v>0.1631</v>
+      </c>
       <c r="G14" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -5668,7 +5774,9 @@
       <c r="E15" s="5" t="n">
         <v>0.053</v>
       </c>
-      <c r="F15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="n">
+        <v>0.1078</v>
+      </c>
       <c r="G15" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
@@ -5750,7 +5858,9 @@
       <c r="E16" s="5" t="n">
         <v>0.004</v>
       </c>
-      <c r="F16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="n">
+        <v>0.0116</v>
+      </c>
       <c r="G16" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -5816,7 +5926,9 @@
       <c r="E17" s="5" t="n">
         <v>0.1852</v>
       </c>
-      <c r="F17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="n">
+        <v>0.2878</v>
+      </c>
       <c r="G17" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
@@ -5958,7 +6070,9 @@
       <c r="E19" s="5" t="n">
         <v>0.0682</v>
       </c>
-      <c r="F19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="n">
+        <v>0.2172</v>
+      </c>
       <c r="G19" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -6040,7 +6154,9 @@
       <c r="E20" s="5" t="n">
         <v>0.0743</v>
       </c>
-      <c r="F20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="n">
+        <v>0.0356</v>
+      </c>
       <c r="G20" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -6122,7 +6238,9 @@
       <c r="E21" s="5" t="n">
         <v>0.1862</v>
       </c>
-      <c r="F21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="n">
+        <v>0.2762</v>
+      </c>
       <c r="G21" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -6268,7 +6386,9 @@
       <c r="E23" s="5" t="n">
         <v>0.0888</v>
       </c>
-      <c r="F23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="n">
+        <v>0.0722</v>
+      </c>
       <c r="G23" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -6350,7 +6470,9 @@
       <c r="E24" s="5" t="n">
         <v>0.1948</v>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="n">
+        <v>0.2924</v>
+      </c>
       <c r="G24" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -6430,7 +6552,9 @@
         <v>0.9791</v>
       </c>
       <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="n">
+        <v>0.1903</v>
+      </c>
       <c r="G25" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
@@ -6496,7 +6620,9 @@
       <c r="E26" s="5" t="n">
         <v>0.0726</v>
       </c>
-      <c r="F26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="n">
+        <v>0.036</v>
+      </c>
       <c r="G26" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -6642,7 +6768,9 @@
       <c r="E28" s="5" t="n">
         <v>0.1106</v>
       </c>
-      <c r="F28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="n">
+        <v>0.3019</v>
+      </c>
       <c r="G28" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -6724,7 +6852,9 @@
       <c r="E29" s="5" t="n">
         <v>0.0506</v>
       </c>
-      <c r="F29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="n">
+        <v>0.2329</v>
+      </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
@@ -6786,7 +6916,9 @@
       <c r="E30" s="5" t="n">
         <v>0.007900000000000001</v>
       </c>
-      <c r="F30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="n">
+        <v>0.0236</v>
+      </c>
       <c r="G30" s="5" t="n">
         <v>0.216663358752891</v>
       </c>
@@ -6928,7 +7060,9 @@
       <c r="E32" s="5" t="n">
         <v>0.3056</v>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="n">
+        <v>0.2647</v>
+      </c>
       <c r="G32" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -7010,7 +7144,9 @@
       <c r="E33" s="5" t="n">
         <v>0.0897</v>
       </c>
-      <c r="F33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="n">
+        <v>0.2016</v>
+      </c>
       <c r="G33" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -7092,7 +7228,9 @@
       <c r="E34" s="5" t="n">
         <v>0.0113</v>
       </c>
-      <c r="F34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="n">
+        <v>0.028</v>
+      </c>
       <c r="G34" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
@@ -7174,7 +7312,9 @@
       <c r="E35" s="5" t="n">
         <v>0.07539999999999999</v>
       </c>
-      <c r="F35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="n">
+        <v>0.2026</v>
+      </c>
       <c r="G35" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
@@ -7256,7 +7396,9 @@
       <c r="E36" s="5" t="n">
         <v>0.0959</v>
       </c>
-      <c r="F36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="n">
+        <v>0.1819</v>
+      </c>
       <c r="G36" s="5" t="n">
         <v>0.219325121104852</v>
       </c>
@@ -7338,7 +7480,9 @@
       <c r="E37" s="5" t="n">
         <v>0.1111</v>
       </c>
-      <c r="F37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="n">
+        <v>0.2397</v>
+      </c>
       <c r="G37" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
@@ -7484,7 +7628,9 @@
       <c r="E39" s="5" t="n">
         <v>0.1905</v>
       </c>
-      <c r="F39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="n">
+        <v>0.3104</v>
+      </c>
       <c r="G39" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
@@ -7566,7 +7712,9 @@
       <c r="E40" s="5" t="n">
         <v>0.3423</v>
       </c>
-      <c r="F40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="n">
+        <v>0.3946</v>
+      </c>
       <c r="G40" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -7648,7 +7796,9 @@
       <c r="E41" s="5" t="n">
         <v>0.3471</v>
       </c>
-      <c r="F41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="n">
+        <v>0.3901</v>
+      </c>
       <c r="G41" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -7730,7 +7880,9 @@
       <c r="E42" s="5" t="n">
         <v>0.1226</v>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="n">
+        <v>0.0295</v>
+      </c>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
@@ -7792,7 +7944,9 @@
       <c r="E43" s="5" t="n">
         <v>0.2744</v>
       </c>
-      <c r="F43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="n">
+        <v>0.2787</v>
+      </c>
       <c r="G43" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
@@ -7874,7 +8028,9 @@
       <c r="E44" s="5" t="n">
         <v>0.1592</v>
       </c>
-      <c r="F44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="n">
+        <v>0.0599</v>
+      </c>
       <c r="G44" s="5" t="n">
         <v>0.23173278497921</v>
       </c>
@@ -7956,7 +8112,9 @@
       <c r="E45" s="5" t="n">
         <v>0.1286</v>
       </c>
-      <c r="F45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="n">
+        <v>0.177</v>
+      </c>
       <c r="G45" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
@@ -8036,7 +8194,9 @@
         <v>0.9313</v>
       </c>
       <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="n">
+        <v>0.0416</v>
+      </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
@@ -8096,7 +8256,9 @@
         <v>0.9313</v>
       </c>
       <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="n">
+        <v>0.0284</v>
+      </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
@@ -8158,7 +8320,9 @@
       <c r="E48" s="5" t="n">
         <v>0.029</v>
       </c>
-      <c r="F48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="n">
+        <v>0.0516</v>
+      </c>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
@@ -8220,7 +8384,9 @@
       <c r="E49" s="5" t="n">
         <v>0.0032</v>
       </c>
-      <c r="F49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
@@ -8282,7 +8448,9 @@
       <c r="E50" s="5" t="n">
         <v>0.0136</v>
       </c>
-      <c r="F50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="n">
+        <v>0.0726</v>
+      </c>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
@@ -8344,7 +8512,9 @@
       <c r="E51" s="5" t="n">
         <v>0.0236</v>
       </c>
-      <c r="F51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="n">
+        <v>0.0135</v>
+      </c>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
@@ -8404,7 +8574,9 @@
         <v>0.9729</v>
       </c>
       <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="n">
+        <v>0.0035</v>
+      </c>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
@@ -8466,7 +8638,9 @@
       <c r="E53" s="5" t="n">
         <v>0.0396</v>
       </c>
-      <c r="F53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="n">
+        <v>0.0188</v>
+      </c>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
@@ -8526,7 +8700,9 @@
         <v>0.9701</v>
       </c>
       <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="n">
+        <v>0.0038</v>
+      </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
